--- a/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_DisenoDigital_VNAL.xlsx
+++ b/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_DisenoDigital_VNAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/micortes_poligran_edu_co/Documents/Escritorio/FORMATOS RA CICLO UNO RC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/FORMATOS RA CICLO UNO RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{9F3238FD-F2D7-44E0-A51B-8284BC0EC71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB14615-B7CE-4457-BE5F-D3E0CA7D40C9}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{9F3238FD-F2D7-44E0-A51B-8284BC0EC71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0AA0464-0DE7-49EC-AD2C-0353E22F47BF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Paso1 Analisis perfil egreso" sheetId="1" r:id="rId1"/>
@@ -1914,6 +1914,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Reconoce los criterios, las técnicas y tecnologías requeridas en la elaboración de animaciones dentro del contexto digital, </t>
@@ -1923,6 +1924,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">para crear soluciones de problemas asociados al diseño digital y a la publicidad. 
 Desarrolla los procesos (boceto, </t>
@@ -1933,6 +1935,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t>storyboard</t>
     </r>
@@ -1941,6 +1944,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">, composición, aplicación de color, creación de secuencias y movimientos) para elaborar animaciones aplicando los conceptos de color, fotografía, imagen vectorial y tipografía, entre otros. </t>
     </r>
@@ -3602,7 +3606,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3761,28 +3765,27 @@
     <font>
       <sz val="11"/>
       <name val="Gill Sans MT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Gill Sans MT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Gill Sans MT"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Gill Sans MT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4461,94 +4464,11 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4562,15 +4482,39 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -4581,18 +4525,77 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7777,7 +7780,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="4" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla 1" pivot="0" count="1" xr9:uid="{D31AC5D5-9EFB-4153-9086-9AA6037B7BF8}">
       <tableStyleElement type="headerRow" dxfId="151"/>
     </tableStyle>
@@ -7787,6 +7790,7 @@
     <tableStyle name="Estilo de tabla 3" pivot="0" count="1" xr9:uid="{BD8219D8-F95E-4ADD-BD98-5883EDA7E91C}">
       <tableStyleElement type="headerRow" dxfId="149"/>
     </tableStyle>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{20570D63-01AE-4314-AEDD-CFD080479D8F}"/>
   </tableStyles>
   <colors>
     <mruColors>
@@ -8685,22 +8689,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FA7EDF-246F-4EE0-BFE4-7EACACD45C48}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="76.26953125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="76.21875" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" style="21" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="53.54296875" style="21" customWidth="1"/>
-    <col min="4" max="4" width="42.7265625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="32.1796875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="53.5546875" style="21" customWidth="1"/>
+    <col min="4" max="4" width="42.77734375" style="21" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" style="21" customWidth="1"/>
     <col min="6" max="6" width="34" style="12" customWidth="1"/>
     <col min="7" max="7" width="51" style="21" customWidth="1"/>
-    <col min="8" max="8" width="23.54296875" style="21" customWidth="1"/>
-    <col min="9" max="9" width="30.26953125" style="21" customWidth="1"/>
-    <col min="10" max="10" width="52.453125" style="21" customWidth="1"/>
-    <col min="11" max="16384" width="76.26953125" style="21"/>
+    <col min="8" max="8" width="23.5546875" style="21" customWidth="1"/>
+    <col min="9" max="9" width="30.21875" style="21" customWidth="1"/>
+    <col min="10" max="10" width="52.44140625" style="21" customWidth="1"/>
+    <col min="11" max="16384" width="76.21875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="19" customFormat="1" ht="42.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="19" customFormat="1" ht="42" x14ac:dyDescent="0.3">
       <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
@@ -8713,21 +8717,21 @@
       <c r="D1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="138" t="s">
+      <c r="E1" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138" t="s">
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
       <c r="K1" s="132" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="133" t="s">
         <v>7</v>
       </c>
@@ -8762,17 +8766,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="43" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="137" t="s">
+    <row r="3" spans="1:11" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="137" t="s">
+      <c r="C3" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="137" t="s">
+      <c r="D3" s="141" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="16" t="s">
@@ -8784,24 +8788,24 @@
       <c r="G3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="139" t="s">
+      <c r="H3" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="139" t="s">
+      <c r="I3" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="139" t="s">
+      <c r="J3" s="156" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="137" t="s">
+      <c r="K3" s="141" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="137"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
+    <row r="4" spans="1:11" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="141"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
       <c r="E4" s="22" t="s">
         <v>29</v>
       </c>
@@ -8811,16 +8815,16 @@
       <c r="G4" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="139"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="139"/>
-      <c r="K4" s="137"/>
-    </row>
-    <row r="5" spans="1:11" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="137"/>
-      <c r="B5" s="137"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="141"/>
+    </row>
+    <row r="5" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="141"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
       <c r="E5" s="98" t="s">
         <v>32</v>
       </c>
@@ -8830,16 +8834,16 @@
       <c r="G5" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="139"/>
-      <c r="I5" s="139"/>
-      <c r="J5" s="139"/>
-      <c r="K5" s="137"/>
-    </row>
-    <row r="6" spans="1:11" ht="74.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="137"/>
-      <c r="B6" s="137"/>
-      <c r="C6" s="137"/>
-      <c r="D6" s="137"/>
+      <c r="H5" s="156"/>
+      <c r="I5" s="156"/>
+      <c r="J5" s="156"/>
+      <c r="K5" s="141"/>
+    </row>
+    <row r="6" spans="1:11" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="141"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="141"/>
+      <c r="D6" s="141"/>
       <c r="E6" s="21" t="s">
         <v>35</v>
       </c>
@@ -8849,51 +8853,51 @@
       <c r="G6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="139"/>
-      <c r="I6" s="139"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="137"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H6" s="156"/>
+      <c r="I6" s="156"/>
+      <c r="J6" s="156"/>
+      <c r="K6" s="141"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" s="20"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E8" s="22"/>
       <c r="F8" s="16"/>
       <c r="G8" s="22"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
@@ -8922,30 +8926,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C1850E-A9C8-4F69-8E80-DEAF9721FFBF}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="21" customWidth="1"/>
     <col min="2" max="2" width="18" style="21" customWidth="1"/>
-    <col min="3" max="3" width="30.453125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="30.44140625" style="21" customWidth="1"/>
     <col min="4" max="4" width="34" style="21" customWidth="1"/>
-    <col min="5" max="5" width="56.7265625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="90.453125" style="21" customWidth="1"/>
-    <col min="7" max="7" width="32.453125" style="21" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="21"/>
+    <col min="5" max="5" width="56.77734375" style="21" customWidth="1"/>
+    <col min="6" max="6" width="90.44140625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="32.44140625" style="21" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="140" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-    </row>
-    <row r="2" spans="1:7" s="30" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+    </row>
+    <row r="2" spans="1:7" s="30" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A2" s="114" t="s">
         <v>39</v>
       </c>
@@ -8968,7 +8972,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="33" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="33" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="117" t="s">
         <v>46</v>
       </c>
@@ -8991,7 +8995,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>1</v>
       </c>
@@ -9014,7 +9018,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="20" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2</v>
       </c>
@@ -9037,7 +9041,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="36" x14ac:dyDescent="0.3">
       <c r="A6" s="123">
         <v>3</v>
       </c>
@@ -9060,7 +9064,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>4</v>
       </c>
@@ -9083,35 +9087,35 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="20"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
       <c r="F11" s="20"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
@@ -9156,21 +9160,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AAF649-42F4-466A-BE11-44357078F961}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="77.453125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="19" customWidth="1"/>
+    <col min="1" max="1" width="77.44140625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="19" customWidth="1"/>
     <col min="3" max="3" width="23" style="21" customWidth="1"/>
-    <col min="4" max="4" width="30.7265625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="25.54296875" style="21" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="21.81640625" style="21" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="27.453125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" style="21" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" style="21" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" style="21" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" style="12" customWidth="1"/>
     <col min="8" max="8" width="20" style="12" customWidth="1"/>
     <col min="9" max="9" width="72" style="39" customWidth="1"/>
-    <col min="10" max="16384" width="11.453125" style="16"/>
+    <col min="10" max="16384" width="11.44140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="35" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="35" customFormat="1" ht="48" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>63</v>
       </c>
@@ -9199,7 +9203,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>72</v>
       </c>
@@ -9228,7 +9232,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>54</v>
       </c>
@@ -9257,7 +9261,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" ht="36" x14ac:dyDescent="0.5">
       <c r="A4" s="21" t="s">
         <v>54</v>
       </c>
@@ -9287,7 +9291,7 @@
       </c>
       <c r="K4" s="68"/>
     </row>
-    <row r="5" spans="1:11" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>54</v>
       </c>
@@ -9316,7 +9320,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="22" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="22" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>57</v>
       </c>
@@ -9345,7 +9349,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="22" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="22" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>57</v>
       </c>
@@ -9374,7 +9378,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="22" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" s="22" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="42" t="s">
         <v>57</v>
       </c>
@@ -9403,7 +9407,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="25" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="25" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>59</v>
       </c>
@@ -9432,7 +9436,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="25" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="25" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>59</v>
       </c>
@@ -9461,7 +9465,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="25" customFormat="1" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" s="25" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="42" t="s">
         <v>59</v>
       </c>
@@ -9490,7 +9494,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>61</v>
       </c>
@@ -9519,7 +9523,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -9529,7 +9533,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="16"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -9539,7 +9543,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="16"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -9549,7 +9553,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="16"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -9559,7 +9563,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -9569,7 +9573,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="16"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -9579,7 +9583,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="20"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="20"/>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
@@ -9626,18 +9630,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F726B80-E6B4-4ED4-A764-E59AF4E18393}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="98.81640625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="98.77734375" style="12" customWidth="1"/>
     <col min="2" max="2" width="55" style="50" customWidth="1"/>
-    <col min="3" max="3" width="44.54296875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="61.54296875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="39.1796875" style="12" customWidth="1"/>
-    <col min="6" max="6" width="47.7265625" style="12" customWidth="1"/>
-    <col min="7" max="16384" width="11.453125" style="12"/>
+    <col min="3" max="3" width="44.5546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="61.5546875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="39.21875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="47.77734375" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>104</v>
       </c>
@@ -9657,7 +9661,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>110</v>
       </c>
@@ -9677,289 +9681,298 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="C3" s="167" t="s">
         <v>117</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="154" t="s">
+      <c r="E3" s="163" t="s">
         <v>119</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="152"/>
-      <c r="C4" s="152"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="168"/>
       <c r="D4" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="149"/>
+      <c r="E4" s="164"/>
       <c r="F4" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
       <c r="D5" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="150"/>
+      <c r="E5" s="165"/>
       <c r="F5" s="40" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A6" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="151" t="s">
+      <c r="B6" s="167" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="151" t="s">
+      <c r="C6" s="167" t="s">
         <v>127</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="148" t="s">
+      <c r="E6" s="166" t="s">
         <v>128</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
+      <c r="B7" s="168"/>
+      <c r="C7" s="168"/>
       <c r="D7" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="149"/>
+      <c r="E7" s="164"/>
       <c r="F7" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="153"/>
-      <c r="C8" s="153"/>
+      <c r="B8" s="169"/>
+      <c r="C8" s="169"/>
       <c r="D8" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="150"/>
+      <c r="E8" s="165"/>
       <c r="F8" s="40" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A9" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="151" t="s">
+      <c r="B9" s="167" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="151" t="s">
+      <c r="C9" s="167" t="s">
         <v>130</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="148" t="s">
+      <c r="E9" s="166" t="s">
         <v>131</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="152"/>
-      <c r="C10" s="152"/>
+      <c r="B10" s="168"/>
+      <c r="C10" s="168"/>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="149"/>
+      <c r="E10" s="164"/>
       <c r="F10" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="153"/>
-      <c r="C11" s="153"/>
+      <c r="B11" s="169"/>
+      <c r="C11" s="169"/>
       <c r="D11" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="E11" s="150"/>
+      <c r="E11" s="165"/>
       <c r="F11" s="40" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="151" t="s">
+      <c r="B12" s="167" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="151" t="s">
+      <c r="C12" s="167" t="s">
         <v>133</v>
       </c>
       <c r="D12" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="E12" s="148" t="s">
+      <c r="E12" s="166" t="s">
         <v>134</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="152"/>
-      <c r="C13" s="152"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="168"/>
       <c r="D13" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E13" s="149"/>
+      <c r="E13" s="164"/>
       <c r="F13" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="153"/>
-      <c r="C14" s="153"/>
+      <c r="B14" s="169"/>
+      <c r="C14" s="169"/>
       <c r="D14" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="150"/>
+      <c r="E14" s="165"/>
       <c r="F14" s="40" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A15" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="146" t="s">
+      <c r="B15" s="140" t="s">
         <v>135</v>
       </c>
       <c r="C15" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="148" t="s">
+      <c r="D15" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="144" t="s">
+      <c r="E15" s="171" t="s">
         <v>137</v>
       </c>
-      <c r="F15" s="142" t="s">
+      <c r="F15" s="155" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="99" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="108" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="137"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="D16" s="149"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="139"/>
-    </row>
-    <row r="17" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+      <c r="D16" s="164"/>
+      <c r="E16" s="171"/>
+      <c r="F16" s="156"/>
+    </row>
+    <row r="17" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="137"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="D17" s="143" t="s">
+      <c r="D17" s="170" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="144"/>
-      <c r="F17" s="143" t="s">
+      <c r="E17" s="171"/>
+      <c r="F17" s="170" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="137"/>
+      <c r="B18" s="141"/>
       <c r="C18" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="143"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="143"/>
-    </row>
-    <row r="19" spans="1:6" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D18" s="170"/>
+      <c r="E18" s="171"/>
+      <c r="F18" s="170"/>
+    </row>
+    <row r="19" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="108"/>
-      <c r="B19" s="147"/>
+      <c r="B19" s="143"/>
       <c r="C19" s="122" t="s">
         <v>142</v>
       </c>
       <c r="D19" s="109" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="145"/>
+      <c r="E19" s="172"/>
       <c r="F19" s="109" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="21"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="21"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="21"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="E6:E8"/>
@@ -9969,15 +9982,6 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="E15:E19"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D17:D18"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A18 A20:A24" xr:uid="{D048ED25-334D-4F32-B2A7-D11385F03FF6}">
@@ -9993,27 +9997,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CB1331-AF3E-489A-B433-09E21B4DF482}">
   <dimension ref="A1:S202"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="58.7265625" defaultRowHeight="16" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="58.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" style="65" customWidth="1"/>
-    <col min="2" max="2" width="73.453125" style="57" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" style="51" customWidth="1"/>
-    <col min="4" max="4" width="24.54296875" style="52" customWidth="1"/>
-    <col min="5" max="5" width="66.7265625" style="65" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" style="51" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" style="51" customWidth="1"/>
-    <col min="8" max="10" width="14.26953125" style="51" customWidth="1"/>
-    <col min="11" max="13" width="16.7265625" style="51" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="73.44140625" style="57" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" style="51" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" style="52" customWidth="1"/>
+    <col min="5" max="5" width="66.77734375" style="65" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" style="51" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="51" customWidth="1"/>
+    <col min="8" max="10" width="14.21875" style="51" customWidth="1"/>
+    <col min="11" max="13" width="16.77734375" style="51" customWidth="1"/>
     <col min="14" max="14" width="36" style="65" customWidth="1"/>
-    <col min="15" max="15" width="40.453125" style="65" customWidth="1"/>
-    <col min="16" max="16" width="45.81640625" style="65" customWidth="1"/>
-    <col min="17" max="17" width="58.7265625" style="65"/>
-    <col min="18" max="18" width="4.54296875" style="65" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.453125" style="51" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="58.7265625" style="51"/>
+    <col min="15" max="15" width="40.44140625" style="65" customWidth="1"/>
+    <col min="16" max="16" width="45.77734375" style="65" customWidth="1"/>
+    <col min="17" max="17" width="58.77734375" style="65"/>
+    <col min="18" max="18" width="4.5546875" style="65" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.44140625" style="51" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="58.77734375" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="12" customFormat="1" ht="78" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" s="12" customFormat="1" ht="84" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>143</v>
       </c>
@@ -10032,11 +10036,11 @@
       <c r="F1" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="155" t="s">
+      <c r="G1" s="158" t="s">
         <v>149</v>
       </c>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
       <c r="J1" s="18" t="s">
         <v>150</v>
       </c>
@@ -10063,7 +10067,7 @@
       </c>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:19" s="12" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" s="12" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="130" t="s">
         <v>158</v>
       </c>
@@ -10117,7 +10121,7 @@
       </c>
       <c r="R2" s="24"/>
     </row>
-    <row r="3" spans="1:19" s="50" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" s="50" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="106" t="str">
         <f>_xlfn.XLOOKUP(B3,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10171,7 +10175,7 @@
       </c>
       <c r="R3" s="24"/>
     </row>
-    <row r="4" spans="1:19" s="50" customFormat="1" ht="297" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" s="50" customFormat="1" ht="342" x14ac:dyDescent="0.3">
       <c r="A4" s="106" t="str">
         <f>_xlfn.XLOOKUP(B4,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10223,7 +10227,7 @@
       </c>
       <c r="R4" s="24"/>
     </row>
-    <row r="5" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="str">
         <f>_xlfn.XLOOKUP(B5,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10231,53 +10235,53 @@
       <c r="B5" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="156">
+      <c r="C5" s="153">
         <v>1</v>
       </c>
-      <c r="D5" s="156" t="s">
+      <c r="D5" s="153" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="159" t="s">
+      <c r="E5" s="145" t="s">
         <v>187</v>
       </c>
-      <c r="F5" s="156" t="s">
+      <c r="F5" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156" t="s">
+      <c r="G5" s="153"/>
+      <c r="H5" s="153" t="s">
         <v>177</v>
       </c>
-      <c r="I5" s="156"/>
-      <c r="J5" s="156">
+      <c r="I5" s="153"/>
+      <c r="J5" s="153">
         <v>2</v>
       </c>
-      <c r="K5" s="156">
+      <c r="K5" s="153">
         <f>J5*12</f>
         <v>24</v>
       </c>
-      <c r="L5" s="156">
+      <c r="L5" s="153">
         <f>36*J5</f>
         <v>72</v>
       </c>
-      <c r="M5" s="156">
+      <c r="M5" s="153">
         <f>SUM(K5:L5)</f>
         <v>96</v>
       </c>
-      <c r="N5" s="159" t="s">
+      <c r="N5" s="145" t="s">
         <v>189</v>
       </c>
-      <c r="O5" s="159" t="s">
+      <c r="O5" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="P5" s="159" t="s">
+      <c r="P5" s="145" t="s">
         <v>190</v>
       </c>
-      <c r="Q5" s="159" t="s">
+      <c r="Q5" s="145" t="s">
         <v>185</v>
       </c>
       <c r="R5" s="24"/>
     </row>
-    <row r="6" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="str">
         <f>_xlfn.XLOOKUP(B6,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10285,24 +10289,24 @@
       <c r="B6" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="156"/>
-      <c r="L6" s="156"/>
-      <c r="M6" s="156"/>
-      <c r="N6" s="159"/>
-      <c r="O6" s="159"/>
-      <c r="P6" s="159"/>
-      <c r="Q6" s="159"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="145"/>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145"/>
       <c r="R6" s="24"/>
     </row>
-    <row r="7" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A7" s="97" t="str">
         <f>_xlfn.XLOOKUP(B7,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10310,24 +10314,24 @@
       <c r="B7" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="157"/>
-      <c r="D7" s="158"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="157"/>
-      <c r="K7" s="157"/>
-      <c r="L7" s="157"/>
-      <c r="M7" s="157"/>
-      <c r="N7" s="160"/>
-      <c r="O7" s="160"/>
-      <c r="P7" s="160"/>
-      <c r="Q7" s="160"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="154"/>
+      <c r="M7" s="154"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
       <c r="R7" s="24"/>
     </row>
-    <row r="8" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="str">
         <f>_xlfn.XLOOKUP(B8,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10335,53 +10339,53 @@
       <c r="B8" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="161">
+      <c r="C8" s="152">
         <v>1</v>
       </c>
-      <c r="D8" s="137" t="s">
+      <c r="D8" s="141" t="s">
         <v>191</v>
       </c>
-      <c r="E8" s="142" t="s">
+      <c r="E8" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="F8" s="146" t="s">
+      <c r="F8" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G8" s="146"/>
-      <c r="H8" s="146" t="s">
+      <c r="G8" s="140"/>
+      <c r="H8" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I8" s="146"/>
-      <c r="J8" s="146">
+      <c r="I8" s="140"/>
+      <c r="J8" s="140">
         <v>3</v>
       </c>
-      <c r="K8" s="146">
+      <c r="K8" s="140">
         <f>J8*12</f>
         <v>36</v>
       </c>
-      <c r="L8" s="146">
+      <c r="L8" s="140">
         <f>36*J8</f>
         <v>108</v>
       </c>
-      <c r="M8" s="146">
+      <c r="M8" s="140">
         <f>SUM(K8:L8)</f>
         <v>144</v>
       </c>
-      <c r="N8" s="142" t="s">
+      <c r="N8" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="O8" s="159" t="s">
+      <c r="O8" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="P8" s="159" t="s">
+      <c r="P8" s="145" t="s">
         <v>194</v>
       </c>
-      <c r="Q8" s="142" t="s">
+      <c r="Q8" s="155" t="s">
         <v>185</v>
       </c>
       <c r="R8" s="24"/>
     </row>
-    <row r="9" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="str">
         <f>_xlfn.XLOOKUP(B9,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10389,24 +10393,24 @@
       <c r="B9" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="156"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="159"/>
-      <c r="P9" s="159"/>
-      <c r="Q9" s="139"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="141"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
+      <c r="N9" s="156"/>
+      <c r="O9" s="145"/>
+      <c r="P9" s="145"/>
+      <c r="Q9" s="156"/>
       <c r="R9" s="24"/>
     </row>
-    <row r="10" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="97" t="str">
         <f>_xlfn.XLOOKUP(B10,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10414,24 +10418,24 @@
       <c r="B10" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="157"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="163"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="162"/>
-      <c r="H10" s="162"/>
-      <c r="I10" s="162"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="162"/>
-      <c r="L10" s="162"/>
-      <c r="M10" s="162"/>
-      <c r="N10" s="163"/>
-      <c r="O10" s="160"/>
-      <c r="P10" s="160"/>
-      <c r="Q10" s="163"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="157"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
+      <c r="L10" s="142"/>
+      <c r="M10" s="142"/>
+      <c r="N10" s="157"/>
+      <c r="O10" s="147"/>
+      <c r="P10" s="147"/>
+      <c r="Q10" s="157"/>
       <c r="R10" s="24"/>
     </row>
-    <row r="11" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="str">
         <f>_xlfn.XLOOKUP(B11,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10439,53 +10443,53 @@
       <c r="B11" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="161">
+      <c r="C11" s="152">
         <v>1</v>
       </c>
-      <c r="D11" s="161" t="s">
+      <c r="D11" s="152" t="s">
         <v>195</v>
       </c>
-      <c r="E11" s="164" t="s">
+      <c r="E11" s="137" t="s">
         <v>196</v>
       </c>
-      <c r="F11" s="146" t="s">
+      <c r="F11" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161" t="s">
+      <c r="G11" s="152"/>
+      <c r="H11" s="152" t="s">
         <v>177</v>
       </c>
-      <c r="I11" s="161"/>
-      <c r="J11" s="161">
+      <c r="I11" s="152"/>
+      <c r="J11" s="152">
         <v>3</v>
       </c>
-      <c r="K11" s="161">
+      <c r="K11" s="152">
         <f>J11*12</f>
         <v>36</v>
       </c>
-      <c r="L11" s="161">
+      <c r="L11" s="152">
         <f>36*J11</f>
         <v>108</v>
       </c>
-      <c r="M11" s="161">
+      <c r="M11" s="152">
         <f>SUM(K11:L11)</f>
         <v>144</v>
       </c>
-      <c r="N11" s="164" t="s">
+      <c r="N11" s="137" t="s">
         <v>197</v>
       </c>
-      <c r="O11" s="159" t="s">
+      <c r="O11" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="P11" s="159" t="s">
+      <c r="P11" s="145" t="s">
         <v>194</v>
       </c>
-      <c r="Q11" s="164" t="s">
+      <c r="Q11" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R11" s="24"/>
     </row>
-    <row r="12" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="str">
         <f>_xlfn.XLOOKUP(B12,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10493,24 +10497,24 @@
       <c r="B12" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="156"/>
-      <c r="D12" s="156"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
-      <c r="L12" s="156"/>
-      <c r="M12" s="156"/>
-      <c r="N12" s="165"/>
-      <c r="O12" s="159"/>
-      <c r="P12" s="159"/>
-      <c r="Q12" s="165"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="138"/>
+      <c r="O12" s="145"/>
+      <c r="P12" s="145"/>
+      <c r="Q12" s="138"/>
       <c r="R12" s="24"/>
     </row>
-    <row r="13" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="97" t="str">
         <f>_xlfn.XLOOKUP(B13,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10518,24 +10522,24 @@
       <c r="B13" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="157"/>
-      <c r="D13" s="157"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="157"/>
-      <c r="H13" s="157"/>
-      <c r="I13" s="157"/>
-      <c r="J13" s="157"/>
-      <c r="K13" s="157"/>
-      <c r="L13" s="157"/>
-      <c r="M13" s="157"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="160"/>
-      <c r="P13" s="160"/>
-      <c r="Q13" s="166"/>
+      <c r="C13" s="154"/>
+      <c r="D13" s="154"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="154"/>
+      <c r="H13" s="154"/>
+      <c r="I13" s="154"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="154"/>
+      <c r="L13" s="154"/>
+      <c r="M13" s="154"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="139"/>
       <c r="R13" s="24"/>
     </row>
-    <row r="14" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="str">
         <f>_xlfn.XLOOKUP(B14,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10543,53 +10547,53 @@
       <c r="B14" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="146">
+      <c r="C14" s="140">
         <v>1</v>
       </c>
-      <c r="D14" s="146" t="s">
+      <c r="D14" s="140" t="s">
         <v>198</v>
       </c>
-      <c r="E14" s="164" t="s">
+      <c r="E14" s="137" t="s">
         <v>199</v>
       </c>
-      <c r="F14" s="146" t="s">
+      <c r="F14" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G14" s="146"/>
-      <c r="H14" s="146" t="s">
+      <c r="G14" s="140"/>
+      <c r="H14" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I14" s="146"/>
-      <c r="J14" s="146">
+      <c r="I14" s="140"/>
+      <c r="J14" s="140">
         <v>3</v>
       </c>
-      <c r="K14" s="146">
+      <c r="K14" s="140">
         <f>J14*12</f>
         <v>36</v>
       </c>
-      <c r="L14" s="146">
+      <c r="L14" s="140">
         <f>36*J14</f>
         <v>108</v>
       </c>
-      <c r="M14" s="146">
+      <c r="M14" s="140">
         <f>SUM(K14:L14)</f>
         <v>144</v>
       </c>
-      <c r="N14" s="164" t="s">
+      <c r="N14" s="137" t="s">
         <v>200</v>
       </c>
-      <c r="O14" s="159" t="s">
+      <c r="O14" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="P14" s="159" t="s">
+      <c r="P14" s="145" t="s">
         <v>201</v>
       </c>
-      <c r="Q14" s="164" t="s">
+      <c r="Q14" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R14" s="24"/>
     </row>
-    <row r="15" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="str">
         <f>_xlfn.XLOOKUP(B15,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10597,24 +10601,24 @@
       <c r="B15" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="165"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="165"/>
-      <c r="O15" s="159"/>
-      <c r="P15" s="159"/>
-      <c r="Q15" s="165"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="141"/>
+      <c r="M15" s="141"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="145"/>
+      <c r="P15" s="145"/>
+      <c r="Q15" s="138"/>
       <c r="R15" s="24"/>
     </row>
-    <row r="16" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A16" s="97" t="str">
         <f>_xlfn.XLOOKUP(B16,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10622,21 +10626,21 @@
       <c r="B16" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="162"/>
-      <c r="D16" s="162"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="162"/>
-      <c r="G16" s="162"/>
-      <c r="H16" s="162"/>
-      <c r="I16" s="162"/>
-      <c r="J16" s="162"/>
-      <c r="K16" s="162"/>
-      <c r="L16" s="162"/>
-      <c r="M16" s="162"/>
-      <c r="N16" s="166"/>
-      <c r="O16" s="160"/>
-      <c r="P16" s="160"/>
-      <c r="Q16" s="166"/>
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="142"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="142"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="142"/>
+      <c r="N16" s="139"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="147"/>
+      <c r="Q16" s="139"/>
       <c r="R16" s="24">
         <f>SUM(J3:J16)</f>
         <v>17</v>
@@ -10646,7 +10650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="50" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" s="50" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="106" t="str">
         <f>_xlfn.XLOOKUP(B17,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10700,7 +10704,7 @@
       </c>
       <c r="R17" s="24"/>
     </row>
-    <row r="18" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="str">
         <f>_xlfn.XLOOKUP(B18,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10708,53 +10712,53 @@
       <c r="B18" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="146">
+      <c r="C18" s="140">
         <v>2</v>
       </c>
-      <c r="D18" s="146" t="s">
+      <c r="D18" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="E18" s="164" t="s">
+      <c r="E18" s="137" t="s">
         <v>207</v>
       </c>
-      <c r="F18" s="146" t="s">
+      <c r="F18" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G18" s="146"/>
-      <c r="H18" s="146" t="s">
+      <c r="G18" s="140"/>
+      <c r="H18" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I18" s="146"/>
-      <c r="J18" s="146">
+      <c r="I18" s="140"/>
+      <c r="J18" s="140">
         <v>3</v>
       </c>
-      <c r="K18" s="146">
+      <c r="K18" s="140">
         <f>J18*12</f>
         <v>36</v>
       </c>
-      <c r="L18" s="146">
+      <c r="L18" s="140">
         <f>36*J18</f>
         <v>108</v>
       </c>
-      <c r="M18" s="146">
+      <c r="M18" s="140">
         <f>SUM(K18:L18)</f>
         <v>144</v>
       </c>
-      <c r="N18" s="164" t="s">
+      <c r="N18" s="137" t="s">
         <v>208</v>
       </c>
-      <c r="O18" s="164" t="s">
+      <c r="O18" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P18" s="164" t="s">
+      <c r="P18" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q18" s="164" t="s">
+      <c r="Q18" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R18" s="24"/>
     </row>
-    <row r="19" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="str">
         <f>_xlfn.XLOOKUP(B19,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10762,24 +10766,24 @@
       <c r="B19" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="137"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="165"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="137"/>
-      <c r="H19" s="137"/>
-      <c r="I19" s="137"/>
-      <c r="J19" s="137"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="165"/>
-      <c r="O19" s="165"/>
-      <c r="P19" s="165"/>
-      <c r="Q19" s="165"/>
+      <c r="C19" s="141"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="141"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="141"/>
+      <c r="L19" s="141"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="138"/>
+      <c r="O19" s="138"/>
+      <c r="P19" s="138"/>
+      <c r="Q19" s="138"/>
       <c r="R19" s="24"/>
     </row>
-    <row r="20" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="97" t="str">
         <f>_xlfn.XLOOKUP(B20,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10787,24 +10791,24 @@
       <c r="B20" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="162"/>
-      <c r="D20" s="162"/>
-      <c r="E20" s="166"/>
-      <c r="F20" s="162"/>
-      <c r="G20" s="162"/>
-      <c r="H20" s="162"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="162"/>
-      <c r="K20" s="162"/>
-      <c r="L20" s="162"/>
-      <c r="M20" s="162"/>
-      <c r="N20" s="166"/>
-      <c r="O20" s="166"/>
-      <c r="P20" s="166"/>
-      <c r="Q20" s="166"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="142"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="142"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="142"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
+      <c r="P20" s="139"/>
+      <c r="Q20" s="139"/>
       <c r="R20" s="24"/>
     </row>
-    <row r="21" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="str">
         <f>_xlfn.XLOOKUP(B21,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10812,53 +10816,53 @@
       <c r="B21" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="146">
+      <c r="C21" s="140">
         <v>2</v>
       </c>
-      <c r="D21" s="146" t="s">
+      <c r="D21" s="140" t="s">
         <v>209</v>
       </c>
-      <c r="E21" s="164" t="s">
+      <c r="E21" s="137" t="s">
         <v>210</v>
       </c>
-      <c r="F21" s="146" t="s">
+      <c r="F21" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G21" s="146"/>
-      <c r="H21" s="146" t="s">
+      <c r="G21" s="140"/>
+      <c r="H21" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I21" s="146"/>
-      <c r="J21" s="146">
+      <c r="I21" s="140"/>
+      <c r="J21" s="140">
         <v>3</v>
       </c>
-      <c r="K21" s="146">
+      <c r="K21" s="140">
         <f>J21*12</f>
         <v>36</v>
       </c>
-      <c r="L21" s="146">
+      <c r="L21" s="140">
         <f>36*J21</f>
         <v>108</v>
       </c>
-      <c r="M21" s="146">
+      <c r="M21" s="140">
         <f>SUM(K21:L21)</f>
         <v>144</v>
       </c>
-      <c r="N21" s="164" t="s">
+      <c r="N21" s="137" t="s">
         <v>211</v>
       </c>
-      <c r="O21" s="164" t="s">
+      <c r="O21" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P21" s="164" t="s">
+      <c r="P21" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q21" s="164" t="s">
+      <c r="Q21" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R21" s="24"/>
     </row>
-    <row r="22" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="str">
         <f>_xlfn.XLOOKUP(B22,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10866,24 +10870,24 @@
       <c r="B22" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="137"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="165"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="165"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="165"/>
-      <c r="Q22" s="165"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="141"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="141"/>
+      <c r="L22" s="141"/>
+      <c r="M22" s="141"/>
+      <c r="N22" s="138"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="138"/>
+      <c r="Q22" s="138"/>
       <c r="R22" s="24"/>
     </row>
-    <row r="23" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="97" t="str">
         <f>_xlfn.XLOOKUP(B23,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10891,24 +10895,24 @@
       <c r="B23" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="162"/>
-      <c r="D23" s="162"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="162"/>
-      <c r="G23" s="162"/>
-      <c r="H23" s="162"/>
-      <c r="I23" s="162"/>
-      <c r="J23" s="162"/>
-      <c r="K23" s="162"/>
-      <c r="L23" s="162"/>
-      <c r="M23" s="162"/>
-      <c r="N23" s="166"/>
-      <c r="O23" s="166"/>
-      <c r="P23" s="166"/>
-      <c r="Q23" s="166"/>
+      <c r="C23" s="142"/>
+      <c r="D23" s="142"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="142"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="142"/>
+      <c r="N23" s="139"/>
+      <c r="O23" s="139"/>
+      <c r="P23" s="139"/>
+      <c r="Q23" s="139"/>
       <c r="R23" s="24"/>
     </row>
-    <row r="24" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="str">
         <f>_xlfn.XLOOKUP(B24,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10916,53 +10920,53 @@
       <c r="B24" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="146">
+      <c r="C24" s="140">
         <v>2</v>
       </c>
-      <c r="D24" s="146" t="s">
+      <c r="D24" s="140" t="s">
         <v>212</v>
       </c>
-      <c r="E24" s="164" t="s">
+      <c r="E24" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="F24" s="146" t="s">
+      <c r="F24" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G24" s="146"/>
-      <c r="H24" s="146" t="s">
+      <c r="G24" s="140"/>
+      <c r="H24" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I24" s="146"/>
-      <c r="J24" s="146">
+      <c r="I24" s="140"/>
+      <c r="J24" s="140">
         <v>3</v>
       </c>
-      <c r="K24" s="146">
+      <c r="K24" s="140">
         <f>J24*12</f>
         <v>36</v>
       </c>
-      <c r="L24" s="146">
+      <c r="L24" s="140">
         <f>36*J24</f>
         <v>108</v>
       </c>
-      <c r="M24" s="146">
+      <c r="M24" s="140">
         <f>SUM(K24:L24)</f>
         <v>144</v>
       </c>
-      <c r="N24" s="164" t="s">
+      <c r="N24" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="O24" s="164" t="s">
+      <c r="O24" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P24" s="164" t="s">
+      <c r="P24" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q24" s="164" t="s">
+      <c r="Q24" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R24" s="24"/>
     </row>
-    <row r="25" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="str">
         <f>_xlfn.XLOOKUP(B25,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10970,24 +10974,24 @@
       <c r="B25" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="165"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="137"/>
-      <c r="J25" s="137"/>
-      <c r="K25" s="137"/>
-      <c r="L25" s="137"/>
-      <c r="M25" s="137"/>
-      <c r="N25" s="165"/>
-      <c r="O25" s="165"/>
-      <c r="P25" s="165"/>
-      <c r="Q25" s="165"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="141"/>
+      <c r="L25" s="141"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="138"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="138"/>
+      <c r="Q25" s="138"/>
       <c r="R25" s="24"/>
     </row>
-    <row r="26" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="97" t="str">
         <f>_xlfn.XLOOKUP(B26,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10995,24 +10999,24 @@
       <c r="B26" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="162"/>
-      <c r="D26" s="162"/>
-      <c r="E26" s="166"/>
-      <c r="F26" s="162"/>
-      <c r="G26" s="162"/>
-      <c r="H26" s="162"/>
-      <c r="I26" s="162"/>
-      <c r="J26" s="162"/>
-      <c r="K26" s="162"/>
-      <c r="L26" s="162"/>
-      <c r="M26" s="162"/>
-      <c r="N26" s="166"/>
-      <c r="O26" s="166"/>
-      <c r="P26" s="166"/>
-      <c r="Q26" s="166"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="142"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="142"/>
+      <c r="N26" s="139"/>
+      <c r="O26" s="139"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="139"/>
       <c r="R26" s="24"/>
     </row>
-    <row r="27" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="str">
         <f>_xlfn.XLOOKUP(B27,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11020,53 +11024,53 @@
       <c r="B27" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="146">
+      <c r="C27" s="140">
         <v>2</v>
       </c>
-      <c r="D27" s="146" t="s">
+      <c r="D27" s="140" t="s">
         <v>215</v>
       </c>
-      <c r="E27" s="164" t="s">
+      <c r="E27" s="137" t="s">
         <v>216</v>
       </c>
-      <c r="F27" s="146" t="s">
+      <c r="F27" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="146"/>
-      <c r="H27" s="146" t="s">
+      <c r="G27" s="140"/>
+      <c r="H27" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I27" s="146"/>
-      <c r="J27" s="146">
+      <c r="I27" s="140"/>
+      <c r="J27" s="140">
         <v>3</v>
       </c>
-      <c r="K27" s="146">
+      <c r="K27" s="140">
         <f>J27*12</f>
         <v>36</v>
       </c>
-      <c r="L27" s="146">
+      <c r="L27" s="140">
         <f>36*J27</f>
         <v>108</v>
       </c>
-      <c r="M27" s="146">
+      <c r="M27" s="140">
         <f>SUM(K27:L27)</f>
         <v>144</v>
       </c>
-      <c r="N27" s="164" t="s">
+      <c r="N27" s="137" t="s">
         <v>217</v>
       </c>
-      <c r="O27" s="164" t="s">
+      <c r="O27" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P27" s="164" t="s">
+      <c r="P27" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q27" s="164" t="s">
+      <c r="Q27" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R27" s="24"/>
     </row>
-    <row r="28" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="str">
         <f>_xlfn.XLOOKUP(B28,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11074,24 +11078,24 @@
       <c r="B28" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="137"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="165"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="137"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="137"/>
-      <c r="K28" s="137"/>
-      <c r="L28" s="137"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="165"/>
-      <c r="O28" s="165"/>
-      <c r="P28" s="165"/>
-      <c r="Q28" s="165"/>
+      <c r="C28" s="141"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="138"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="138"/>
+      <c r="Q28" s="138"/>
       <c r="R28" s="24"/>
     </row>
-    <row r="29" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="97" t="str">
         <f>_xlfn.XLOOKUP(B29,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11099,24 +11103,24 @@
       <c r="B29" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="162"/>
-      <c r="D29" s="162"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="162"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="162"/>
-      <c r="I29" s="162"/>
-      <c r="J29" s="162"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="162"/>
-      <c r="M29" s="162"/>
-      <c r="N29" s="166"/>
-      <c r="O29" s="166"/>
-      <c r="P29" s="166"/>
-      <c r="Q29" s="166"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="142"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="142"/>
+      <c r="N29" s="139"/>
+      <c r="O29" s="139"/>
+      <c r="P29" s="139"/>
+      <c r="Q29" s="139"/>
       <c r="R29" s="24"/>
     </row>
-    <row r="30" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="str">
         <f>_xlfn.XLOOKUP(B30,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11124,53 +11128,53 @@
       <c r="B30" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="146">
+      <c r="C30" s="140">
         <v>2</v>
       </c>
-      <c r="D30" s="146" t="s">
+      <c r="D30" s="140" t="s">
         <v>218</v>
       </c>
-      <c r="E30" s="168" t="s">
+      <c r="E30" s="144" t="s">
         <v>219</v>
       </c>
-      <c r="F30" s="146" t="s">
+      <c r="F30" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="146"/>
-      <c r="H30" s="146" t="s">
+      <c r="G30" s="140"/>
+      <c r="H30" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I30" s="146"/>
-      <c r="J30" s="146">
+      <c r="I30" s="140"/>
+      <c r="J30" s="140">
         <v>2</v>
       </c>
-      <c r="K30" s="146">
+      <c r="K30" s="140">
         <f>J30*12</f>
         <v>24</v>
       </c>
-      <c r="L30" s="146">
+      <c r="L30" s="140">
         <f>36*J30</f>
         <v>72</v>
       </c>
-      <c r="M30" s="146">
+      <c r="M30" s="140">
         <f>SUM(K30:L30)</f>
         <v>96</v>
       </c>
-      <c r="N30" s="164" t="s">
+      <c r="N30" s="137" t="s">
         <v>220</v>
       </c>
-      <c r="O30" s="164" t="s">
+      <c r="O30" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P30" s="164" t="s">
+      <c r="P30" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q30" s="164" t="s">
+      <c r="Q30" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R30" s="24"/>
     </row>
-    <row r="31" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="str">
         <f>_xlfn.XLOOKUP(B31,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11178,24 +11182,24 @@
       <c r="B31" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="137"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="159"/>
-      <c r="F31" s="137"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="137"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="137"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="165"/>
-      <c r="O31" s="165"/>
-      <c r="P31" s="165"/>
-      <c r="Q31" s="165"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="141"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="141"/>
+      <c r="M31" s="141"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="138"/>
+      <c r="P31" s="138"/>
+      <c r="Q31" s="138"/>
       <c r="R31" s="24"/>
     </row>
-    <row r="32" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="97" t="str">
         <f>_xlfn.XLOOKUP(B32,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11203,21 +11207,21 @@
       <c r="B32" s="98" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="162"/>
-      <c r="D32" s="162"/>
-      <c r="E32" s="160"/>
-      <c r="F32" s="162"/>
-      <c r="G32" s="162"/>
-      <c r="H32" s="162"/>
-      <c r="I32" s="162"/>
-      <c r="J32" s="162"/>
-      <c r="K32" s="162"/>
-      <c r="L32" s="162"/>
-      <c r="M32" s="162"/>
-      <c r="N32" s="166"/>
-      <c r="O32" s="166"/>
-      <c r="P32" s="166"/>
-      <c r="Q32" s="166"/>
+      <c r="C32" s="142"/>
+      <c r="D32" s="142"/>
+      <c r="E32" s="147"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="142"/>
+      <c r="I32" s="142"/>
+      <c r="J32" s="142"/>
+      <c r="K32" s="142"/>
+      <c r="L32" s="142"/>
+      <c r="M32" s="142"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="139"/>
+      <c r="P32" s="139"/>
+      <c r="Q32" s="139"/>
       <c r="R32" s="24">
         <f>SUM(J17:J32)</f>
         <v>17</v>
@@ -11227,7 +11231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="50" customFormat="1" ht="363.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:19" s="50" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="106" t="str">
         <f>_xlfn.XLOOKUP(B33,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11281,7 +11285,7 @@
       </c>
       <c r="R33" s="24"/>
     </row>
-    <row r="34" spans="1:19" s="12" customFormat="1" ht="297.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:19" s="12" customFormat="1" ht="342.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="106" t="str">
         <f>_xlfn.XLOOKUP(B34,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11335,7 +11339,7 @@
       </c>
       <c r="R34" s="24"/>
     </row>
-    <row r="35" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="str">
         <f>_xlfn.XLOOKUP(B35,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11343,53 +11347,53 @@
       <c r="B35" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="146">
+      <c r="C35" s="140">
         <v>3</v>
       </c>
-      <c r="D35" s="146" t="s">
+      <c r="D35" s="140" t="s">
         <v>229</v>
       </c>
-      <c r="E35" s="164" t="s">
+      <c r="E35" s="137" t="s">
         <v>230</v>
       </c>
-      <c r="F35" s="146" t="s">
+      <c r="F35" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G35" s="146"/>
-      <c r="H35" s="146" t="s">
+      <c r="G35" s="140"/>
+      <c r="H35" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I35" s="146"/>
-      <c r="J35" s="146">
+      <c r="I35" s="140"/>
+      <c r="J35" s="140">
         <v>3</v>
       </c>
-      <c r="K35" s="146">
+      <c r="K35" s="140">
         <f>J35*12</f>
         <v>36</v>
       </c>
-      <c r="L35" s="146">
+      <c r="L35" s="140">
         <f>36*J35</f>
         <v>108</v>
       </c>
-      <c r="M35" s="146">
+      <c r="M35" s="140">
         <f>SUM(K35:L35)</f>
         <v>144</v>
       </c>
-      <c r="N35" s="164" t="s">
+      <c r="N35" s="137" t="s">
         <v>231</v>
       </c>
-      <c r="O35" s="164" t="s">
+      <c r="O35" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P35" s="164" t="s">
+      <c r="P35" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q35" s="164" t="s">
+      <c r="Q35" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R35" s="24"/>
     </row>
-    <row r="36" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A36" s="24" t="str">
         <f>_xlfn.XLOOKUP(B36,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11397,24 +11401,24 @@
       <c r="B36" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="137"/>
-      <c r="D36" s="137"/>
-      <c r="E36" s="165"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="137"/>
-      <c r="H36" s="137"/>
-      <c r="I36" s="137"/>
-      <c r="J36" s="137"/>
-      <c r="K36" s="137"/>
-      <c r="L36" s="137"/>
-      <c r="M36" s="137"/>
-      <c r="N36" s="165"/>
-      <c r="O36" s="165"/>
-      <c r="P36" s="165"/>
-      <c r="Q36" s="165"/>
+      <c r="C36" s="141"/>
+      <c r="D36" s="141"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="141"/>
+      <c r="G36" s="141"/>
+      <c r="H36" s="141"/>
+      <c r="I36" s="141"/>
+      <c r="J36" s="141"/>
+      <c r="K36" s="141"/>
+      <c r="L36" s="141"/>
+      <c r="M36" s="141"/>
+      <c r="N36" s="138"/>
+      <c r="O36" s="138"/>
+      <c r="P36" s="138"/>
+      <c r="Q36" s="138"/>
       <c r="R36" s="24"/>
     </row>
-    <row r="37" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="97" t="str">
         <f>_xlfn.XLOOKUP(B37,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11422,24 +11426,24 @@
       <c r="B37" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="162"/>
-      <c r="D37" s="162"/>
-      <c r="E37" s="166"/>
-      <c r="F37" s="162"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="162"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="162"/>
-      <c r="K37" s="162"/>
-      <c r="L37" s="162"/>
-      <c r="M37" s="162"/>
-      <c r="N37" s="166"/>
-      <c r="O37" s="166"/>
-      <c r="P37" s="166"/>
-      <c r="Q37" s="166"/>
+      <c r="C37" s="142"/>
+      <c r="D37" s="142"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="142"/>
+      <c r="H37" s="142"/>
+      <c r="I37" s="142"/>
+      <c r="J37" s="142"/>
+      <c r="K37" s="142"/>
+      <c r="L37" s="142"/>
+      <c r="M37" s="142"/>
+      <c r="N37" s="139"/>
+      <c r="O37" s="139"/>
+      <c r="P37" s="139"/>
+      <c r="Q37" s="139"/>
       <c r="R37" s="24"/>
     </row>
-    <row r="38" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="str">
         <f>_xlfn.XLOOKUP(B38,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11447,53 +11451,53 @@
       <c r="B38" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="146">
+      <c r="C38" s="140">
         <v>3</v>
       </c>
-      <c r="D38" s="146" t="s">
+      <c r="D38" s="140" t="s">
         <v>232</v>
       </c>
-      <c r="E38" s="164" t="s">
+      <c r="E38" s="137" t="s">
         <v>233</v>
       </c>
-      <c r="F38" s="146" t="s">
+      <c r="F38" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G38" s="146"/>
-      <c r="H38" s="146" t="s">
+      <c r="G38" s="140"/>
+      <c r="H38" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I38" s="146"/>
-      <c r="J38" s="146">
+      <c r="I38" s="140"/>
+      <c r="J38" s="140">
         <v>3</v>
       </c>
-      <c r="K38" s="146">
+      <c r="K38" s="140">
         <f>J38*12</f>
         <v>36</v>
       </c>
-      <c r="L38" s="146">
+      <c r="L38" s="140">
         <f>36*J38</f>
         <v>108</v>
       </c>
-      <c r="M38" s="146">
+      <c r="M38" s="140">
         <f>SUM(K38:L38)</f>
         <v>144</v>
       </c>
-      <c r="N38" s="164" t="s">
+      <c r="N38" s="137" t="s">
         <v>234</v>
       </c>
-      <c r="O38" s="164" t="s">
+      <c r="O38" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P38" s="164" t="s">
+      <c r="P38" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q38" s="164" t="s">
+      <c r="Q38" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R38" s="24"/>
     </row>
-    <row r="39" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="str">
         <f>_xlfn.XLOOKUP(B39,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11501,24 +11505,24 @@
       <c r="B39" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="137"/>
-      <c r="D39" s="137"/>
-      <c r="E39" s="165"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="137"/>
-      <c r="I39" s="137"/>
-      <c r="J39" s="137"/>
-      <c r="K39" s="137"/>
-      <c r="L39" s="137"/>
-      <c r="M39" s="137"/>
-      <c r="N39" s="165"/>
-      <c r="O39" s="165"/>
-      <c r="P39" s="165"/>
-      <c r="Q39" s="165"/>
+      <c r="C39" s="141"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="138"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="141"/>
+      <c r="I39" s="141"/>
+      <c r="J39" s="141"/>
+      <c r="K39" s="141"/>
+      <c r="L39" s="141"/>
+      <c r="M39" s="141"/>
+      <c r="N39" s="138"/>
+      <c r="O39" s="138"/>
+      <c r="P39" s="138"/>
+      <c r="Q39" s="138"/>
       <c r="R39" s="24"/>
     </row>
-    <row r="40" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="97" t="str">
         <f>_xlfn.XLOOKUP(B40,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11526,24 +11530,24 @@
       <c r="B40" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="162"/>
-      <c r="D40" s="162"/>
-      <c r="E40" s="166"/>
-      <c r="F40" s="162"/>
-      <c r="G40" s="162"/>
-      <c r="H40" s="162"/>
-      <c r="I40" s="162"/>
-      <c r="J40" s="162"/>
-      <c r="K40" s="162"/>
-      <c r="L40" s="162"/>
-      <c r="M40" s="162"/>
-      <c r="N40" s="166"/>
-      <c r="O40" s="166"/>
-      <c r="P40" s="166"/>
-      <c r="Q40" s="166"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="142"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="142"/>
+      <c r="I40" s="142"/>
+      <c r="J40" s="142"/>
+      <c r="K40" s="142"/>
+      <c r="L40" s="142"/>
+      <c r="M40" s="142"/>
+      <c r="N40" s="139"/>
+      <c r="O40" s="139"/>
+      <c r="P40" s="139"/>
+      <c r="Q40" s="139"/>
       <c r="R40" s="24"/>
     </row>
-    <row r="41" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="str">
         <f>_xlfn.XLOOKUP(B41,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11551,53 +11555,53 @@
       <c r="B41" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="146">
+      <c r="C41" s="140">
         <v>3</v>
       </c>
-      <c r="D41" s="146" t="s">
+      <c r="D41" s="140" t="s">
         <v>235</v>
       </c>
-      <c r="E41" s="164" t="s">
+      <c r="E41" s="137" t="s">
         <v>236</v>
       </c>
-      <c r="F41" s="146" t="s">
+      <c r="F41" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G41" s="146"/>
-      <c r="H41" s="146" t="s">
+      <c r="G41" s="140"/>
+      <c r="H41" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146">
+      <c r="I41" s="140"/>
+      <c r="J41" s="140">
         <v>3</v>
       </c>
-      <c r="K41" s="146">
+      <c r="K41" s="140">
         <f>J41*12</f>
         <v>36</v>
       </c>
-      <c r="L41" s="146">
+      <c r="L41" s="140">
         <f>36*J41</f>
         <v>108</v>
       </c>
-      <c r="M41" s="146">
+      <c r="M41" s="140">
         <f>SUM(K41:L41)</f>
         <v>144</v>
       </c>
-      <c r="N41" s="164" t="s">
+      <c r="N41" s="137" t="s">
         <v>237</v>
       </c>
-      <c r="O41" s="164" t="s">
+      <c r="O41" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P41" s="164" t="s">
+      <c r="P41" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q41" s="164" t="s">
+      <c r="Q41" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R41" s="24"/>
     </row>
-    <row r="42" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="str">
         <f>_xlfn.XLOOKUP(B42,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11605,24 +11609,24 @@
       <c r="B42" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="165"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="137"/>
-      <c r="I42" s="137"/>
-      <c r="J42" s="137"/>
-      <c r="K42" s="137"/>
-      <c r="L42" s="137"/>
-      <c r="M42" s="137"/>
-      <c r="N42" s="165"/>
-      <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
-      <c r="Q42" s="165"/>
+      <c r="C42" s="141"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="138"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="141"/>
+      <c r="I42" s="141"/>
+      <c r="J42" s="141"/>
+      <c r="K42" s="141"/>
+      <c r="L42" s="141"/>
+      <c r="M42" s="141"/>
+      <c r="N42" s="138"/>
+      <c r="O42" s="138"/>
+      <c r="P42" s="138"/>
+      <c r="Q42" s="138"/>
       <c r="R42" s="24"/>
     </row>
-    <row r="43" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="97" t="str">
         <f>_xlfn.XLOOKUP(B43,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11630,24 +11634,24 @@
       <c r="B43" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="162"/>
-      <c r="D43" s="162"/>
-      <c r="E43" s="166"/>
-      <c r="F43" s="162"/>
-      <c r="G43" s="162"/>
-      <c r="H43" s="162"/>
-      <c r="I43" s="162"/>
-      <c r="J43" s="162"/>
-      <c r="K43" s="162"/>
-      <c r="L43" s="162"/>
-      <c r="M43" s="162"/>
-      <c r="N43" s="166"/>
-      <c r="O43" s="166"/>
-      <c r="P43" s="166"/>
-      <c r="Q43" s="166"/>
+      <c r="C43" s="142"/>
+      <c r="D43" s="142"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="142"/>
+      <c r="G43" s="142"/>
+      <c r="H43" s="142"/>
+      <c r="I43" s="142"/>
+      <c r="J43" s="142"/>
+      <c r="K43" s="142"/>
+      <c r="L43" s="142"/>
+      <c r="M43" s="142"/>
+      <c r="N43" s="139"/>
+      <c r="O43" s="139"/>
+      <c r="P43" s="139"/>
+      <c r="Q43" s="139"/>
       <c r="R43" s="24"/>
     </row>
-    <row r="44" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="str">
         <f>_xlfn.XLOOKUP(B44,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11655,53 +11659,53 @@
       <c r="B44" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="146">
+      <c r="C44" s="140">
         <v>3</v>
       </c>
-      <c r="D44" s="146" t="s">
+      <c r="D44" s="140" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="164" t="s">
+      <c r="E44" s="137" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="146" t="s">
+      <c r="F44" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G44" s="146"/>
-      <c r="H44" s="146" t="s">
+      <c r="G44" s="140"/>
+      <c r="H44" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I44" s="146"/>
-      <c r="J44" s="146">
+      <c r="I44" s="140"/>
+      <c r="J44" s="140">
         <v>3</v>
       </c>
-      <c r="K44" s="146">
+      <c r="K44" s="140">
         <f>J44*12</f>
         <v>36</v>
       </c>
-      <c r="L44" s="146">
+      <c r="L44" s="140">
         <f>36*J44</f>
         <v>108</v>
       </c>
-      <c r="M44" s="146">
+      <c r="M44" s="140">
         <f>SUM(K44:L44)</f>
         <v>144</v>
       </c>
-      <c r="N44" s="164" t="s">
+      <c r="N44" s="137" t="s">
         <v>240</v>
       </c>
-      <c r="O44" s="164" t="s">
+      <c r="O44" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P44" s="164" t="s">
+      <c r="P44" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q44" s="164" t="s">
+      <c r="Q44" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R44" s="24"/>
     </row>
-    <row r="45" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="str">
         <f>_xlfn.XLOOKUP(B45,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11709,24 +11713,24 @@
       <c r="B45" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="137"/>
-      <c r="D45" s="137"/>
-      <c r="E45" s="165"/>
-      <c r="F45" s="137"/>
-      <c r="G45" s="137"/>
-      <c r="H45" s="137"/>
-      <c r="I45" s="137"/>
-      <c r="J45" s="137"/>
-      <c r="K45" s="137"/>
-      <c r="L45" s="137"/>
-      <c r="M45" s="137"/>
-      <c r="N45" s="165"/>
-      <c r="O45" s="165"/>
-      <c r="P45" s="165"/>
-      <c r="Q45" s="165"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="141"/>
+      <c r="E45" s="138"/>
+      <c r="F45" s="141"/>
+      <c r="G45" s="141"/>
+      <c r="H45" s="141"/>
+      <c r="I45" s="141"/>
+      <c r="J45" s="141"/>
+      <c r="K45" s="141"/>
+      <c r="L45" s="141"/>
+      <c r="M45" s="141"/>
+      <c r="N45" s="138"/>
+      <c r="O45" s="138"/>
+      <c r="P45" s="138"/>
+      <c r="Q45" s="138"/>
       <c r="R45" s="24"/>
     </row>
-    <row r="46" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="97" t="str">
         <f>_xlfn.XLOOKUP(B46,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11734,21 +11738,21 @@
       <c r="B46" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="162"/>
-      <c r="D46" s="162"/>
-      <c r="E46" s="166"/>
-      <c r="F46" s="162"/>
-      <c r="G46" s="162"/>
-      <c r="H46" s="162"/>
-      <c r="I46" s="162"/>
-      <c r="J46" s="162"/>
-      <c r="K46" s="162"/>
-      <c r="L46" s="162"/>
-      <c r="M46" s="162"/>
-      <c r="N46" s="166"/>
-      <c r="O46" s="166"/>
-      <c r="P46" s="166"/>
-      <c r="Q46" s="166"/>
+      <c r="C46" s="142"/>
+      <c r="D46" s="142"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="142"/>
+      <c r="G46" s="142"/>
+      <c r="H46" s="142"/>
+      <c r="I46" s="142"/>
+      <c r="J46" s="142"/>
+      <c r="K46" s="142"/>
+      <c r="L46" s="142"/>
+      <c r="M46" s="142"/>
+      <c r="N46" s="139"/>
+      <c r="O46" s="139"/>
+      <c r="P46" s="139"/>
+      <c r="Q46" s="139"/>
       <c r="R46" s="24">
         <f>SUM(J33:J46)</f>
         <v>18</v>
@@ -11758,7 +11762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:19" s="50" customFormat="1" ht="347" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:19" s="50" customFormat="1" ht="396.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="106" t="str">
         <f>_xlfn.XLOOKUP(B47,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11812,7 +11816,7 @@
       </c>
       <c r="R47" s="24"/>
     </row>
-    <row r="48" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A48" s="24" t="str">
         <f>_xlfn.XLOOKUP(B48,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11820,53 +11824,53 @@
       <c r="B48" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="146">
+      <c r="C48" s="140">
         <v>4</v>
       </c>
-      <c r="D48" s="146" t="s">
+      <c r="D48" s="140" t="s">
         <v>245</v>
       </c>
-      <c r="E48" s="164" t="s">
+      <c r="E48" s="137" t="s">
         <v>246</v>
       </c>
-      <c r="F48" s="146" t="s">
+      <c r="F48" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G48" s="146"/>
-      <c r="H48" s="146" t="s">
+      <c r="G48" s="140"/>
+      <c r="H48" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I48" s="146"/>
-      <c r="J48" s="146">
+      <c r="I48" s="140"/>
+      <c r="J48" s="140">
         <v>3</v>
       </c>
-      <c r="K48" s="146">
+      <c r="K48" s="140">
         <f>J48*12</f>
         <v>36</v>
       </c>
-      <c r="L48" s="146">
+      <c r="L48" s="140">
         <f>36*J48</f>
         <v>108</v>
       </c>
-      <c r="M48" s="146">
+      <c r="M48" s="140">
         <f>SUM(K48:L48)</f>
         <v>144</v>
       </c>
-      <c r="N48" s="164" t="s">
+      <c r="N48" s="137" t="s">
         <v>247</v>
       </c>
-      <c r="O48" s="164" t="s">
+      <c r="O48" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P48" s="164" t="s">
+      <c r="P48" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q48" s="164" t="s">
+      <c r="Q48" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R48" s="24"/>
     </row>
-    <row r="49" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="str">
         <f>_xlfn.XLOOKUP(B49,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11874,24 +11878,24 @@
       <c r="B49" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="165"/>
-      <c r="F49" s="137"/>
-      <c r="G49" s="137"/>
-      <c r="H49" s="137"/>
-      <c r="I49" s="137"/>
-      <c r="J49" s="137"/>
-      <c r="K49" s="137"/>
-      <c r="L49" s="137"/>
-      <c r="M49" s="137"/>
-      <c r="N49" s="165"/>
-      <c r="O49" s="165"/>
-      <c r="P49" s="165"/>
-      <c r="Q49" s="165"/>
+      <c r="C49" s="141"/>
+      <c r="D49" s="141"/>
+      <c r="E49" s="138"/>
+      <c r="F49" s="141"/>
+      <c r="G49" s="141"/>
+      <c r="H49" s="141"/>
+      <c r="I49" s="141"/>
+      <c r="J49" s="141"/>
+      <c r="K49" s="141"/>
+      <c r="L49" s="141"/>
+      <c r="M49" s="141"/>
+      <c r="N49" s="138"/>
+      <c r="O49" s="138"/>
+      <c r="P49" s="138"/>
+      <c r="Q49" s="138"/>
       <c r="R49" s="24"/>
     </row>
-    <row r="50" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="97" t="str">
         <f>_xlfn.XLOOKUP(B50,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11899,24 +11903,24 @@
       <c r="B50" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="162"/>
-      <c r="D50" s="162"/>
-      <c r="E50" s="166"/>
-      <c r="F50" s="162"/>
-      <c r="G50" s="162"/>
-      <c r="H50" s="162"/>
-      <c r="I50" s="162"/>
-      <c r="J50" s="162"/>
-      <c r="K50" s="162"/>
-      <c r="L50" s="162"/>
-      <c r="M50" s="162"/>
-      <c r="N50" s="166"/>
-      <c r="O50" s="166"/>
-      <c r="P50" s="166"/>
-      <c r="Q50" s="166"/>
+      <c r="C50" s="142"/>
+      <c r="D50" s="142"/>
+      <c r="E50" s="139"/>
+      <c r="F50" s="142"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="142"/>
+      <c r="I50" s="142"/>
+      <c r="J50" s="142"/>
+      <c r="K50" s="142"/>
+      <c r="L50" s="142"/>
+      <c r="M50" s="142"/>
+      <c r="N50" s="139"/>
+      <c r="O50" s="139"/>
+      <c r="P50" s="139"/>
+      <c r="Q50" s="139"/>
       <c r="R50" s="24"/>
     </row>
-    <row r="51" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="str">
         <f>_xlfn.XLOOKUP(B51,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11924,53 +11928,53 @@
       <c r="B51" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C51" s="146">
+      <c r="C51" s="140">
         <v>4</v>
       </c>
-      <c r="D51" s="146" t="s">
+      <c r="D51" s="140" t="s">
         <v>248</v>
       </c>
-      <c r="E51" s="169" t="s">
+      <c r="E51" s="149" t="s">
         <v>249</v>
       </c>
-      <c r="F51" s="146" t="s">
+      <c r="F51" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G51" s="146"/>
-      <c r="H51" s="146" t="s">
+      <c r="G51" s="140"/>
+      <c r="H51" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I51" s="146"/>
-      <c r="J51" s="146">
+      <c r="I51" s="140"/>
+      <c r="J51" s="140">
         <v>3</v>
       </c>
-      <c r="K51" s="146">
+      <c r="K51" s="140">
         <f>J51*12</f>
         <v>36</v>
       </c>
-      <c r="L51" s="146">
+      <c r="L51" s="140">
         <f>36*J51</f>
         <v>108</v>
       </c>
-      <c r="M51" s="146">
+      <c r="M51" s="140">
         <f>SUM(K51:L51)</f>
         <v>144</v>
       </c>
-      <c r="N51" s="164" t="s">
+      <c r="N51" s="137" t="s">
         <v>250</v>
       </c>
-      <c r="O51" s="164" t="s">
+      <c r="O51" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P51" s="164" t="s">
+      <c r="P51" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q51" s="164" t="s">
+      <c r="Q51" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R51" s="24"/>
     </row>
-    <row r="52" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A52" s="24" t="str">
         <f>_xlfn.XLOOKUP(B52,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11978,24 +11982,24 @@
       <c r="B52" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C52" s="137"/>
-      <c r="D52" s="137"/>
-      <c r="E52" s="170"/>
-      <c r="F52" s="137"/>
-      <c r="G52" s="137"/>
-      <c r="H52" s="137"/>
-      <c r="I52" s="137"/>
-      <c r="J52" s="137"/>
-      <c r="K52" s="137"/>
-      <c r="L52" s="137"/>
-      <c r="M52" s="137"/>
-      <c r="N52" s="165"/>
-      <c r="O52" s="165"/>
-      <c r="P52" s="165"/>
-      <c r="Q52" s="165"/>
+      <c r="C52" s="141"/>
+      <c r="D52" s="141"/>
+      <c r="E52" s="150"/>
+      <c r="F52" s="141"/>
+      <c r="G52" s="141"/>
+      <c r="H52" s="141"/>
+      <c r="I52" s="141"/>
+      <c r="J52" s="141"/>
+      <c r="K52" s="141"/>
+      <c r="L52" s="141"/>
+      <c r="M52" s="141"/>
+      <c r="N52" s="138"/>
+      <c r="O52" s="138"/>
+      <c r="P52" s="138"/>
+      <c r="Q52" s="138"/>
       <c r="R52" s="24"/>
     </row>
-    <row r="53" spans="1:19" s="50" customFormat="1" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:19" s="50" customFormat="1" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="97" t="str">
         <f>_xlfn.XLOOKUP(B53,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12003,24 +12007,24 @@
       <c r="B53" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="162"/>
-      <c r="D53" s="162"/>
-      <c r="E53" s="171"/>
-      <c r="F53" s="162"/>
-      <c r="G53" s="162"/>
-      <c r="H53" s="162"/>
-      <c r="I53" s="162"/>
-      <c r="J53" s="162"/>
-      <c r="K53" s="162"/>
-      <c r="L53" s="162"/>
-      <c r="M53" s="162"/>
-      <c r="N53" s="166"/>
-      <c r="O53" s="166"/>
-      <c r="P53" s="166"/>
-      <c r="Q53" s="166"/>
+      <c r="C53" s="142"/>
+      <c r="D53" s="142"/>
+      <c r="E53" s="151"/>
+      <c r="F53" s="142"/>
+      <c r="G53" s="142"/>
+      <c r="H53" s="142"/>
+      <c r="I53" s="142"/>
+      <c r="J53" s="142"/>
+      <c r="K53" s="142"/>
+      <c r="L53" s="142"/>
+      <c r="M53" s="142"/>
+      <c r="N53" s="139"/>
+      <c r="O53" s="139"/>
+      <c r="P53" s="139"/>
+      <c r="Q53" s="139"/>
       <c r="R53" s="24"/>
     </row>
-    <row r="54" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="str">
         <f>_xlfn.XLOOKUP(B54,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12028,53 +12032,53 @@
       <c r="B54" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C54" s="146">
+      <c r="C54" s="140">
         <v>4</v>
       </c>
-      <c r="D54" s="146" t="s">
+      <c r="D54" s="140" t="s">
         <v>251</v>
       </c>
-      <c r="E54" s="164" t="s">
+      <c r="E54" s="137" t="s">
         <v>252</v>
       </c>
-      <c r="F54" s="146" t="s">
+      <c r="F54" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G54" s="146"/>
-      <c r="H54" s="146" t="s">
+      <c r="G54" s="140"/>
+      <c r="H54" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I54" s="146"/>
-      <c r="J54" s="146">
+      <c r="I54" s="140"/>
+      <c r="J54" s="140">
         <v>3</v>
       </c>
-      <c r="K54" s="146">
+      <c r="K54" s="140">
         <f>J54*12</f>
         <v>36</v>
       </c>
-      <c r="L54" s="146">
+      <c r="L54" s="140">
         <f>36*J54</f>
         <v>108</v>
       </c>
-      <c r="M54" s="146">
+      <c r="M54" s="140">
         <f>SUM(K54:L54)</f>
         <v>144</v>
       </c>
-      <c r="N54" s="164" t="s">
+      <c r="N54" s="137" t="s">
         <v>253</v>
       </c>
-      <c r="O54" s="164" t="s">
+      <c r="O54" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P54" s="164" t="s">
+      <c r="P54" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q54" s="164" t="s">
+      <c r="Q54" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R54" s="24"/>
     </row>
-    <row r="55" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A55" s="24" t="str">
         <f>_xlfn.XLOOKUP(B55,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12082,24 +12086,24 @@
       <c r="B55" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C55" s="137"/>
-      <c r="D55" s="137"/>
-      <c r="E55" s="165"/>
-      <c r="F55" s="137"/>
-      <c r="G55" s="137"/>
-      <c r="H55" s="137"/>
-      <c r="I55" s="137"/>
-      <c r="J55" s="137"/>
-      <c r="K55" s="137"/>
-      <c r="L55" s="137"/>
-      <c r="M55" s="137"/>
-      <c r="N55" s="165"/>
-      <c r="O55" s="165"/>
-      <c r="P55" s="165"/>
-      <c r="Q55" s="165"/>
+      <c r="C55" s="141"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="138"/>
+      <c r="F55" s="141"/>
+      <c r="G55" s="141"/>
+      <c r="H55" s="141"/>
+      <c r="I55" s="141"/>
+      <c r="J55" s="141"/>
+      <c r="K55" s="141"/>
+      <c r="L55" s="141"/>
+      <c r="M55" s="141"/>
+      <c r="N55" s="138"/>
+      <c r="O55" s="138"/>
+      <c r="P55" s="138"/>
+      <c r="Q55" s="138"/>
       <c r="R55" s="24"/>
     </row>
-    <row r="56" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="97" t="str">
         <f>_xlfn.XLOOKUP(B56,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12107,24 +12111,24 @@
       <c r="B56" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="162"/>
-      <c r="D56" s="162"/>
-      <c r="E56" s="166"/>
-      <c r="F56" s="162"/>
-      <c r="G56" s="162"/>
-      <c r="H56" s="162"/>
-      <c r="I56" s="162"/>
-      <c r="J56" s="162"/>
-      <c r="K56" s="162"/>
-      <c r="L56" s="162"/>
-      <c r="M56" s="162"/>
-      <c r="N56" s="166"/>
-      <c r="O56" s="166"/>
-      <c r="P56" s="166"/>
-      <c r="Q56" s="166"/>
+      <c r="C56" s="142"/>
+      <c r="D56" s="142"/>
+      <c r="E56" s="139"/>
+      <c r="F56" s="142"/>
+      <c r="G56" s="142"/>
+      <c r="H56" s="142"/>
+      <c r="I56" s="142"/>
+      <c r="J56" s="142"/>
+      <c r="K56" s="142"/>
+      <c r="L56" s="142"/>
+      <c r="M56" s="142"/>
+      <c r="N56" s="139"/>
+      <c r="O56" s="139"/>
+      <c r="P56" s="139"/>
+      <c r="Q56" s="139"/>
       <c r="R56" s="24"/>
     </row>
-    <row r="57" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="str">
         <f>_xlfn.XLOOKUP(B57,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12132,53 +12136,53 @@
       <c r="B57" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="146">
+      <c r="C57" s="140">
         <v>4</v>
       </c>
-      <c r="D57" s="146" t="s">
+      <c r="D57" s="140" t="s">
         <v>254</v>
       </c>
-      <c r="E57" s="164" t="s">
+      <c r="E57" s="137" t="s">
         <v>255</v>
       </c>
-      <c r="F57" s="146" t="s">
+      <c r="F57" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G57" s="146"/>
-      <c r="H57" s="146" t="s">
+      <c r="G57" s="140"/>
+      <c r="H57" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I57" s="146"/>
-      <c r="J57" s="146">
+      <c r="I57" s="140"/>
+      <c r="J57" s="140">
         <v>3</v>
       </c>
-      <c r="K57" s="146">
+      <c r="K57" s="140">
         <f>J57*12</f>
         <v>36</v>
       </c>
-      <c r="L57" s="146">
+      <c r="L57" s="140">
         <f>36*J57</f>
         <v>108</v>
       </c>
-      <c r="M57" s="146">
+      <c r="M57" s="140">
         <f>SUM(K57:L57)</f>
         <v>144</v>
       </c>
-      <c r="N57" s="164" t="s">
+      <c r="N57" s="137" t="s">
         <v>256</v>
       </c>
-      <c r="O57" s="164" t="s">
+      <c r="O57" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P57" s="164" t="s">
+      <c r="P57" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q57" s="164" t="s">
+      <c r="Q57" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R57" s="24"/>
     </row>
-    <row r="58" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="str">
         <f>_xlfn.XLOOKUP(B58,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12186,24 +12190,24 @@
       <c r="B58" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="137"/>
-      <c r="D58" s="137"/>
-      <c r="E58" s="165"/>
-      <c r="F58" s="137"/>
-      <c r="G58" s="137"/>
-      <c r="H58" s="137"/>
-      <c r="I58" s="137"/>
-      <c r="J58" s="137"/>
-      <c r="K58" s="137"/>
-      <c r="L58" s="137"/>
-      <c r="M58" s="137"/>
-      <c r="N58" s="165"/>
-      <c r="O58" s="165"/>
-      <c r="P58" s="165"/>
-      <c r="Q58" s="165"/>
+      <c r="C58" s="141"/>
+      <c r="D58" s="141"/>
+      <c r="E58" s="138"/>
+      <c r="F58" s="141"/>
+      <c r="G58" s="141"/>
+      <c r="H58" s="141"/>
+      <c r="I58" s="141"/>
+      <c r="J58" s="141"/>
+      <c r="K58" s="141"/>
+      <c r="L58" s="141"/>
+      <c r="M58" s="141"/>
+      <c r="N58" s="138"/>
+      <c r="O58" s="138"/>
+      <c r="P58" s="138"/>
+      <c r="Q58" s="138"/>
       <c r="R58" s="24"/>
     </row>
-    <row r="59" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="97" t="str">
         <f>_xlfn.XLOOKUP(B59,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12211,24 +12215,24 @@
       <c r="B59" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="162"/>
-      <c r="D59" s="162"/>
-      <c r="E59" s="166"/>
-      <c r="F59" s="162"/>
-      <c r="G59" s="162"/>
-      <c r="H59" s="162"/>
-      <c r="I59" s="162"/>
-      <c r="J59" s="162"/>
-      <c r="K59" s="162"/>
-      <c r="L59" s="162"/>
-      <c r="M59" s="162"/>
-      <c r="N59" s="166"/>
-      <c r="O59" s="166"/>
-      <c r="P59" s="166"/>
-      <c r="Q59" s="166"/>
+      <c r="C59" s="142"/>
+      <c r="D59" s="142"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="142"/>
+      <c r="G59" s="142"/>
+      <c r="H59" s="142"/>
+      <c r="I59" s="142"/>
+      <c r="J59" s="142"/>
+      <c r="K59" s="142"/>
+      <c r="L59" s="142"/>
+      <c r="M59" s="142"/>
+      <c r="N59" s="139"/>
+      <c r="O59" s="139"/>
+      <c r="P59" s="139"/>
+      <c r="Q59" s="139"/>
       <c r="R59" s="24"/>
     </row>
-    <row r="60" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="str">
         <f>_xlfn.XLOOKUP(B60,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12236,53 +12240,53 @@
       <c r="B60" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C60" s="146">
+      <c r="C60" s="140">
         <v>4</v>
       </c>
-      <c r="D60" s="146" t="s">
+      <c r="D60" s="140" t="s">
         <v>257</v>
       </c>
-      <c r="E60" s="164" t="s">
+      <c r="E60" s="137" t="s">
         <v>258</v>
       </c>
-      <c r="F60" s="146" t="s">
+      <c r="F60" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G60" s="146"/>
-      <c r="H60" s="146" t="s">
+      <c r="G60" s="140"/>
+      <c r="H60" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I60" s="146"/>
-      <c r="J60" s="146">
+      <c r="I60" s="140"/>
+      <c r="J60" s="140">
         <v>3</v>
       </c>
-      <c r="K60" s="146">
+      <c r="K60" s="140">
         <f>J60*12</f>
         <v>36</v>
       </c>
-      <c r="L60" s="146">
+      <c r="L60" s="140">
         <f>36*J60</f>
         <v>108</v>
       </c>
-      <c r="M60" s="146">
+      <c r="M60" s="140">
         <f>SUM(K60:L60)</f>
         <v>144</v>
       </c>
-      <c r="N60" s="164" t="s">
+      <c r="N60" s="137" t="s">
         <v>259</v>
       </c>
-      <c r="O60" s="164" t="s">
+      <c r="O60" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P60" s="164" t="s">
+      <c r="P60" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q60" s="164" t="s">
+      <c r="Q60" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R60" s="24"/>
     </row>
-    <row r="61" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="str">
         <f>_xlfn.XLOOKUP(B61,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12290,24 +12294,24 @@
       <c r="B61" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C61" s="137"/>
-      <c r="D61" s="137"/>
-      <c r="E61" s="165"/>
-      <c r="F61" s="137"/>
-      <c r="G61" s="137"/>
-      <c r="H61" s="137"/>
-      <c r="I61" s="137"/>
-      <c r="J61" s="137"/>
-      <c r="K61" s="137"/>
-      <c r="L61" s="137"/>
-      <c r="M61" s="137"/>
-      <c r="N61" s="165"/>
-      <c r="O61" s="165"/>
-      <c r="P61" s="165"/>
-      <c r="Q61" s="165"/>
+      <c r="C61" s="141"/>
+      <c r="D61" s="141"/>
+      <c r="E61" s="138"/>
+      <c r="F61" s="141"/>
+      <c r="G61" s="141"/>
+      <c r="H61" s="141"/>
+      <c r="I61" s="141"/>
+      <c r="J61" s="141"/>
+      <c r="K61" s="141"/>
+      <c r="L61" s="141"/>
+      <c r="M61" s="141"/>
+      <c r="N61" s="138"/>
+      <c r="O61" s="138"/>
+      <c r="P61" s="138"/>
+      <c r="Q61" s="138"/>
       <c r="R61" s="24"/>
     </row>
-    <row r="62" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="97" t="str">
         <f>_xlfn.XLOOKUP(B62,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12315,21 +12319,21 @@
       <c r="B62" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C62" s="162"/>
-      <c r="D62" s="162"/>
-      <c r="E62" s="166"/>
-      <c r="F62" s="162"/>
-      <c r="G62" s="162"/>
-      <c r="H62" s="162"/>
-      <c r="I62" s="162"/>
-      <c r="J62" s="162"/>
-      <c r="K62" s="162"/>
-      <c r="L62" s="162"/>
-      <c r="M62" s="162"/>
-      <c r="N62" s="166"/>
-      <c r="O62" s="166"/>
-      <c r="P62" s="166"/>
-      <c r="Q62" s="166"/>
+      <c r="C62" s="142"/>
+      <c r="D62" s="142"/>
+      <c r="E62" s="139"/>
+      <c r="F62" s="142"/>
+      <c r="G62" s="142"/>
+      <c r="H62" s="142"/>
+      <c r="I62" s="142"/>
+      <c r="J62" s="142"/>
+      <c r="K62" s="142"/>
+      <c r="L62" s="142"/>
+      <c r="M62" s="142"/>
+      <c r="N62" s="139"/>
+      <c r="O62" s="139"/>
+      <c r="P62" s="139"/>
+      <c r="Q62" s="139"/>
       <c r="R62" s="24">
         <f>SUM(J47:J62)</f>
         <v>18</v>
@@ -12339,7 +12343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="str">
         <f>_xlfn.XLOOKUP(B63,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12347,53 +12351,53 @@
       <c r="B63" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="146">
+      <c r="C63" s="140">
         <v>5</v>
       </c>
-      <c r="D63" s="146" t="s">
+      <c r="D63" s="140" t="s">
         <v>260</v>
       </c>
-      <c r="E63" s="164" t="s">
+      <c r="E63" s="137" t="s">
         <v>239</v>
       </c>
-      <c r="F63" s="146" t="s">
+      <c r="F63" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G63" s="146"/>
-      <c r="H63" s="146" t="s">
+      <c r="G63" s="140"/>
+      <c r="H63" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I63" s="146"/>
-      <c r="J63" s="146">
+      <c r="I63" s="140"/>
+      <c r="J63" s="140">
         <v>3</v>
       </c>
-      <c r="K63" s="146">
+      <c r="K63" s="140">
         <f>J63*12</f>
         <v>36</v>
       </c>
-      <c r="L63" s="146">
+      <c r="L63" s="140">
         <f>36*J63</f>
         <v>108</v>
       </c>
-      <c r="M63" s="146">
+      <c r="M63" s="140">
         <f>SUM(K63:L63)</f>
         <v>144</v>
       </c>
-      <c r="N63" s="164" t="s">
+      <c r="N63" s="137" t="s">
         <v>261</v>
       </c>
-      <c r="O63" s="164" t="s">
+      <c r="O63" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P63" s="164" t="s">
+      <c r="P63" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q63" s="164" t="s">
+      <c r="Q63" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R63" s="24"/>
     </row>
-    <row r="64" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="str">
         <f>_xlfn.XLOOKUP(B64,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12401,24 +12405,24 @@
       <c r="B64" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="137"/>
-      <c r="D64" s="137"/>
-      <c r="E64" s="165"/>
-      <c r="F64" s="137"/>
-      <c r="G64" s="137"/>
-      <c r="H64" s="137"/>
-      <c r="I64" s="137"/>
-      <c r="J64" s="137"/>
-      <c r="K64" s="137"/>
-      <c r="L64" s="137"/>
-      <c r="M64" s="137"/>
-      <c r="N64" s="165"/>
-      <c r="O64" s="165"/>
-      <c r="P64" s="165"/>
-      <c r="Q64" s="165"/>
+      <c r="C64" s="141"/>
+      <c r="D64" s="141"/>
+      <c r="E64" s="138"/>
+      <c r="F64" s="141"/>
+      <c r="G64" s="141"/>
+      <c r="H64" s="141"/>
+      <c r="I64" s="141"/>
+      <c r="J64" s="141"/>
+      <c r="K64" s="141"/>
+      <c r="L64" s="141"/>
+      <c r="M64" s="141"/>
+      <c r="N64" s="138"/>
+      <c r="O64" s="138"/>
+      <c r="P64" s="138"/>
+      <c r="Q64" s="138"/>
       <c r="R64" s="24"/>
     </row>
-    <row r="65" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A65" s="97" t="str">
         <f>_xlfn.XLOOKUP(B65,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12426,24 +12430,24 @@
       <c r="B65" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C65" s="162"/>
-      <c r="D65" s="162"/>
-      <c r="E65" s="166"/>
-      <c r="F65" s="162"/>
-      <c r="G65" s="162"/>
-      <c r="H65" s="162"/>
-      <c r="I65" s="162"/>
-      <c r="J65" s="162"/>
-      <c r="K65" s="162"/>
-      <c r="L65" s="162"/>
-      <c r="M65" s="147"/>
-      <c r="N65" s="166"/>
-      <c r="O65" s="166"/>
-      <c r="P65" s="166"/>
-      <c r="Q65" s="166"/>
+      <c r="C65" s="142"/>
+      <c r="D65" s="142"/>
+      <c r="E65" s="139"/>
+      <c r="F65" s="142"/>
+      <c r="G65" s="142"/>
+      <c r="H65" s="142"/>
+      <c r="I65" s="142"/>
+      <c r="J65" s="142"/>
+      <c r="K65" s="142"/>
+      <c r="L65" s="142"/>
+      <c r="M65" s="143"/>
+      <c r="N65" s="139"/>
+      <c r="O65" s="139"/>
+      <c r="P65" s="139"/>
+      <c r="Q65" s="139"/>
       <c r="R65" s="24"/>
     </row>
-    <row r="66" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19" s="50" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="str">
         <f>_xlfn.XLOOKUP(B66,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12451,53 +12455,53 @@
       <c r="B66" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C66" s="146">
+      <c r="C66" s="140">
         <v>5</v>
       </c>
-      <c r="D66" s="146" t="s">
+      <c r="D66" s="140" t="s">
         <v>262</v>
       </c>
-      <c r="E66" s="164" t="s">
+      <c r="E66" s="137" t="s">
         <v>263</v>
       </c>
-      <c r="F66" s="146" t="s">
+      <c r="F66" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G66" s="146"/>
-      <c r="H66" s="146" t="s">
+      <c r="G66" s="140"/>
+      <c r="H66" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I66" s="146"/>
-      <c r="J66" s="146">
+      <c r="I66" s="140"/>
+      <c r="J66" s="140">
         <v>4</v>
       </c>
-      <c r="K66" s="146">
+      <c r="K66" s="140">
         <f>J66*12</f>
         <v>48</v>
       </c>
-      <c r="L66" s="146">
+      <c r="L66" s="140">
         <f>36*J66</f>
         <v>144</v>
       </c>
-      <c r="M66" s="137">
+      <c r="M66" s="141">
         <f>SUM(K66:L66)</f>
         <v>192</v>
       </c>
-      <c r="N66" s="164" t="s">
+      <c r="N66" s="137" t="s">
         <v>264</v>
       </c>
-      <c r="O66" s="164" t="s">
+      <c r="O66" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P66" s="164" t="s">
+      <c r="P66" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q66" s="164" t="s">
+      <c r="Q66" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R66" s="24"/>
     </row>
-    <row r="67" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="str">
         <f>_xlfn.XLOOKUP(B67,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12505,24 +12509,24 @@
       <c r="B67" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C67" s="137"/>
-      <c r="D67" s="137"/>
-      <c r="E67" s="165"/>
-      <c r="F67" s="137"/>
-      <c r="G67" s="137"/>
-      <c r="H67" s="137"/>
-      <c r="I67" s="137"/>
-      <c r="J67" s="137"/>
-      <c r="K67" s="137"/>
-      <c r="L67" s="137"/>
-      <c r="M67" s="137"/>
-      <c r="N67" s="165"/>
-      <c r="O67" s="165"/>
-      <c r="P67" s="165"/>
-      <c r="Q67" s="165"/>
+      <c r="C67" s="141"/>
+      <c r="D67" s="141"/>
+      <c r="E67" s="138"/>
+      <c r="F67" s="141"/>
+      <c r="G67" s="141"/>
+      <c r="H67" s="141"/>
+      <c r="I67" s="141"/>
+      <c r="J67" s="141"/>
+      <c r="K67" s="141"/>
+      <c r="L67" s="141"/>
+      <c r="M67" s="141"/>
+      <c r="N67" s="138"/>
+      <c r="O67" s="138"/>
+      <c r="P67" s="138"/>
+      <c r="Q67" s="138"/>
       <c r="R67" s="24"/>
     </row>
-    <row r="68" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="97" t="str">
         <f>_xlfn.XLOOKUP(B68,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12530,24 +12534,24 @@
       <c r="B68" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C68" s="162"/>
-      <c r="D68" s="162"/>
-      <c r="E68" s="166"/>
-      <c r="F68" s="162"/>
-      <c r="G68" s="162"/>
-      <c r="H68" s="162"/>
-      <c r="I68" s="162"/>
-      <c r="J68" s="162"/>
-      <c r="K68" s="162"/>
-      <c r="L68" s="162"/>
-      <c r="M68" s="162"/>
-      <c r="N68" s="166"/>
-      <c r="O68" s="166"/>
-      <c r="P68" s="166"/>
-      <c r="Q68" s="166"/>
+      <c r="C68" s="142"/>
+      <c r="D68" s="142"/>
+      <c r="E68" s="139"/>
+      <c r="F68" s="142"/>
+      <c r="G68" s="142"/>
+      <c r="H68" s="142"/>
+      <c r="I68" s="142"/>
+      <c r="J68" s="142"/>
+      <c r="K68" s="142"/>
+      <c r="L68" s="142"/>
+      <c r="M68" s="142"/>
+      <c r="N68" s="139"/>
+      <c r="O68" s="139"/>
+      <c r="P68" s="139"/>
+      <c r="Q68" s="139"/>
       <c r="R68" s="24"/>
     </row>
-    <row r="69" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="str">
         <f>_xlfn.XLOOKUP(B69,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12555,53 +12559,53 @@
       <c r="B69" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="146">
+      <c r="C69" s="140">
         <v>5</v>
       </c>
-      <c r="D69" s="146" t="s">
+      <c r="D69" s="140" t="s">
         <v>265</v>
       </c>
-      <c r="E69" s="164" t="s">
+      <c r="E69" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="F69" s="146" t="s">
+      <c r="F69" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G69" s="146"/>
-      <c r="H69" s="146" t="s">
+      <c r="G69" s="140"/>
+      <c r="H69" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I69" s="146"/>
-      <c r="J69" s="146">
+      <c r="I69" s="140"/>
+      <c r="J69" s="140">
         <v>3</v>
       </c>
-      <c r="K69" s="146">
+      <c r="K69" s="140">
         <f>J69*12</f>
         <v>36</v>
       </c>
-      <c r="L69" s="146">
+      <c r="L69" s="140">
         <f>36*J69</f>
         <v>108</v>
       </c>
-      <c r="M69" s="146">
+      <c r="M69" s="140">
         <f>SUM(K69:L69)</f>
         <v>144</v>
       </c>
-      <c r="N69" s="164" t="s">
+      <c r="N69" s="137" t="s">
         <v>267</v>
       </c>
-      <c r="O69" s="164" t="s">
+      <c r="O69" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P69" s="164" t="s">
+      <c r="P69" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q69" s="164" t="s">
+      <c r="Q69" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R69" s="24"/>
     </row>
-    <row r="70" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="str">
         <f>_xlfn.XLOOKUP(B70,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12609,24 +12613,24 @@
       <c r="B70" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C70" s="137"/>
-      <c r="D70" s="137"/>
-      <c r="E70" s="165"/>
-      <c r="F70" s="137"/>
-      <c r="G70" s="137"/>
-      <c r="H70" s="137"/>
-      <c r="I70" s="137"/>
-      <c r="J70" s="137"/>
-      <c r="K70" s="137"/>
-      <c r="L70" s="137"/>
-      <c r="M70" s="137"/>
-      <c r="N70" s="165"/>
-      <c r="O70" s="165"/>
-      <c r="P70" s="165"/>
-      <c r="Q70" s="165"/>
+      <c r="C70" s="141"/>
+      <c r="D70" s="141"/>
+      <c r="E70" s="138"/>
+      <c r="F70" s="141"/>
+      <c r="G70" s="141"/>
+      <c r="H70" s="141"/>
+      <c r="I70" s="141"/>
+      <c r="J70" s="141"/>
+      <c r="K70" s="141"/>
+      <c r="L70" s="141"/>
+      <c r="M70" s="141"/>
+      <c r="N70" s="138"/>
+      <c r="O70" s="138"/>
+      <c r="P70" s="138"/>
+      <c r="Q70" s="138"/>
       <c r="R70" s="24"/>
     </row>
-    <row r="71" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="97" t="str">
         <f>_xlfn.XLOOKUP(B71,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12634,24 +12638,24 @@
       <c r="B71" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C71" s="162"/>
-      <c r="D71" s="162"/>
-      <c r="E71" s="167"/>
-      <c r="F71" s="162"/>
-      <c r="G71" s="162"/>
-      <c r="H71" s="162"/>
-      <c r="I71" s="162"/>
-      <c r="J71" s="162"/>
-      <c r="K71" s="162"/>
-      <c r="L71" s="162"/>
-      <c r="M71" s="162"/>
-      <c r="N71" s="166"/>
-      <c r="O71" s="166"/>
-      <c r="P71" s="166"/>
-      <c r="Q71" s="166"/>
+      <c r="C71" s="142"/>
+      <c r="D71" s="142"/>
+      <c r="E71" s="148"/>
+      <c r="F71" s="142"/>
+      <c r="G71" s="142"/>
+      <c r="H71" s="142"/>
+      <c r="I71" s="142"/>
+      <c r="J71" s="142"/>
+      <c r="K71" s="142"/>
+      <c r="L71" s="142"/>
+      <c r="M71" s="142"/>
+      <c r="N71" s="139"/>
+      <c r="O71" s="139"/>
+      <c r="P71" s="139"/>
+      <c r="Q71" s="139"/>
       <c r="R71" s="24"/>
     </row>
-    <row r="72" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A72" s="24" t="str">
         <f>_xlfn.XLOOKUP(B72,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12659,53 +12663,53 @@
       <c r="B72" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="146">
+      <c r="C72" s="140">
         <v>5</v>
       </c>
-      <c r="D72" s="146" t="s">
+      <c r="D72" s="140" t="s">
         <v>268</v>
       </c>
-      <c r="E72" s="165" t="s">
+      <c r="E72" s="138" t="s">
         <v>269</v>
       </c>
-      <c r="F72" s="146" t="s">
+      <c r="F72" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G72" s="146"/>
-      <c r="H72" s="146" t="s">
+      <c r="G72" s="140"/>
+      <c r="H72" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I72" s="146"/>
-      <c r="J72" s="146">
+      <c r="I72" s="140"/>
+      <c r="J72" s="140">
         <v>3</v>
       </c>
-      <c r="K72" s="146">
+      <c r="K72" s="140">
         <f>J72*12</f>
         <v>36</v>
       </c>
-      <c r="L72" s="146">
+      <c r="L72" s="140">
         <f>36*J72</f>
         <v>108</v>
       </c>
-      <c r="M72" s="146">
+      <c r="M72" s="140">
         <f>SUM(K72:L72)</f>
         <v>144</v>
       </c>
-      <c r="N72" s="164" t="s">
+      <c r="N72" s="137" t="s">
         <v>270</v>
       </c>
-      <c r="O72" s="164" t="s">
+      <c r="O72" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P72" s="164" t="s">
+      <c r="P72" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q72" s="164" t="s">
+      <c r="Q72" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R72" s="24"/>
     </row>
-    <row r="73" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="str">
         <f>_xlfn.XLOOKUP(B73,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12713,24 +12717,24 @@
       <c r="B73" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C73" s="137"/>
-      <c r="D73" s="137"/>
-      <c r="E73" s="165"/>
-      <c r="F73" s="137"/>
-      <c r="G73" s="137"/>
-      <c r="H73" s="137"/>
-      <c r="I73" s="137"/>
-      <c r="J73" s="137"/>
-      <c r="K73" s="137"/>
-      <c r="L73" s="137"/>
-      <c r="M73" s="137"/>
-      <c r="N73" s="165"/>
-      <c r="O73" s="165"/>
-      <c r="P73" s="165"/>
-      <c r="Q73" s="165"/>
+      <c r="C73" s="141"/>
+      <c r="D73" s="141"/>
+      <c r="E73" s="138"/>
+      <c r="F73" s="141"/>
+      <c r="G73" s="141"/>
+      <c r="H73" s="141"/>
+      <c r="I73" s="141"/>
+      <c r="J73" s="141"/>
+      <c r="K73" s="141"/>
+      <c r="L73" s="141"/>
+      <c r="M73" s="141"/>
+      <c r="N73" s="138"/>
+      <c r="O73" s="138"/>
+      <c r="P73" s="138"/>
+      <c r="Q73" s="138"/>
       <c r="R73" s="24"/>
     </row>
-    <row r="74" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="97" t="str">
         <f>_xlfn.XLOOKUP(B74,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12738,24 +12742,24 @@
       <c r="B74" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C74" s="162"/>
-      <c r="D74" s="162"/>
-      <c r="E74" s="167"/>
-      <c r="F74" s="162"/>
-      <c r="G74" s="147"/>
-      <c r="H74" s="147"/>
-      <c r="I74" s="147"/>
-      <c r="J74" s="147"/>
-      <c r="K74" s="162"/>
-      <c r="L74" s="162"/>
-      <c r="M74" s="147"/>
-      <c r="N74" s="167"/>
-      <c r="O74" s="166"/>
-      <c r="P74" s="166"/>
-      <c r="Q74" s="166"/>
+      <c r="C74" s="142"/>
+      <c r="D74" s="142"/>
+      <c r="E74" s="148"/>
+      <c r="F74" s="142"/>
+      <c r="G74" s="143"/>
+      <c r="H74" s="143"/>
+      <c r="I74" s="143"/>
+      <c r="J74" s="143"/>
+      <c r="K74" s="142"/>
+      <c r="L74" s="142"/>
+      <c r="M74" s="143"/>
+      <c r="N74" s="148"/>
+      <c r="O74" s="139"/>
+      <c r="P74" s="139"/>
+      <c r="Q74" s="139"/>
       <c r="R74" s="24"/>
     </row>
-    <row r="75" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A75" s="24" t="str">
         <f>_xlfn.XLOOKUP(B75,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12763,53 +12767,53 @@
       <c r="B75" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C75" s="146">
+      <c r="C75" s="140">
         <v>5</v>
       </c>
-      <c r="D75" s="146" t="s">
+      <c r="D75" s="140" t="s">
         <v>271</v>
       </c>
-      <c r="E75" s="165" t="s">
+      <c r="E75" s="138" t="s">
         <v>272</v>
       </c>
-      <c r="F75" s="146" t="s">
+      <c r="F75" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G75" s="137"/>
-      <c r="H75" s="137" t="s">
+      <c r="G75" s="141"/>
+      <c r="H75" s="141" t="s">
         <v>177</v>
       </c>
-      <c r="I75" s="137"/>
-      <c r="J75" s="137">
+      <c r="I75" s="141"/>
+      <c r="J75" s="141">
         <v>3</v>
       </c>
-      <c r="K75" s="146">
+      <c r="K75" s="140">
         <f>J75*12</f>
         <v>36</v>
       </c>
-      <c r="L75" s="146">
+      <c r="L75" s="140">
         <f>36*J75</f>
         <v>108</v>
       </c>
-      <c r="M75" s="137">
+      <c r="M75" s="141">
         <f>SUM(K75:L75)</f>
         <v>144</v>
       </c>
-      <c r="N75" s="165" t="s">
+      <c r="N75" s="138" t="s">
         <v>273</v>
       </c>
-      <c r="O75" s="164" t="s">
+      <c r="O75" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P75" s="164" t="s">
+      <c r="P75" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q75" s="164" t="s">
+      <c r="Q75" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R75" s="24"/>
     </row>
-    <row r="76" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="str">
         <f>_xlfn.XLOOKUP(B76,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12817,24 +12821,24 @@
       <c r="B76" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C76" s="137"/>
-      <c r="D76" s="137"/>
-      <c r="E76" s="165"/>
-      <c r="F76" s="137"/>
-      <c r="G76" s="137"/>
-      <c r="H76" s="137"/>
-      <c r="I76" s="137"/>
-      <c r="J76" s="137"/>
-      <c r="K76" s="137"/>
-      <c r="L76" s="137"/>
-      <c r="M76" s="137"/>
-      <c r="N76" s="165"/>
-      <c r="O76" s="165"/>
-      <c r="P76" s="165"/>
-      <c r="Q76" s="165"/>
+      <c r="C76" s="141"/>
+      <c r="D76" s="141"/>
+      <c r="E76" s="138"/>
+      <c r="F76" s="141"/>
+      <c r="G76" s="141"/>
+      <c r="H76" s="141"/>
+      <c r="I76" s="141"/>
+      <c r="J76" s="141"/>
+      <c r="K76" s="141"/>
+      <c r="L76" s="141"/>
+      <c r="M76" s="141"/>
+      <c r="N76" s="138"/>
+      <c r="O76" s="138"/>
+      <c r="P76" s="138"/>
+      <c r="Q76" s="138"/>
       <c r="R76" s="24"/>
     </row>
-    <row r="77" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="97" t="str">
         <f>_xlfn.XLOOKUP(B77,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12842,24 +12846,24 @@
       <c r="B77" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="162"/>
-      <c r="D77" s="162"/>
-      <c r="E77" s="166"/>
-      <c r="F77" s="162"/>
-      <c r="G77" s="162"/>
-      <c r="H77" s="162"/>
-      <c r="I77" s="162"/>
-      <c r="J77" s="162"/>
-      <c r="K77" s="162"/>
-      <c r="L77" s="162"/>
-      <c r="M77" s="162"/>
-      <c r="N77" s="166"/>
-      <c r="O77" s="166"/>
-      <c r="P77" s="166"/>
-      <c r="Q77" s="166"/>
+      <c r="C77" s="142"/>
+      <c r="D77" s="142"/>
+      <c r="E77" s="139"/>
+      <c r="F77" s="142"/>
+      <c r="G77" s="142"/>
+      <c r="H77" s="142"/>
+      <c r="I77" s="142"/>
+      <c r="J77" s="142"/>
+      <c r="K77" s="142"/>
+      <c r="L77" s="142"/>
+      <c r="M77" s="142"/>
+      <c r="N77" s="139"/>
+      <c r="O77" s="139"/>
+      <c r="P77" s="139"/>
+      <c r="Q77" s="139"/>
       <c r="R77" s="24"/>
     </row>
-    <row r="78" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="str">
         <f>_xlfn.XLOOKUP(B78,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12867,53 +12871,53 @@
       <c r="B78" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C78" s="146">
+      <c r="C78" s="140">
         <v>5</v>
       </c>
-      <c r="D78" s="146" t="s">
+      <c r="D78" s="140" t="s">
         <v>274</v>
       </c>
-      <c r="E78" s="168" t="s">
+      <c r="E78" s="144" t="s">
         <v>275</v>
       </c>
-      <c r="F78" s="146" t="s">
+      <c r="F78" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G78" s="146"/>
-      <c r="H78" s="146" t="s">
+      <c r="G78" s="140"/>
+      <c r="H78" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I78" s="146"/>
-      <c r="J78" s="146">
+      <c r="I78" s="140"/>
+      <c r="J78" s="140">
         <v>3</v>
       </c>
-      <c r="K78" s="146">
+      <c r="K78" s="140">
         <f>J78*12</f>
         <v>36</v>
       </c>
-      <c r="L78" s="146">
+      <c r="L78" s="140">
         <f>36*J78</f>
         <v>108</v>
       </c>
-      <c r="M78" s="146">
+      <c r="M78" s="140">
         <f>SUM(K78:L78)</f>
         <v>144</v>
       </c>
-      <c r="N78" s="164" t="s">
+      <c r="N78" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="O78" s="164" t="s">
+      <c r="O78" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P78" s="164" t="s">
+      <c r="P78" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q78" s="164" t="s">
+      <c r="Q78" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R78" s="24"/>
     </row>
-    <row r="79" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="str">
         <f>_xlfn.XLOOKUP(B79,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12921,24 +12925,24 @@
       <c r="B79" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C79" s="137"/>
-      <c r="D79" s="137"/>
-      <c r="E79" s="159"/>
-      <c r="F79" s="137"/>
-      <c r="G79" s="137"/>
-      <c r="H79" s="137"/>
-      <c r="I79" s="137"/>
-      <c r="J79" s="137"/>
-      <c r="K79" s="137"/>
-      <c r="L79" s="137"/>
-      <c r="M79" s="137"/>
-      <c r="N79" s="165"/>
-      <c r="O79" s="165"/>
-      <c r="P79" s="165"/>
-      <c r="Q79" s="165"/>
+      <c r="C79" s="141"/>
+      <c r="D79" s="141"/>
+      <c r="E79" s="145"/>
+      <c r="F79" s="141"/>
+      <c r="G79" s="141"/>
+      <c r="H79" s="141"/>
+      <c r="I79" s="141"/>
+      <c r="J79" s="141"/>
+      <c r="K79" s="141"/>
+      <c r="L79" s="141"/>
+      <c r="M79" s="141"/>
+      <c r="N79" s="138"/>
+      <c r="O79" s="138"/>
+      <c r="P79" s="138"/>
+      <c r="Q79" s="138"/>
       <c r="R79" s="24"/>
     </row>
-    <row r="80" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="97" t="str">
         <f>_xlfn.XLOOKUP(B80,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12946,21 +12950,21 @@
       <c r="B80" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C80" s="162"/>
-      <c r="D80" s="162"/>
-      <c r="E80" s="160"/>
-      <c r="F80" s="162"/>
-      <c r="G80" s="162"/>
-      <c r="H80" s="162"/>
-      <c r="I80" s="162"/>
-      <c r="J80" s="162"/>
-      <c r="K80" s="162"/>
-      <c r="L80" s="162"/>
-      <c r="M80" s="162"/>
-      <c r="N80" s="166"/>
-      <c r="O80" s="166"/>
-      <c r="P80" s="166"/>
-      <c r="Q80" s="166"/>
+      <c r="C80" s="142"/>
+      <c r="D80" s="142"/>
+      <c r="E80" s="147"/>
+      <c r="F80" s="142"/>
+      <c r="G80" s="142"/>
+      <c r="H80" s="142"/>
+      <c r="I80" s="142"/>
+      <c r="J80" s="142"/>
+      <c r="K80" s="142"/>
+      <c r="L80" s="142"/>
+      <c r="M80" s="142"/>
+      <c r="N80" s="139"/>
+      <c r="O80" s="139"/>
+      <c r="P80" s="139"/>
+      <c r="Q80" s="139"/>
       <c r="R80" s="24">
         <f>SUM(J63:J80)</f>
         <v>19</v>
@@ -12970,7 +12974,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:18" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="str">
         <f>_xlfn.XLOOKUP(B81,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12978,53 +12982,53 @@
       <c r="B81" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="146">
+      <c r="C81" s="140">
         <v>6</v>
       </c>
-      <c r="D81" s="146" t="s">
+      <c r="D81" s="140" t="s">
         <v>277</v>
       </c>
-      <c r="E81" s="164" t="s">
+      <c r="E81" s="137" t="s">
         <v>278</v>
       </c>
-      <c r="F81" s="146" t="s">
+      <c r="F81" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G81" s="146"/>
-      <c r="H81" s="146" t="s">
+      <c r="G81" s="140"/>
+      <c r="H81" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I81" s="146"/>
-      <c r="J81" s="146">
+      <c r="I81" s="140"/>
+      <c r="J81" s="140">
         <v>3</v>
       </c>
-      <c r="K81" s="146">
+      <c r="K81" s="140">
         <f>J81*12</f>
         <v>36</v>
       </c>
-      <c r="L81" s="146">
+      <c r="L81" s="140">
         <f>36*J81</f>
         <v>108</v>
       </c>
-      <c r="M81" s="146">
+      <c r="M81" s="140">
         <f>SUM(K81:L81)</f>
         <v>144</v>
       </c>
-      <c r="N81" s="164" t="s">
+      <c r="N81" s="137" t="s">
         <v>279</v>
       </c>
-      <c r="O81" s="164" t="s">
+      <c r="O81" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P81" s="164" t="s">
+      <c r="P81" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q81" s="164" t="s">
+      <c r="Q81" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R81" s="24"/>
     </row>
-    <row r="82" spans="1:18" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A82" s="24" t="str">
         <f>_xlfn.XLOOKUP(B82,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13032,24 +13036,24 @@
       <c r="B82" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C82" s="137"/>
-      <c r="D82" s="137"/>
-      <c r="E82" s="165"/>
-      <c r="F82" s="137"/>
-      <c r="G82" s="137"/>
-      <c r="H82" s="137"/>
-      <c r="I82" s="137"/>
-      <c r="J82" s="137"/>
-      <c r="K82" s="137"/>
-      <c r="L82" s="137"/>
-      <c r="M82" s="137"/>
-      <c r="N82" s="165"/>
-      <c r="O82" s="165"/>
-      <c r="P82" s="165"/>
-      <c r="Q82" s="165"/>
+      <c r="C82" s="141"/>
+      <c r="D82" s="141"/>
+      <c r="E82" s="138"/>
+      <c r="F82" s="141"/>
+      <c r="G82" s="141"/>
+      <c r="H82" s="141"/>
+      <c r="I82" s="141"/>
+      <c r="J82" s="141"/>
+      <c r="K82" s="141"/>
+      <c r="L82" s="141"/>
+      <c r="M82" s="141"/>
+      <c r="N82" s="138"/>
+      <c r="O82" s="138"/>
+      <c r="P82" s="138"/>
+      <c r="Q82" s="138"/>
       <c r="R82" s="24"/>
     </row>
-    <row r="83" spans="1:18" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:18" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="97" t="str">
         <f>_xlfn.XLOOKUP(B83,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13057,24 +13061,24 @@
       <c r="B83" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C83" s="162"/>
-      <c r="D83" s="162"/>
-      <c r="E83" s="166"/>
-      <c r="F83" s="162"/>
-      <c r="G83" s="162"/>
-      <c r="H83" s="162"/>
-      <c r="I83" s="162"/>
-      <c r="J83" s="162"/>
-      <c r="K83" s="162"/>
-      <c r="L83" s="162"/>
-      <c r="M83" s="162"/>
-      <c r="N83" s="166"/>
-      <c r="O83" s="166"/>
-      <c r="P83" s="166"/>
-      <c r="Q83" s="166"/>
+      <c r="C83" s="142"/>
+      <c r="D83" s="142"/>
+      <c r="E83" s="139"/>
+      <c r="F83" s="142"/>
+      <c r="G83" s="142"/>
+      <c r="H83" s="142"/>
+      <c r="I83" s="142"/>
+      <c r="J83" s="142"/>
+      <c r="K83" s="142"/>
+      <c r="L83" s="142"/>
+      <c r="M83" s="142"/>
+      <c r="N83" s="139"/>
+      <c r="O83" s="139"/>
+      <c r="P83" s="139"/>
+      <c r="Q83" s="139"/>
       <c r="R83" s="24"/>
     </row>
-    <row r="84" spans="1:18" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="str">
         <f>_xlfn.XLOOKUP(B84,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13082,53 +13086,53 @@
       <c r="B84" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C84" s="146">
+      <c r="C84" s="140">
         <v>6</v>
       </c>
-      <c r="D84" s="146" t="s">
+      <c r="D84" s="140" t="s">
         <v>280</v>
       </c>
-      <c r="E84" s="164" t="s">
+      <c r="E84" s="137" t="s">
         <v>281</v>
       </c>
-      <c r="F84" s="146" t="s">
+      <c r="F84" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G84" s="146"/>
-      <c r="H84" s="146" t="s">
+      <c r="G84" s="140"/>
+      <c r="H84" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I84" s="146"/>
-      <c r="J84" s="146">
+      <c r="I84" s="140"/>
+      <c r="J84" s="140">
         <v>3</v>
       </c>
-      <c r="K84" s="146">
+      <c r="K84" s="140">
         <f>J84*12</f>
         <v>36</v>
       </c>
-      <c r="L84" s="146">
+      <c r="L84" s="140">
         <f>36*J84</f>
         <v>108</v>
       </c>
-      <c r="M84" s="146">
+      <c r="M84" s="140">
         <f>SUM(K84:L84)</f>
         <v>144</v>
       </c>
-      <c r="N84" s="164" t="s">
+      <c r="N84" s="137" t="s">
         <v>282</v>
       </c>
-      <c r="O84" s="164" t="s">
+      <c r="O84" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P84" s="164" t="s">
+      <c r="P84" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q84" s="164" t="s">
+      <c r="Q84" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R84" s="24"/>
     </row>
-    <row r="85" spans="1:18" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="str">
         <f>_xlfn.XLOOKUP(B85,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13136,24 +13140,24 @@
       <c r="B85" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C85" s="137"/>
-      <c r="D85" s="137"/>
-      <c r="E85" s="165"/>
-      <c r="F85" s="137"/>
-      <c r="G85" s="137"/>
-      <c r="H85" s="137"/>
-      <c r="I85" s="137"/>
-      <c r="J85" s="137"/>
-      <c r="K85" s="137"/>
-      <c r="L85" s="137"/>
-      <c r="M85" s="137"/>
-      <c r="N85" s="165"/>
-      <c r="O85" s="165"/>
-      <c r="P85" s="165"/>
-      <c r="Q85" s="165"/>
+      <c r="C85" s="141"/>
+      <c r="D85" s="141"/>
+      <c r="E85" s="138"/>
+      <c r="F85" s="141"/>
+      <c r="G85" s="141"/>
+      <c r="H85" s="141"/>
+      <c r="I85" s="141"/>
+      <c r="J85" s="141"/>
+      <c r="K85" s="141"/>
+      <c r="L85" s="141"/>
+      <c r="M85" s="141"/>
+      <c r="N85" s="138"/>
+      <c r="O85" s="138"/>
+      <c r="P85" s="138"/>
+      <c r="Q85" s="138"/>
       <c r="R85" s="24"/>
     </row>
-    <row r="86" spans="1:18" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:18" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="97" t="str">
         <f>_xlfn.XLOOKUP(B86,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13161,24 +13165,24 @@
       <c r="B86" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C86" s="162"/>
-      <c r="D86" s="162"/>
-      <c r="E86" s="166"/>
-      <c r="F86" s="162"/>
-      <c r="G86" s="162"/>
-      <c r="H86" s="162"/>
-      <c r="I86" s="162"/>
-      <c r="J86" s="162"/>
-      <c r="K86" s="162"/>
-      <c r="L86" s="162"/>
-      <c r="M86" s="162"/>
-      <c r="N86" s="166"/>
-      <c r="O86" s="166"/>
-      <c r="P86" s="166"/>
-      <c r="Q86" s="166"/>
+      <c r="C86" s="142"/>
+      <c r="D86" s="142"/>
+      <c r="E86" s="139"/>
+      <c r="F86" s="142"/>
+      <c r="G86" s="142"/>
+      <c r="H86" s="142"/>
+      <c r="I86" s="142"/>
+      <c r="J86" s="142"/>
+      <c r="K86" s="142"/>
+      <c r="L86" s="142"/>
+      <c r="M86" s="142"/>
+      <c r="N86" s="139"/>
+      <c r="O86" s="139"/>
+      <c r="P86" s="139"/>
+      <c r="Q86" s="139"/>
       <c r="R86" s="24"/>
     </row>
-    <row r="87" spans="1:18" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="str">
         <f>_xlfn.XLOOKUP(B87,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13186,53 +13190,53 @@
       <c r="B87" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C87" s="146">
+      <c r="C87" s="140">
         <v>6</v>
       </c>
-      <c r="D87" s="146" t="s">
+      <c r="D87" s="140" t="s">
         <v>283</v>
       </c>
-      <c r="E87" s="164" t="s">
+      <c r="E87" s="137" t="s">
         <v>284</v>
       </c>
-      <c r="F87" s="146" t="s">
+      <c r="F87" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G87" s="146"/>
-      <c r="H87" s="146" t="s">
+      <c r="G87" s="140"/>
+      <c r="H87" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I87" s="146"/>
-      <c r="J87" s="146">
+      <c r="I87" s="140"/>
+      <c r="J87" s="140">
         <v>3</v>
       </c>
-      <c r="K87" s="146">
+      <c r="K87" s="140">
         <f>J87*12</f>
         <v>36</v>
       </c>
-      <c r="L87" s="146">
+      <c r="L87" s="140">
         <f>36*J87</f>
         <v>108</v>
       </c>
-      <c r="M87" s="146">
+      <c r="M87" s="140">
         <f>SUM(K87:L87)</f>
         <v>144</v>
       </c>
-      <c r="N87" s="164" t="s">
+      <c r="N87" s="137" t="s">
         <v>285</v>
       </c>
-      <c r="O87" s="164" t="s">
+      <c r="O87" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P87" s="164" t="s">
+      <c r="P87" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q87" s="164" t="s">
+      <c r="Q87" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R87" s="24"/>
     </row>
-    <row r="88" spans="1:18" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A88" s="24" t="str">
         <f>_xlfn.XLOOKUP(B88,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13240,24 +13244,24 @@
       <c r="B88" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C88" s="137"/>
-      <c r="D88" s="137"/>
-      <c r="E88" s="165"/>
-      <c r="F88" s="137"/>
-      <c r="G88" s="137"/>
-      <c r="H88" s="137"/>
-      <c r="I88" s="137"/>
-      <c r="J88" s="137"/>
-      <c r="K88" s="137"/>
-      <c r="L88" s="137"/>
-      <c r="M88" s="137"/>
-      <c r="N88" s="165"/>
-      <c r="O88" s="165"/>
-      <c r="P88" s="165"/>
-      <c r="Q88" s="165"/>
+      <c r="C88" s="141"/>
+      <c r="D88" s="141"/>
+      <c r="E88" s="138"/>
+      <c r="F88" s="141"/>
+      <c r="G88" s="141"/>
+      <c r="H88" s="141"/>
+      <c r="I88" s="141"/>
+      <c r="J88" s="141"/>
+      <c r="K88" s="141"/>
+      <c r="L88" s="141"/>
+      <c r="M88" s="141"/>
+      <c r="N88" s="138"/>
+      <c r="O88" s="138"/>
+      <c r="P88" s="138"/>
+      <c r="Q88" s="138"/>
       <c r="R88" s="24"/>
     </row>
-    <row r="89" spans="1:18" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:18" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="97" t="str">
         <f>_xlfn.XLOOKUP(B89,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13265,24 +13269,24 @@
       <c r="B89" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="162"/>
-      <c r="D89" s="162"/>
-      <c r="E89" s="166"/>
-      <c r="F89" s="162"/>
-      <c r="G89" s="162"/>
-      <c r="H89" s="162"/>
-      <c r="I89" s="162"/>
-      <c r="J89" s="162"/>
-      <c r="K89" s="162"/>
-      <c r="L89" s="162"/>
-      <c r="M89" s="162"/>
-      <c r="N89" s="166"/>
-      <c r="O89" s="166"/>
-      <c r="P89" s="166"/>
-      <c r="Q89" s="166"/>
+      <c r="C89" s="142"/>
+      <c r="D89" s="142"/>
+      <c r="E89" s="139"/>
+      <c r="F89" s="142"/>
+      <c r="G89" s="142"/>
+      <c r="H89" s="142"/>
+      <c r="I89" s="142"/>
+      <c r="J89" s="142"/>
+      <c r="K89" s="142"/>
+      <c r="L89" s="142"/>
+      <c r="M89" s="142"/>
+      <c r="N89" s="139"/>
+      <c r="O89" s="139"/>
+      <c r="P89" s="139"/>
+      <c r="Q89" s="139"/>
       <c r="R89" s="24"/>
     </row>
-    <row r="90" spans="1:18" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="str">
         <f>_xlfn.XLOOKUP(B90,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13290,53 +13294,53 @@
       <c r="B90" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C90" s="146">
+      <c r="C90" s="140">
         <v>6</v>
       </c>
-      <c r="D90" s="146" t="s">
+      <c r="D90" s="140" t="s">
         <v>286</v>
       </c>
-      <c r="E90" s="164" t="s">
+      <c r="E90" s="137" t="s">
         <v>287</v>
       </c>
-      <c r="F90" s="146" t="s">
+      <c r="F90" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G90" s="146"/>
-      <c r="H90" s="146" t="s">
+      <c r="G90" s="140"/>
+      <c r="H90" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I90" s="146"/>
-      <c r="J90" s="146">
+      <c r="I90" s="140"/>
+      <c r="J90" s="140">
         <v>3</v>
       </c>
-      <c r="K90" s="146">
+      <c r="K90" s="140">
         <f>J90*12</f>
         <v>36</v>
       </c>
-      <c r="L90" s="146">
+      <c r="L90" s="140">
         <f>36*J90</f>
         <v>108</v>
       </c>
-      <c r="M90" s="146">
+      <c r="M90" s="140">
         <f>SUM(K90:L90)</f>
         <v>144</v>
       </c>
-      <c r="N90" s="164" t="s">
+      <c r="N90" s="137" t="s">
         <v>288</v>
       </c>
-      <c r="O90" s="164" t="s">
+      <c r="O90" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P90" s="164" t="s">
+      <c r="P90" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q90" s="164" t="s">
+      <c r="Q90" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R90" s="24"/>
     </row>
-    <row r="91" spans="1:18" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="str">
         <f>_xlfn.XLOOKUP(B91,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13344,24 +13348,24 @@
       <c r="B91" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C91" s="137"/>
-      <c r="D91" s="137"/>
-      <c r="E91" s="165"/>
-      <c r="F91" s="137"/>
-      <c r="G91" s="137"/>
-      <c r="H91" s="137"/>
-      <c r="I91" s="137"/>
-      <c r="J91" s="137"/>
-      <c r="K91" s="137"/>
-      <c r="L91" s="137"/>
-      <c r="M91" s="137"/>
-      <c r="N91" s="165"/>
-      <c r="O91" s="165"/>
-      <c r="P91" s="165"/>
-      <c r="Q91" s="165"/>
+      <c r="C91" s="141"/>
+      <c r="D91" s="141"/>
+      <c r="E91" s="138"/>
+      <c r="F91" s="141"/>
+      <c r="G91" s="141"/>
+      <c r="H91" s="141"/>
+      <c r="I91" s="141"/>
+      <c r="J91" s="141"/>
+      <c r="K91" s="141"/>
+      <c r="L91" s="141"/>
+      <c r="M91" s="141"/>
+      <c r="N91" s="138"/>
+      <c r="O91" s="138"/>
+      <c r="P91" s="138"/>
+      <c r="Q91" s="138"/>
       <c r="R91" s="24"/>
     </row>
-    <row r="92" spans="1:18" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:18" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="97" t="str">
         <f>_xlfn.XLOOKUP(B92,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13369,24 +13373,24 @@
       <c r="B92" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C92" s="162"/>
-      <c r="D92" s="162"/>
-      <c r="E92" s="166"/>
-      <c r="F92" s="162"/>
-      <c r="G92" s="162"/>
-      <c r="H92" s="162"/>
-      <c r="I92" s="162"/>
-      <c r="J92" s="162"/>
-      <c r="K92" s="162"/>
-      <c r="L92" s="162"/>
-      <c r="M92" s="162"/>
-      <c r="N92" s="166"/>
-      <c r="O92" s="166"/>
-      <c r="P92" s="166"/>
-      <c r="Q92" s="166"/>
+      <c r="C92" s="142"/>
+      <c r="D92" s="142"/>
+      <c r="E92" s="139"/>
+      <c r="F92" s="142"/>
+      <c r="G92" s="142"/>
+      <c r="H92" s="142"/>
+      <c r="I92" s="142"/>
+      <c r="J92" s="142"/>
+      <c r="K92" s="142"/>
+      <c r="L92" s="142"/>
+      <c r="M92" s="142"/>
+      <c r="N92" s="139"/>
+      <c r="O92" s="139"/>
+      <c r="P92" s="139"/>
+      <c r="Q92" s="139"/>
       <c r="R92" s="24"/>
     </row>
-    <row r="93" spans="1:18" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="str">
         <f>_xlfn.XLOOKUP(B93,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13394,53 +13398,53 @@
       <c r="B93" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C93" s="146">
+      <c r="C93" s="140">
         <v>6</v>
       </c>
-      <c r="D93" s="146" t="s">
+      <c r="D93" s="140" t="s">
         <v>289</v>
       </c>
-      <c r="E93" s="164" t="s">
+      <c r="E93" s="137" t="s">
         <v>290</v>
       </c>
-      <c r="F93" s="146" t="s">
+      <c r="F93" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G93" s="146"/>
-      <c r="H93" s="146" t="s">
+      <c r="G93" s="140"/>
+      <c r="H93" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I93" s="146"/>
-      <c r="J93" s="146">
+      <c r="I93" s="140"/>
+      <c r="J93" s="140">
         <v>3</v>
       </c>
-      <c r="K93" s="146">
+      <c r="K93" s="140">
         <f>J93*12</f>
         <v>36</v>
       </c>
-      <c r="L93" s="146">
+      <c r="L93" s="140">
         <f>36*J93</f>
         <v>108</v>
       </c>
-      <c r="M93" s="146">
+      <c r="M93" s="140">
         <f>SUM(K93:L93)</f>
         <v>144</v>
       </c>
-      <c r="N93" s="164" t="s">
+      <c r="N93" s="137" t="s">
         <v>291</v>
       </c>
-      <c r="O93" s="164" t="s">
+      <c r="O93" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P93" s="164" t="s">
+      <c r="P93" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q93" s="164" t="s">
+      <c r="Q93" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R93" s="24"/>
     </row>
-    <row r="94" spans="1:18" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="str">
         <f>_xlfn.XLOOKUP(B94,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13448,24 +13452,24 @@
       <c r="B94" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C94" s="137"/>
-      <c r="D94" s="137"/>
-      <c r="E94" s="165"/>
-      <c r="F94" s="137"/>
-      <c r="G94" s="137"/>
-      <c r="H94" s="137"/>
-      <c r="I94" s="137"/>
-      <c r="J94" s="137"/>
-      <c r="K94" s="137"/>
-      <c r="L94" s="137"/>
-      <c r="M94" s="137"/>
-      <c r="N94" s="165"/>
-      <c r="O94" s="165"/>
-      <c r="P94" s="165"/>
-      <c r="Q94" s="165"/>
+      <c r="C94" s="141"/>
+      <c r="D94" s="141"/>
+      <c r="E94" s="138"/>
+      <c r="F94" s="141"/>
+      <c r="G94" s="141"/>
+      <c r="H94" s="141"/>
+      <c r="I94" s="141"/>
+      <c r="J94" s="141"/>
+      <c r="K94" s="141"/>
+      <c r="L94" s="141"/>
+      <c r="M94" s="141"/>
+      <c r="N94" s="138"/>
+      <c r="O94" s="138"/>
+      <c r="P94" s="138"/>
+      <c r="Q94" s="138"/>
       <c r="R94" s="24"/>
     </row>
-    <row r="95" spans="1:18" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:18" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="97" t="str">
         <f>_xlfn.XLOOKUP(B95,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13473,24 +13477,24 @@
       <c r="B95" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C95" s="162"/>
-      <c r="D95" s="162"/>
-      <c r="E95" s="166"/>
-      <c r="F95" s="162"/>
-      <c r="G95" s="162"/>
-      <c r="H95" s="162"/>
-      <c r="I95" s="162"/>
-      <c r="J95" s="162"/>
-      <c r="K95" s="162"/>
-      <c r="L95" s="162"/>
-      <c r="M95" s="162"/>
-      <c r="N95" s="166"/>
-      <c r="O95" s="166"/>
-      <c r="P95" s="166"/>
-      <c r="Q95" s="166"/>
+      <c r="C95" s="142"/>
+      <c r="D95" s="142"/>
+      <c r="E95" s="139"/>
+      <c r="F95" s="142"/>
+      <c r="G95" s="142"/>
+      <c r="H95" s="142"/>
+      <c r="I95" s="142"/>
+      <c r="J95" s="142"/>
+      <c r="K95" s="142"/>
+      <c r="L95" s="142"/>
+      <c r="M95" s="142"/>
+      <c r="N95" s="139"/>
+      <c r="O95" s="139"/>
+      <c r="P95" s="139"/>
+      <c r="Q95" s="139"/>
       <c r="R95" s="24"/>
     </row>
-    <row r="96" spans="1:18" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="str">
         <f>_xlfn.XLOOKUP(B96,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13498,53 +13502,53 @@
       <c r="B96" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="146">
+      <c r="C96" s="140">
         <v>6</v>
       </c>
-      <c r="D96" s="146" t="s">
+      <c r="D96" s="140" t="s">
         <v>292</v>
       </c>
-      <c r="E96" s="164" t="s">
+      <c r="E96" s="137" t="s">
         <v>293</v>
       </c>
-      <c r="F96" s="146" t="s">
+      <c r="F96" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G96" s="146"/>
-      <c r="H96" s="146" t="s">
+      <c r="G96" s="140"/>
+      <c r="H96" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I96" s="146"/>
-      <c r="J96" s="146">
+      <c r="I96" s="140"/>
+      <c r="J96" s="140">
         <v>3</v>
       </c>
-      <c r="K96" s="146">
+      <c r="K96" s="140">
         <f>J96*12</f>
         <v>36</v>
       </c>
-      <c r="L96" s="146">
+      <c r="L96" s="140">
         <f>36*J96</f>
         <v>108</v>
       </c>
-      <c r="M96" s="146">
+      <c r="M96" s="140">
         <f>SUM(K96:L96)</f>
         <v>144</v>
       </c>
-      <c r="N96" s="164" t="s">
+      <c r="N96" s="137" t="s">
         <v>294</v>
       </c>
-      <c r="O96" s="164" t="s">
+      <c r="O96" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P96" s="164" t="s">
+      <c r="P96" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q96" s="164" t="s">
+      <c r="Q96" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R96" s="24"/>
     </row>
-    <row r="97" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="str">
         <f>_xlfn.XLOOKUP(B97,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13552,24 +13556,24 @@
       <c r="B97" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="137"/>
-      <c r="D97" s="137"/>
-      <c r="E97" s="165"/>
-      <c r="F97" s="137"/>
-      <c r="G97" s="137"/>
-      <c r="H97" s="137"/>
-      <c r="I97" s="137"/>
-      <c r="J97" s="137"/>
-      <c r="K97" s="137"/>
-      <c r="L97" s="137"/>
-      <c r="M97" s="137"/>
-      <c r="N97" s="165"/>
-      <c r="O97" s="165"/>
-      <c r="P97" s="165"/>
-      <c r="Q97" s="165"/>
+      <c r="C97" s="141"/>
+      <c r="D97" s="141"/>
+      <c r="E97" s="138"/>
+      <c r="F97" s="141"/>
+      <c r="G97" s="141"/>
+      <c r="H97" s="141"/>
+      <c r="I97" s="141"/>
+      <c r="J97" s="141"/>
+      <c r="K97" s="141"/>
+      <c r="L97" s="141"/>
+      <c r="M97" s="141"/>
+      <c r="N97" s="138"/>
+      <c r="O97" s="138"/>
+      <c r="P97" s="138"/>
+      <c r="Q97" s="138"/>
       <c r="R97" s="24"/>
     </row>
-    <row r="98" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="97" t="str">
         <f>_xlfn.XLOOKUP(B98,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13577,21 +13581,21 @@
       <c r="B98" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C98" s="162"/>
-      <c r="D98" s="162"/>
-      <c r="E98" s="166"/>
-      <c r="F98" s="162"/>
-      <c r="G98" s="162"/>
-      <c r="H98" s="162"/>
-      <c r="I98" s="162"/>
-      <c r="J98" s="162"/>
-      <c r="K98" s="162"/>
-      <c r="L98" s="162"/>
-      <c r="M98" s="162"/>
-      <c r="N98" s="166"/>
-      <c r="O98" s="166"/>
-      <c r="P98" s="166"/>
-      <c r="Q98" s="166"/>
+      <c r="C98" s="142"/>
+      <c r="D98" s="142"/>
+      <c r="E98" s="139"/>
+      <c r="F98" s="142"/>
+      <c r="G98" s="142"/>
+      <c r="H98" s="142"/>
+      <c r="I98" s="142"/>
+      <c r="J98" s="142"/>
+      <c r="K98" s="142"/>
+      <c r="L98" s="142"/>
+      <c r="M98" s="142"/>
+      <c r="N98" s="139"/>
+      <c r="O98" s="139"/>
+      <c r="P98" s="139"/>
+      <c r="Q98" s="139"/>
       <c r="R98" s="24">
         <f>SUM(J81:J98)</f>
         <v>18</v>
@@ -13601,7 +13605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="str">
         <f>_xlfn.XLOOKUP(B99,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13609,53 +13613,53 @@
       <c r="B99" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C99" s="146">
+      <c r="C99" s="140">
         <v>7</v>
       </c>
-      <c r="D99" s="146" t="s">
+      <c r="D99" s="140" t="s">
         <v>295</v>
       </c>
-      <c r="E99" s="164" t="s">
+      <c r="E99" s="137" t="s">
         <v>296</v>
       </c>
-      <c r="F99" s="146" t="s">
+      <c r="F99" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G99" s="146"/>
-      <c r="H99" s="146" t="s">
+      <c r="G99" s="140"/>
+      <c r="H99" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I99" s="146"/>
-      <c r="J99" s="146">
+      <c r="I99" s="140"/>
+      <c r="J99" s="140">
         <v>3</v>
       </c>
-      <c r="K99" s="146">
+      <c r="K99" s="140">
         <f>J99*12</f>
         <v>36</v>
       </c>
-      <c r="L99" s="146">
+      <c r="L99" s="140">
         <f>36*J99</f>
         <v>108</v>
       </c>
-      <c r="M99" s="146">
+      <c r="M99" s="140">
         <f>SUM(K99:L99)</f>
         <v>144</v>
       </c>
-      <c r="N99" s="164" t="s">
+      <c r="N99" s="137" t="s">
         <v>297</v>
       </c>
-      <c r="O99" s="164" t="s">
+      <c r="O99" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P99" s="164" t="s">
+      <c r="P99" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q99" s="164" t="s">
+      <c r="Q99" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R99" s="24"/>
     </row>
-    <row r="100" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A100" s="24" t="str">
         <f>_xlfn.XLOOKUP(B100,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13663,24 +13667,24 @@
       <c r="B100" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C100" s="137"/>
-      <c r="D100" s="137"/>
-      <c r="E100" s="165"/>
-      <c r="F100" s="137"/>
-      <c r="G100" s="137"/>
-      <c r="H100" s="137"/>
-      <c r="I100" s="137"/>
-      <c r="J100" s="137"/>
-      <c r="K100" s="137"/>
-      <c r="L100" s="137"/>
-      <c r="M100" s="137"/>
-      <c r="N100" s="165"/>
-      <c r="O100" s="165"/>
-      <c r="P100" s="165"/>
-      <c r="Q100" s="165"/>
+      <c r="C100" s="141"/>
+      <c r="D100" s="141"/>
+      <c r="E100" s="138"/>
+      <c r="F100" s="141"/>
+      <c r="G100" s="141"/>
+      <c r="H100" s="141"/>
+      <c r="I100" s="141"/>
+      <c r="J100" s="141"/>
+      <c r="K100" s="141"/>
+      <c r="L100" s="141"/>
+      <c r="M100" s="141"/>
+      <c r="N100" s="138"/>
+      <c r="O100" s="138"/>
+      <c r="P100" s="138"/>
+      <c r="Q100" s="138"/>
       <c r="R100" s="24"/>
     </row>
-    <row r="101" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A101" s="97" t="str">
         <f>_xlfn.XLOOKUP(B101,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13688,24 +13692,24 @@
       <c r="B101" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C101" s="162"/>
-      <c r="D101" s="162"/>
-      <c r="E101" s="167"/>
-      <c r="F101" s="162"/>
-      <c r="G101" s="162"/>
-      <c r="H101" s="162"/>
-      <c r="I101" s="162"/>
-      <c r="J101" s="162"/>
-      <c r="K101" s="162"/>
-      <c r="L101" s="162"/>
-      <c r="M101" s="162"/>
-      <c r="N101" s="166"/>
-      <c r="O101" s="166"/>
-      <c r="P101" s="166"/>
-      <c r="Q101" s="166"/>
+      <c r="C101" s="142"/>
+      <c r="D101" s="142"/>
+      <c r="E101" s="148"/>
+      <c r="F101" s="142"/>
+      <c r="G101" s="142"/>
+      <c r="H101" s="142"/>
+      <c r="I101" s="142"/>
+      <c r="J101" s="142"/>
+      <c r="K101" s="142"/>
+      <c r="L101" s="142"/>
+      <c r="M101" s="142"/>
+      <c r="N101" s="139"/>
+      <c r="O101" s="139"/>
+      <c r="P101" s="139"/>
+      <c r="Q101" s="139"/>
       <c r="R101" s="24"/>
     </row>
-    <row r="102" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A102" s="24" t="str">
         <f>_xlfn.XLOOKUP(B102,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13713,53 +13717,53 @@
       <c r="B102" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C102" s="146">
+      <c r="C102" s="140">
         <v>7</v>
       </c>
-      <c r="D102" s="146" t="s">
+      <c r="D102" s="140" t="s">
         <v>298</v>
       </c>
-      <c r="E102" s="159" t="s">
+      <c r="E102" s="145" t="s">
         <v>299</v>
       </c>
-      <c r="F102" s="146" t="s">
+      <c r="F102" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G102" s="146"/>
-      <c r="H102" s="146" t="s">
+      <c r="G102" s="140"/>
+      <c r="H102" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I102" s="146"/>
-      <c r="J102" s="146">
+      <c r="I102" s="140"/>
+      <c r="J102" s="140">
         <v>3</v>
       </c>
-      <c r="K102" s="146">
+      <c r="K102" s="140">
         <f>J102*12</f>
         <v>36</v>
       </c>
-      <c r="L102" s="146">
+      <c r="L102" s="140">
         <f>36*J102</f>
         <v>108</v>
       </c>
-      <c r="M102" s="146">
+      <c r="M102" s="140">
         <f>SUM(K102:L102)</f>
         <v>144</v>
       </c>
-      <c r="N102" s="164" t="s">
+      <c r="N102" s="137" t="s">
         <v>300</v>
       </c>
-      <c r="O102" s="164" t="s">
+      <c r="O102" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P102" s="164" t="s">
+      <c r="P102" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q102" s="164" t="s">
+      <c r="Q102" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R102" s="24"/>
     </row>
-    <row r="103" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="str">
         <f>_xlfn.XLOOKUP(B103,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13767,24 +13771,24 @@
       <c r="B103" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C103" s="137"/>
-      <c r="D103" s="137"/>
-      <c r="E103" s="159"/>
-      <c r="F103" s="137"/>
-      <c r="G103" s="137"/>
-      <c r="H103" s="137"/>
-      <c r="I103" s="137"/>
-      <c r="J103" s="137"/>
-      <c r="K103" s="137"/>
-      <c r="L103" s="137"/>
-      <c r="M103" s="137"/>
-      <c r="N103" s="165"/>
-      <c r="O103" s="165"/>
-      <c r="P103" s="165"/>
-      <c r="Q103" s="165"/>
+      <c r="C103" s="141"/>
+      <c r="D103" s="141"/>
+      <c r="E103" s="145"/>
+      <c r="F103" s="141"/>
+      <c r="G103" s="141"/>
+      <c r="H103" s="141"/>
+      <c r="I103" s="141"/>
+      <c r="J103" s="141"/>
+      <c r="K103" s="141"/>
+      <c r="L103" s="141"/>
+      <c r="M103" s="141"/>
+      <c r="N103" s="138"/>
+      <c r="O103" s="138"/>
+      <c r="P103" s="138"/>
+      <c r="Q103" s="138"/>
       <c r="R103" s="24"/>
     </row>
-    <row r="104" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="97" t="str">
         <f>_xlfn.XLOOKUP(B104,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13792,24 +13796,24 @@
       <c r="B104" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C104" s="162"/>
-      <c r="D104" s="162"/>
-      <c r="E104" s="160"/>
-      <c r="F104" s="162"/>
-      <c r="G104" s="162"/>
-      <c r="H104" s="162"/>
-      <c r="I104" s="162"/>
-      <c r="J104" s="162"/>
-      <c r="K104" s="162"/>
-      <c r="L104" s="162"/>
-      <c r="M104" s="162"/>
-      <c r="N104" s="166"/>
-      <c r="O104" s="166"/>
-      <c r="P104" s="166"/>
-      <c r="Q104" s="166"/>
+      <c r="C104" s="142"/>
+      <c r="D104" s="142"/>
+      <c r="E104" s="147"/>
+      <c r="F104" s="142"/>
+      <c r="G104" s="142"/>
+      <c r="H104" s="142"/>
+      <c r="I104" s="142"/>
+      <c r="J104" s="142"/>
+      <c r="K104" s="142"/>
+      <c r="L104" s="142"/>
+      <c r="M104" s="142"/>
+      <c r="N104" s="139"/>
+      <c r="O104" s="139"/>
+      <c r="P104" s="139"/>
+      <c r="Q104" s="139"/>
       <c r="R104" s="24"/>
     </row>
-    <row r="105" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A105" s="24" t="str">
         <f>_xlfn.XLOOKUP(B105,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13817,53 +13821,53 @@
       <c r="B105" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C105" s="146">
+      <c r="C105" s="140">
         <v>7</v>
       </c>
-      <c r="D105" s="146" t="s">
+      <c r="D105" s="140" t="s">
         <v>301</v>
       </c>
-      <c r="E105" s="168" t="s">
+      <c r="E105" s="144" t="s">
         <v>302</v>
       </c>
-      <c r="F105" s="146" t="s">
+      <c r="F105" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G105" s="146"/>
-      <c r="H105" s="146" t="s">
+      <c r="G105" s="140"/>
+      <c r="H105" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I105" s="146"/>
-      <c r="J105" s="146">
+      <c r="I105" s="140"/>
+      <c r="J105" s="140">
         <v>3</v>
       </c>
-      <c r="K105" s="146">
+      <c r="K105" s="140">
         <f>J105*12</f>
         <v>36</v>
       </c>
-      <c r="L105" s="146">
+      <c r="L105" s="140">
         <f>36*J105</f>
         <v>108</v>
       </c>
-      <c r="M105" s="146">
+      <c r="M105" s="140">
         <f>SUM(K105:L105)</f>
         <v>144</v>
       </c>
-      <c r="N105" s="164" t="s">
+      <c r="N105" s="137" t="s">
         <v>303</v>
       </c>
-      <c r="O105" s="164" t="s">
+      <c r="O105" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P105" s="164" t="s">
+      <c r="P105" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q105" s="164" t="s">
+      <c r="Q105" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R105" s="24"/>
     </row>
-    <row r="106" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A106" s="24" t="str">
         <f>_xlfn.XLOOKUP(B106,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13871,24 +13875,24 @@
       <c r="B106" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C106" s="137"/>
-      <c r="D106" s="137"/>
-      <c r="E106" s="159"/>
-      <c r="F106" s="137"/>
-      <c r="G106" s="137"/>
-      <c r="H106" s="137"/>
-      <c r="I106" s="137"/>
-      <c r="J106" s="137"/>
-      <c r="K106" s="137"/>
-      <c r="L106" s="137"/>
-      <c r="M106" s="137"/>
-      <c r="N106" s="165"/>
-      <c r="O106" s="165"/>
-      <c r="P106" s="165"/>
-      <c r="Q106" s="165"/>
+      <c r="C106" s="141"/>
+      <c r="D106" s="141"/>
+      <c r="E106" s="145"/>
+      <c r="F106" s="141"/>
+      <c r="G106" s="141"/>
+      <c r="H106" s="141"/>
+      <c r="I106" s="141"/>
+      <c r="J106" s="141"/>
+      <c r="K106" s="141"/>
+      <c r="L106" s="141"/>
+      <c r="M106" s="141"/>
+      <c r="N106" s="138"/>
+      <c r="O106" s="138"/>
+      <c r="P106" s="138"/>
+      <c r="Q106" s="138"/>
       <c r="R106" s="24"/>
     </row>
-    <row r="107" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A107" s="127" t="str">
         <f>_xlfn.XLOOKUP(B107,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13896,24 +13900,24 @@
       <c r="B107" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C107" s="162"/>
-      <c r="D107" s="162"/>
-      <c r="E107" s="172"/>
-      <c r="F107" s="162"/>
-      <c r="G107" s="162"/>
-      <c r="H107" s="162"/>
-      <c r="I107" s="162"/>
-      <c r="J107" s="162"/>
-      <c r="K107" s="162"/>
-      <c r="L107" s="162"/>
-      <c r="M107" s="162"/>
-      <c r="N107" s="166"/>
-      <c r="O107" s="166"/>
-      <c r="P107" s="166"/>
-      <c r="Q107" s="166"/>
+      <c r="C107" s="142"/>
+      <c r="D107" s="142"/>
+      <c r="E107" s="146"/>
+      <c r="F107" s="142"/>
+      <c r="G107" s="142"/>
+      <c r="H107" s="142"/>
+      <c r="I107" s="142"/>
+      <c r="J107" s="142"/>
+      <c r="K107" s="142"/>
+      <c r="L107" s="142"/>
+      <c r="M107" s="142"/>
+      <c r="N107" s="139"/>
+      <c r="O107" s="139"/>
+      <c r="P107" s="139"/>
+      <c r="Q107" s="139"/>
       <c r="R107" s="24"/>
     </row>
-    <row r="108" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A108" s="24" t="str">
         <f>_xlfn.XLOOKUP(B108,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13921,53 +13925,53 @@
       <c r="B108" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C108" s="146">
+      <c r="C108" s="140">
         <v>7</v>
       </c>
-      <c r="D108" s="146" t="s">
+      <c r="D108" s="140" t="s">
         <v>304</v>
       </c>
-      <c r="E108" s="165" t="s">
+      <c r="E108" s="138" t="s">
         <v>305</v>
       </c>
-      <c r="F108" s="146" t="s">
+      <c r="F108" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G108" s="146"/>
-      <c r="H108" s="146" t="s">
+      <c r="G108" s="140"/>
+      <c r="H108" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I108" s="146"/>
-      <c r="J108" s="146">
+      <c r="I108" s="140"/>
+      <c r="J108" s="140">
         <v>3</v>
       </c>
-      <c r="K108" s="146">
+      <c r="K108" s="140">
         <f>J108*12</f>
         <v>36</v>
       </c>
-      <c r="L108" s="146">
+      <c r="L108" s="140">
         <f>36*J108</f>
         <v>108</v>
       </c>
-      <c r="M108" s="146">
+      <c r="M108" s="140">
         <f>SUM(K108:L108)</f>
         <v>144</v>
       </c>
-      <c r="N108" s="164" t="s">
+      <c r="N108" s="137" t="s">
         <v>306</v>
       </c>
-      <c r="O108" s="164" t="s">
+      <c r="O108" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P108" s="164" t="s">
+      <c r="P108" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q108" s="164" t="s">
+      <c r="Q108" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R108" s="24"/>
     </row>
-    <row r="109" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A109" s="24" t="str">
         <f>_xlfn.XLOOKUP(B109,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13975,24 +13979,24 @@
       <c r="B109" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="137"/>
-      <c r="D109" s="137"/>
-      <c r="E109" s="165"/>
-      <c r="F109" s="137"/>
-      <c r="G109" s="137"/>
-      <c r="H109" s="137"/>
-      <c r="I109" s="137"/>
-      <c r="J109" s="137"/>
-      <c r="K109" s="137"/>
-      <c r="L109" s="137"/>
-      <c r="M109" s="137"/>
-      <c r="N109" s="165"/>
-      <c r="O109" s="165"/>
-      <c r="P109" s="165"/>
-      <c r="Q109" s="165"/>
+      <c r="C109" s="141"/>
+      <c r="D109" s="141"/>
+      <c r="E109" s="138"/>
+      <c r="F109" s="141"/>
+      <c r="G109" s="141"/>
+      <c r="H109" s="141"/>
+      <c r="I109" s="141"/>
+      <c r="J109" s="141"/>
+      <c r="K109" s="141"/>
+      <c r="L109" s="141"/>
+      <c r="M109" s="141"/>
+      <c r="N109" s="138"/>
+      <c r="O109" s="138"/>
+      <c r="P109" s="138"/>
+      <c r="Q109" s="138"/>
       <c r="R109" s="24"/>
     </row>
-    <row r="110" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A110" s="97" t="str">
         <f>_xlfn.XLOOKUP(B110,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14000,24 +14004,24 @@
       <c r="B110" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C110" s="162"/>
-      <c r="D110" s="162"/>
-      <c r="E110" s="166"/>
-      <c r="F110" s="162"/>
-      <c r="G110" s="162"/>
-      <c r="H110" s="162"/>
-      <c r="I110" s="162"/>
-      <c r="J110" s="162"/>
-      <c r="K110" s="162"/>
-      <c r="L110" s="162"/>
-      <c r="M110" s="147"/>
-      <c r="N110" s="167"/>
-      <c r="O110" s="166"/>
-      <c r="P110" s="166"/>
-      <c r="Q110" s="166"/>
+      <c r="C110" s="142"/>
+      <c r="D110" s="142"/>
+      <c r="E110" s="139"/>
+      <c r="F110" s="142"/>
+      <c r="G110" s="142"/>
+      <c r="H110" s="142"/>
+      <c r="I110" s="142"/>
+      <c r="J110" s="142"/>
+      <c r="K110" s="142"/>
+      <c r="L110" s="142"/>
+      <c r="M110" s="143"/>
+      <c r="N110" s="148"/>
+      <c r="O110" s="139"/>
+      <c r="P110" s="139"/>
+      <c r="Q110" s="139"/>
       <c r="R110" s="24"/>
     </row>
-    <row r="111" spans="1:19" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A111" s="94"/>
       <c r="B111" s="82"/>
       <c r="C111" s="83">
@@ -14054,7 +14058,7 @@
       <c r="Q111" s="88"/>
       <c r="R111" s="24"/>
     </row>
-    <row r="112" spans="1:19" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A112" s="94"/>
       <c r="B112" s="82"/>
       <c r="C112" s="83">
@@ -14098,7 +14102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A113" s="24" t="str">
         <f>_xlfn.XLOOKUP(B113,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -14106,53 +14110,53 @@
       <c r="B113" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C113" s="146">
+      <c r="C113" s="140">
         <v>8</v>
       </c>
-      <c r="D113" s="146" t="s">
+      <c r="D113" s="140" t="s">
         <v>309</v>
       </c>
-      <c r="E113" s="164" t="s">
+      <c r="E113" s="137" t="s">
         <v>310</v>
       </c>
-      <c r="F113" s="146" t="s">
+      <c r="F113" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G113" s="146"/>
-      <c r="H113" s="146" t="s">
+      <c r="G113" s="140"/>
+      <c r="H113" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I113" s="146"/>
-      <c r="J113" s="146">
+      <c r="I113" s="140"/>
+      <c r="J113" s="140">
         <v>3</v>
       </c>
-      <c r="K113" s="146">
+      <c r="K113" s="140">
         <f>J113*12</f>
         <v>36</v>
       </c>
-      <c r="L113" s="146">
+      <c r="L113" s="140">
         <f>36*J113</f>
         <v>108</v>
       </c>
-      <c r="M113" s="146">
+      <c r="M113" s="140">
         <f>SUM(K113:L113)</f>
         <v>144</v>
       </c>
-      <c r="N113" s="164" t="s">
+      <c r="N113" s="137" t="s">
         <v>311</v>
       </c>
-      <c r="O113" s="164" t="s">
+      <c r="O113" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P113" s="164" t="s">
+      <c r="P113" s="137" t="s">
         <v>194</v>
       </c>
-      <c r="Q113" s="164" t="s">
+      <c r="Q113" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R113" s="24"/>
     </row>
-    <row r="114" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A114" s="24" t="str">
         <f>_xlfn.XLOOKUP(B114,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14160,24 +14164,24 @@
       <c r="B114" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C114" s="137"/>
-      <c r="D114" s="137"/>
-      <c r="E114" s="165"/>
-      <c r="F114" s="137"/>
-      <c r="G114" s="137"/>
-      <c r="H114" s="137"/>
-      <c r="I114" s="137"/>
-      <c r="J114" s="137"/>
-      <c r="K114" s="137"/>
-      <c r="L114" s="137"/>
-      <c r="M114" s="137"/>
-      <c r="N114" s="165"/>
-      <c r="O114" s="165"/>
-      <c r="P114" s="165"/>
-      <c r="Q114" s="165"/>
+      <c r="C114" s="141"/>
+      <c r="D114" s="141"/>
+      <c r="E114" s="138"/>
+      <c r="F114" s="141"/>
+      <c r="G114" s="141"/>
+      <c r="H114" s="141"/>
+      <c r="I114" s="141"/>
+      <c r="J114" s="141"/>
+      <c r="K114" s="141"/>
+      <c r="L114" s="141"/>
+      <c r="M114" s="141"/>
+      <c r="N114" s="138"/>
+      <c r="O114" s="138"/>
+      <c r="P114" s="138"/>
+      <c r="Q114" s="138"/>
       <c r="R114" s="24"/>
     </row>
-    <row r="115" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="97" t="str">
         <f>_xlfn.XLOOKUP(B115,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14185,24 +14189,24 @@
       <c r="B115" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C115" s="162"/>
-      <c r="D115" s="162"/>
-      <c r="E115" s="166"/>
-      <c r="F115" s="162"/>
-      <c r="G115" s="162"/>
-      <c r="H115" s="162"/>
-      <c r="I115" s="162"/>
-      <c r="J115" s="162"/>
-      <c r="K115" s="162"/>
-      <c r="L115" s="162"/>
-      <c r="M115" s="162"/>
-      <c r="N115" s="166"/>
-      <c r="O115" s="166"/>
-      <c r="P115" s="166"/>
-      <c r="Q115" s="166"/>
+      <c r="C115" s="142"/>
+      <c r="D115" s="142"/>
+      <c r="E115" s="139"/>
+      <c r="F115" s="142"/>
+      <c r="G115" s="142"/>
+      <c r="H115" s="142"/>
+      <c r="I115" s="142"/>
+      <c r="J115" s="142"/>
+      <c r="K115" s="142"/>
+      <c r="L115" s="142"/>
+      <c r="M115" s="142"/>
+      <c r="N115" s="139"/>
+      <c r="O115" s="139"/>
+      <c r="P115" s="139"/>
+      <c r="Q115" s="139"/>
       <c r="R115" s="24"/>
     </row>
-    <row r="116" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A116" s="24" t="str">
         <f>_xlfn.XLOOKUP(B116,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14210,53 +14214,53 @@
       <c r="B116" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C116" s="146">
+      <c r="C116" s="140">
         <v>8</v>
       </c>
-      <c r="D116" s="146" t="s">
+      <c r="D116" s="140" t="s">
         <v>312</v>
       </c>
-      <c r="E116" s="168" t="s">
+      <c r="E116" s="144" t="s">
         <v>313</v>
       </c>
-      <c r="F116" s="146" t="s">
+      <c r="F116" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G116" s="146"/>
-      <c r="H116" s="146" t="s">
+      <c r="G116" s="140"/>
+      <c r="H116" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I116" s="146"/>
-      <c r="J116" s="146">
+      <c r="I116" s="140"/>
+      <c r="J116" s="140">
         <v>6</v>
       </c>
-      <c r="K116" s="146">
+      <c r="K116" s="140">
         <f>J116*12</f>
         <v>72</v>
       </c>
-      <c r="L116" s="146">
+      <c r="L116" s="140">
         <f>36*J116</f>
         <v>216</v>
       </c>
-      <c r="M116" s="146">
+      <c r="M116" s="140">
         <f>SUM(K116:L116)</f>
         <v>288</v>
       </c>
-      <c r="N116" s="164" t="s">
+      <c r="N116" s="137" t="s">
         <v>314</v>
       </c>
-      <c r="O116" s="164" t="s">
+      <c r="O116" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P116" s="164" t="s">
+      <c r="P116" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q116" s="164" t="s">
+      <c r="Q116" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R116" s="24"/>
     </row>
-    <row r="117" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A117" s="24" t="str">
         <f>_xlfn.XLOOKUP(B117,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -14264,24 +14268,24 @@
       <c r="B117" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C117" s="137"/>
-      <c r="D117" s="137"/>
-      <c r="E117" s="159"/>
-      <c r="F117" s="137"/>
-      <c r="G117" s="137"/>
-      <c r="H117" s="137"/>
-      <c r="I117" s="137"/>
-      <c r="J117" s="137"/>
-      <c r="K117" s="137"/>
-      <c r="L117" s="137"/>
-      <c r="M117" s="137"/>
-      <c r="N117" s="165"/>
-      <c r="O117" s="165"/>
-      <c r="P117" s="165"/>
-      <c r="Q117" s="165"/>
+      <c r="C117" s="141"/>
+      <c r="D117" s="141"/>
+      <c r="E117" s="145"/>
+      <c r="F117" s="141"/>
+      <c r="G117" s="141"/>
+      <c r="H117" s="141"/>
+      <c r="I117" s="141"/>
+      <c r="J117" s="141"/>
+      <c r="K117" s="141"/>
+      <c r="L117" s="141"/>
+      <c r="M117" s="141"/>
+      <c r="N117" s="138"/>
+      <c r="O117" s="138"/>
+      <c r="P117" s="138"/>
+      <c r="Q117" s="138"/>
       <c r="R117" s="24"/>
     </row>
-    <row r="118" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A118" s="24" t="str">
         <f>_xlfn.XLOOKUP(B118,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14289,24 +14293,24 @@
       <c r="B118" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C118" s="137"/>
-      <c r="D118" s="137"/>
-      <c r="E118" s="159"/>
-      <c r="F118" s="137"/>
-      <c r="G118" s="137"/>
-      <c r="H118" s="137"/>
-      <c r="I118" s="137"/>
-      <c r="J118" s="137"/>
-      <c r="K118" s="137"/>
-      <c r="L118" s="137"/>
-      <c r="M118" s="137"/>
-      <c r="N118" s="165"/>
-      <c r="O118" s="165"/>
-      <c r="P118" s="165"/>
-      <c r="Q118" s="165"/>
+      <c r="C118" s="141"/>
+      <c r="D118" s="141"/>
+      <c r="E118" s="145"/>
+      <c r="F118" s="141"/>
+      <c r="G118" s="141"/>
+      <c r="H118" s="141"/>
+      <c r="I118" s="141"/>
+      <c r="J118" s="141"/>
+      <c r="K118" s="141"/>
+      <c r="L118" s="141"/>
+      <c r="M118" s="141"/>
+      <c r="N118" s="138"/>
+      <c r="O118" s="138"/>
+      <c r="P118" s="138"/>
+      <c r="Q118" s="138"/>
       <c r="R118" s="24"/>
     </row>
-    <row r="119" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="97" t="str">
         <f>_xlfn.XLOOKUP(B119,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14314,24 +14318,24 @@
       <c r="B119" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C119" s="162"/>
-      <c r="D119" s="147"/>
-      <c r="E119" s="172"/>
-      <c r="F119" s="162"/>
-      <c r="G119" s="162"/>
-      <c r="H119" s="162"/>
-      <c r="I119" s="162"/>
-      <c r="J119" s="162"/>
-      <c r="K119" s="162"/>
-      <c r="L119" s="162"/>
-      <c r="M119" s="162"/>
-      <c r="N119" s="166"/>
-      <c r="O119" s="166"/>
-      <c r="P119" s="166"/>
-      <c r="Q119" s="166"/>
+      <c r="C119" s="142"/>
+      <c r="D119" s="143"/>
+      <c r="E119" s="146"/>
+      <c r="F119" s="142"/>
+      <c r="G119" s="142"/>
+      <c r="H119" s="142"/>
+      <c r="I119" s="142"/>
+      <c r="J119" s="142"/>
+      <c r="K119" s="142"/>
+      <c r="L119" s="142"/>
+      <c r="M119" s="142"/>
+      <c r="N119" s="139"/>
+      <c r="O119" s="139"/>
+      <c r="P119" s="139"/>
+      <c r="Q119" s="139"/>
       <c r="R119" s="24"/>
     </row>
-    <row r="120" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A120" s="24" t="str">
         <f>_xlfn.XLOOKUP(B120,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14339,53 +14343,53 @@
       <c r="B120" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C120" s="146">
+      <c r="C120" s="140">
         <v>8</v>
       </c>
-      <c r="D120" s="137" t="s">
+      <c r="D120" s="141" t="s">
         <v>315</v>
       </c>
-      <c r="E120" s="159" t="s">
+      <c r="E120" s="145" t="s">
         <v>316</v>
       </c>
-      <c r="F120" s="146" t="s">
+      <c r="F120" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G120" s="146"/>
-      <c r="H120" s="146" t="s">
+      <c r="G120" s="140"/>
+      <c r="H120" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="I120" s="146"/>
-      <c r="J120" s="146">
+      <c r="I120" s="140"/>
+      <c r="J120" s="140">
         <v>3</v>
       </c>
-      <c r="K120" s="146">
+      <c r="K120" s="140">
         <f>J120*12</f>
         <v>36</v>
       </c>
-      <c r="L120" s="146">
+      <c r="L120" s="140">
         <f>36*J120</f>
         <v>108</v>
       </c>
-      <c r="M120" s="146">
+      <c r="M120" s="140">
         <f>SUM(K120:L120)</f>
         <v>144</v>
       </c>
-      <c r="N120" s="164" t="s">
+      <c r="N120" s="137" t="s">
         <v>317</v>
       </c>
-      <c r="O120" s="164" t="s">
+      <c r="O120" s="137" t="s">
         <v>179</v>
       </c>
-      <c r="P120" s="164" t="s">
+      <c r="P120" s="137" t="s">
         <v>201</v>
       </c>
-      <c r="Q120" s="164" t="s">
+      <c r="Q120" s="137" t="s">
         <v>185</v>
       </c>
       <c r="R120" s="24"/>
     </row>
-    <row r="121" spans="1:19" s="50" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="str">
         <f>_xlfn.XLOOKUP(B121,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14393,24 +14397,24 @@
       <c r="B121" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C121" s="137"/>
-      <c r="D121" s="137"/>
-      <c r="E121" s="159"/>
-      <c r="F121" s="137"/>
-      <c r="G121" s="137"/>
-      <c r="H121" s="137"/>
-      <c r="I121" s="137"/>
-      <c r="J121" s="137"/>
-      <c r="K121" s="137"/>
-      <c r="L121" s="137"/>
-      <c r="M121" s="137"/>
-      <c r="N121" s="165"/>
-      <c r="O121" s="165"/>
-      <c r="P121" s="165"/>
-      <c r="Q121" s="165"/>
+      <c r="C121" s="141"/>
+      <c r="D121" s="141"/>
+      <c r="E121" s="145"/>
+      <c r="F121" s="141"/>
+      <c r="G121" s="141"/>
+      <c r="H121" s="141"/>
+      <c r="I121" s="141"/>
+      <c r="J121" s="141"/>
+      <c r="K121" s="141"/>
+      <c r="L121" s="141"/>
+      <c r="M121" s="141"/>
+      <c r="N121" s="138"/>
+      <c r="O121" s="138"/>
+      <c r="P121" s="138"/>
+      <c r="Q121" s="138"/>
       <c r="R121" s="24"/>
     </row>
-    <row r="122" spans="1:19" s="50" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:19" s="50" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="97" t="str">
         <f>_xlfn.XLOOKUP(B122,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14418,24 +14422,24 @@
       <c r="B122" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C122" s="162"/>
-      <c r="D122" s="162"/>
-      <c r="E122" s="160"/>
-      <c r="F122" s="162"/>
-      <c r="G122" s="162"/>
-      <c r="H122" s="162"/>
-      <c r="I122" s="162"/>
-      <c r="J122" s="162"/>
-      <c r="K122" s="162"/>
-      <c r="L122" s="162"/>
-      <c r="M122" s="162"/>
-      <c r="N122" s="166"/>
-      <c r="O122" s="166"/>
-      <c r="P122" s="166"/>
-      <c r="Q122" s="166"/>
+      <c r="C122" s="142"/>
+      <c r="D122" s="142"/>
+      <c r="E122" s="147"/>
+      <c r="F122" s="142"/>
+      <c r="G122" s="142"/>
+      <c r="H122" s="142"/>
+      <c r="I122" s="142"/>
+      <c r="J122" s="142"/>
+      <c r="K122" s="142"/>
+      <c r="L122" s="142"/>
+      <c r="M122" s="142"/>
+      <c r="N122" s="139"/>
+      <c r="O122" s="139"/>
+      <c r="P122" s="139"/>
+      <c r="Q122" s="139"/>
       <c r="R122" s="24"/>
     </row>
-    <row r="123" spans="1:19" s="50" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:19" s="50" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="94"/>
       <c r="B123" s="125"/>
       <c r="C123" s="90">
@@ -14472,7 +14476,7 @@
       <c r="Q123" s="93"/>
       <c r="R123" s="24"/>
     </row>
-    <row r="124" spans="1:19" s="50" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:19" s="50" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="94"/>
       <c r="B124" s="126"/>
       <c r="C124" s="83">
@@ -14516,7 +14520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:19" s="50" customFormat="1" ht="32" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19" s="50" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A125" s="24"/>
       <c r="B125" s="124"/>
       <c r="C125" s="101" t="s">
@@ -14553,7 +14557,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="126" spans="1:19" s="50" customFormat="1" ht="48" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19" s="50" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A126" s="24"/>
       <c r="B126" s="16"/>
       <c r="D126" s="19"/>
@@ -14577,7 +14581,7 @@
       <c r="Q126" s="16"/>
       <c r="R126" s="24"/>
     </row>
-    <row r="127" spans="1:19" s="50" customFormat="1" ht="48" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19" s="50" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A127" s="24"/>
       <c r="B127" s="16"/>
       <c r="D127" s="32"/>
@@ -14601,7 +14605,7 @@
       <c r="Q127" s="71"/>
       <c r="R127" s="24"/>
     </row>
-    <row r="128" spans="1:19" s="50" customFormat="1" ht="32" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19" s="50" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A128" s="24"/>
       <c r="B128" s="16"/>
       <c r="D128" s="32"/>
@@ -14625,7 +14629,7 @@
       <c r="Q128" s="71"/>
       <c r="R128" s="24"/>
     </row>
-    <row r="129" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A129" s="24"/>
       <c r="B129" s="16"/>
       <c r="D129" s="32"/>
@@ -14644,7 +14648,7 @@
       <c r="Q129" s="71"/>
       <c r="R129" s="24"/>
     </row>
-    <row r="130" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A130" s="24"/>
       <c r="B130" s="16"/>
       <c r="D130" s="32"/>
@@ -14663,7 +14667,7 @@
       <c r="Q130" s="71"/>
       <c r="R130" s="24"/>
     </row>
-    <row r="131" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A131" s="24"/>
       <c r="B131" s="16"/>
       <c r="D131" s="19"/>
@@ -14682,7 +14686,7 @@
       <c r="Q131" s="16"/>
       <c r="R131" s="24"/>
     </row>
-    <row r="132" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A132" s="24"/>
       <c r="B132" s="16"/>
       <c r="D132" s="19"/>
@@ -14701,7 +14705,7 @@
       <c r="Q132" s="16"/>
       <c r="R132" s="24"/>
     </row>
-    <row r="133" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A133" s="24"/>
       <c r="B133" s="16"/>
       <c r="D133" s="19"/>
@@ -14720,7 +14724,7 @@
       <c r="Q133" s="16"/>
       <c r="R133" s="24"/>
     </row>
-    <row r="134" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A134" s="24"/>
       <c r="B134" s="16"/>
       <c r="D134" s="19"/>
@@ -14739,7 +14743,7 @@
       <c r="Q134" s="16"/>
       <c r="R134" s="24"/>
     </row>
-    <row r="135" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A135" s="24"/>
       <c r="B135" s="16"/>
       <c r="D135" s="19"/>
@@ -14758,7 +14762,7 @@
       <c r="Q135" s="16"/>
       <c r="R135" s="24"/>
     </row>
-    <row r="136" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A136" s="24"/>
       <c r="B136" s="16"/>
       <c r="D136" s="19"/>
@@ -14777,7 +14781,7 @@
       <c r="Q136" s="16"/>
       <c r="R136" s="24"/>
     </row>
-    <row r="137" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A137" s="24"/>
       <c r="B137" s="16"/>
       <c r="D137" s="19"/>
@@ -14796,7 +14800,7 @@
       <c r="Q137" s="16"/>
       <c r="R137" s="24"/>
     </row>
-    <row r="138" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A138" s="24"/>
       <c r="B138" s="16"/>
       <c r="D138" s="19"/>
@@ -14815,7 +14819,7 @@
       <c r="Q138" s="16"/>
       <c r="R138" s="24"/>
     </row>
-    <row r="139" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A139" s="24"/>
       <c r="B139" s="16"/>
       <c r="D139" s="19"/>
@@ -14834,7 +14838,7 @@
       <c r="Q139" s="16"/>
       <c r="R139" s="24"/>
     </row>
-    <row r="140" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A140" s="24"/>
       <c r="B140" s="16"/>
       <c r="D140" s="19"/>
@@ -14853,7 +14857,7 @@
       <c r="Q140" s="16"/>
       <c r="R140" s="24"/>
     </row>
-    <row r="141" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A141" s="24"/>
       <c r="B141" s="22"/>
       <c r="D141" s="19"/>
@@ -14872,7 +14876,7 @@
       <c r="Q141" s="22"/>
       <c r="R141" s="24"/>
     </row>
-    <row r="142" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A142" s="24"/>
       <c r="B142" s="22"/>
       <c r="D142" s="19"/>
@@ -14891,7 +14895,7 @@
       <c r="Q142" s="22"/>
       <c r="R142" s="24"/>
     </row>
-    <row r="143" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A143" s="24"/>
       <c r="B143" s="22"/>
       <c r="D143" s="19"/>
@@ -14910,7 +14914,7 @@
       <c r="Q143" s="22"/>
       <c r="R143" s="24"/>
     </row>
-    <row r="144" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A144" s="24"/>
       <c r="B144" s="22"/>
       <c r="D144" s="19"/>
@@ -14929,7 +14933,7 @@
       <c r="Q144" s="22"/>
       <c r="R144" s="24"/>
     </row>
-    <row r="145" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A145" s="24"/>
       <c r="B145" s="16"/>
       <c r="D145" s="32"/>
@@ -14948,7 +14952,7 @@
       <c r="Q145" s="71"/>
       <c r="R145" s="24"/>
     </row>
-    <row r="146" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A146" s="24"/>
       <c r="B146" s="16"/>
       <c r="D146" s="32"/>
@@ -14967,7 +14971,7 @@
       <c r="Q146" s="71"/>
       <c r="R146" s="24"/>
     </row>
-    <row r="147" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A147" s="24"/>
       <c r="B147" s="16"/>
       <c r="D147" s="32"/>
@@ -14986,7 +14990,7 @@
       <c r="Q147" s="71"/>
       <c r="R147" s="24"/>
     </row>
-    <row r="148" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A148" s="24"/>
       <c r="B148" s="16"/>
       <c r="D148" s="32"/>
@@ -15005,7 +15009,7 @@
       <c r="Q148" s="71"/>
       <c r="R148" s="24"/>
     </row>
-    <row r="149" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A149" s="24"/>
       <c r="B149" s="16"/>
       <c r="D149" s="19"/>
@@ -15019,7 +15023,7 @@
       <c r="Q149" s="16"/>
       <c r="R149" s="24"/>
     </row>
-    <row r="150" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A150" s="24"/>
       <c r="B150" s="16"/>
       <c r="D150" s="19"/>
@@ -15033,7 +15037,7 @@
       <c r="Q150" s="16"/>
       <c r="R150" s="24"/>
     </row>
-    <row r="151" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A151" s="24"/>
       <c r="B151" s="16"/>
       <c r="D151" s="19"/>
@@ -15047,7 +15051,7 @@
       <c r="Q151" s="16"/>
       <c r="R151" s="24"/>
     </row>
-    <row r="152" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A152" s="24"/>
       <c r="B152" s="16"/>
       <c r="D152" s="19"/>
@@ -15061,7 +15065,7 @@
       <c r="Q152" s="16"/>
       <c r="R152" s="24"/>
     </row>
-    <row r="153" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A153" s="24"/>
       <c r="B153" s="16"/>
       <c r="D153" s="19"/>
@@ -15080,7 +15084,7 @@
       <c r="Q153" s="72"/>
       <c r="R153" s="24"/>
     </row>
-    <row r="154" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A154" s="24"/>
       <c r="B154" s="16"/>
       <c r="D154" s="32"/>
@@ -15099,7 +15103,7 @@
       <c r="Q154" s="71"/>
       <c r="R154" s="24"/>
     </row>
-    <row r="155" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A155" s="24"/>
       <c r="B155" s="16"/>
       <c r="D155" s="32"/>
@@ -15118,7 +15122,7 @@
       <c r="Q155" s="71"/>
       <c r="R155" s="24"/>
     </row>
-    <row r="156" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A156" s="24"/>
       <c r="B156" s="16"/>
       <c r="D156" s="32"/>
@@ -15137,7 +15141,7 @@
       <c r="Q156" s="71"/>
       <c r="R156" s="24"/>
     </row>
-    <row r="157" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A157" s="24"/>
       <c r="B157" s="16"/>
       <c r="D157" s="32"/>
@@ -15156,7 +15160,7 @@
       <c r="Q157" s="71"/>
       <c r="R157" s="24"/>
     </row>
-    <row r="158" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A158" s="24"/>
       <c r="B158" s="16"/>
       <c r="D158" s="19"/>
@@ -15175,7 +15179,7 @@
       <c r="Q158" s="71"/>
       <c r="R158" s="24"/>
     </row>
-    <row r="159" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A159" s="24"/>
       <c r="B159" s="16"/>
       <c r="D159" s="19"/>
@@ -15194,7 +15198,7 @@
       <c r="Q159" s="71"/>
       <c r="R159" s="24"/>
     </row>
-    <row r="160" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A160" s="24"/>
       <c r="B160" s="16"/>
       <c r="D160" s="19"/>
@@ -15213,7 +15217,7 @@
       <c r="Q160" s="71"/>
       <c r="R160" s="24"/>
     </row>
-    <row r="161" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A161" s="24"/>
       <c r="B161" s="16"/>
       <c r="D161" s="19"/>
@@ -15232,7 +15236,7 @@
       <c r="Q161" s="71"/>
       <c r="R161" s="24"/>
     </row>
-    <row r="162" spans="1:18" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A162" s="24"/>
       <c r="B162" s="16"/>
       <c r="D162" s="19"/>
@@ -15246,7 +15250,7 @@
       <c r="Q162" s="16"/>
       <c r="R162" s="24"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E163" s="57"/>
       <c r="F163" s="52"/>
       <c r="L163" s="58"/>
@@ -15256,7 +15260,7 @@
       <c r="P163" s="57"/>
       <c r="Q163" s="57"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E164" s="57"/>
       <c r="F164" s="52"/>
       <c r="L164" s="58"/>
@@ -15266,7 +15270,7 @@
       <c r="P164" s="57"/>
       <c r="Q164" s="57"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E165" s="57"/>
       <c r="F165" s="52"/>
       <c r="L165" s="58"/>
@@ -15276,7 +15280,7 @@
       <c r="P165" s="57"/>
       <c r="Q165" s="57"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E166" s="61"/>
       <c r="F166" s="52"/>
       <c r="G166" s="54"/>
@@ -15291,7 +15295,7 @@
       <c r="P166" s="61"/>
       <c r="Q166" s="61"/>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E167" s="62"/>
       <c r="F167" s="52"/>
       <c r="G167" s="63"/>
@@ -15306,7 +15310,7 @@
       <c r="P167" s="62"/>
       <c r="Q167" s="62"/>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E168" s="53"/>
       <c r="F168" s="52"/>
       <c r="G168" s="54"/>
@@ -15321,7 +15325,7 @@
       <c r="P168" s="67"/>
       <c r="Q168" s="67"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E169" s="53"/>
       <c r="F169" s="52"/>
       <c r="G169" s="54"/>
@@ -15336,7 +15340,7 @@
       <c r="P169" s="67"/>
       <c r="Q169" s="67"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E170" s="53"/>
       <c r="F170" s="52"/>
       <c r="G170" s="54"/>
@@ -15351,7 +15355,7 @@
       <c r="P170" s="67"/>
       <c r="Q170" s="67"/>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E171" s="53"/>
       <c r="F171" s="52"/>
       <c r="G171" s="54"/>
@@ -15366,7 +15370,7 @@
       <c r="P171" s="67"/>
       <c r="Q171" s="67"/>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E172" s="57"/>
       <c r="F172" s="52"/>
       <c r="G172" s="58"/>
@@ -15381,7 +15385,7 @@
       <c r="P172" s="57"/>
       <c r="Q172" s="57"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E173" s="57"/>
       <c r="F173" s="52"/>
       <c r="G173" s="58"/>
@@ -15396,7 +15400,7 @@
       <c r="P173" s="57"/>
       <c r="Q173" s="57"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E174" s="57"/>
       <c r="F174" s="52"/>
       <c r="G174" s="58"/>
@@ -15411,7 +15415,7 @@
       <c r="P174" s="57"/>
       <c r="Q174" s="57"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E175" s="57"/>
       <c r="F175" s="52"/>
       <c r="G175" s="58"/>
@@ -15426,7 +15430,7 @@
       <c r="P175" s="57"/>
       <c r="Q175" s="57"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E176" s="57"/>
       <c r="F176" s="52"/>
       <c r="I176" s="52"/>
@@ -15435,7 +15439,7 @@
       <c r="P176" s="57"/>
       <c r="Q176" s="57"/>
     </row>
-    <row r="177" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E177" s="57"/>
       <c r="F177" s="52"/>
       <c r="I177" s="52"/>
@@ -15444,7 +15448,7 @@
       <c r="P177" s="57"/>
       <c r="Q177" s="57"/>
     </row>
-    <row r="178" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="178" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E178" s="57"/>
       <c r="F178" s="52"/>
       <c r="I178" s="52"/>
@@ -15453,7 +15457,7 @@
       <c r="P178" s="57"/>
       <c r="Q178" s="57"/>
     </row>
-    <row r="179" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E179" s="57"/>
       <c r="F179" s="52"/>
       <c r="I179" s="52"/>
@@ -15462,7 +15466,7 @@
       <c r="P179" s="57"/>
       <c r="Q179" s="57"/>
     </row>
-    <row r="180" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E180" s="64"/>
       <c r="F180" s="52"/>
       <c r="G180" s="54"/>
@@ -15477,7 +15481,7 @@
       <c r="P180" s="56"/>
       <c r="Q180" s="56"/>
     </row>
-    <row r="181" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E181" s="64"/>
       <c r="F181" s="52"/>
       <c r="G181" s="54"/>
@@ -15492,7 +15496,7 @@
       <c r="P181" s="56"/>
       <c r="Q181" s="56"/>
     </row>
-    <row r="182" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="182" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E182" s="64"/>
       <c r="F182" s="52"/>
       <c r="G182" s="54"/>
@@ -15507,7 +15511,7 @@
       <c r="P182" s="56"/>
       <c r="Q182" s="56"/>
     </row>
-    <row r="183" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E183" s="53"/>
       <c r="F183" s="52"/>
       <c r="G183" s="54"/>
@@ -15522,7 +15526,7 @@
       <c r="P183" s="67"/>
       <c r="Q183" s="67"/>
     </row>
-    <row r="184" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E184" s="53"/>
       <c r="F184" s="52"/>
       <c r="G184" s="54"/>
@@ -15537,7 +15541,7 @@
       <c r="P184" s="67"/>
       <c r="Q184" s="67"/>
     </row>
-    <row r="185" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E185" s="53"/>
       <c r="F185" s="52"/>
       <c r="G185" s="54"/>
@@ -15552,7 +15556,7 @@
       <c r="P185" s="67"/>
       <c r="Q185" s="67"/>
     </row>
-    <row r="186" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E186" s="53"/>
       <c r="F186" s="52"/>
       <c r="G186" s="54"/>
@@ -15567,7 +15571,7 @@
       <c r="P186" s="67"/>
       <c r="Q186" s="67"/>
     </row>
-    <row r="187" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="187" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E187" s="53"/>
       <c r="F187" s="52"/>
       <c r="G187" s="54"/>
@@ -15582,7 +15586,7 @@
       <c r="P187" s="67"/>
       <c r="Q187" s="67"/>
     </row>
-    <row r="188" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="188" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E188" s="53"/>
       <c r="F188" s="52"/>
       <c r="G188" s="54"/>
@@ -15597,7 +15601,7 @@
       <c r="P188" s="67"/>
       <c r="Q188" s="67"/>
     </row>
-    <row r="189" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="189" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E189" s="53"/>
       <c r="F189" s="52"/>
       <c r="G189" s="54"/>
@@ -15612,7 +15616,7 @@
       <c r="P189" s="67"/>
       <c r="Q189" s="67"/>
     </row>
-    <row r="190" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="190" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E190" s="53"/>
       <c r="F190" s="52"/>
       <c r="G190" s="54"/>
@@ -15627,7 +15631,7 @@
       <c r="P190" s="67"/>
       <c r="Q190" s="67"/>
     </row>
-    <row r="191" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="191" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E191" s="53"/>
       <c r="F191" s="52"/>
       <c r="G191" s="54"/>
@@ -15642,7 +15646,7 @@
       <c r="P191" s="67"/>
       <c r="Q191" s="67"/>
     </row>
-    <row r="192" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="192" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E192" s="53"/>
       <c r="F192" s="52"/>
       <c r="G192" s="54"/>
@@ -15657,7 +15661,7 @@
       <c r="P192" s="67"/>
       <c r="Q192" s="67"/>
     </row>
-    <row r="193" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="193" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E193" s="53"/>
       <c r="F193" s="52"/>
       <c r="G193" s="54"/>
@@ -15672,7 +15676,7 @@
       <c r="P193" s="67"/>
       <c r="Q193" s="67"/>
     </row>
-    <row r="194" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="194" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E194" s="53"/>
       <c r="F194" s="52"/>
       <c r="G194" s="54"/>
@@ -15687,7 +15691,7 @@
       <c r="P194" s="67"/>
       <c r="Q194" s="67"/>
     </row>
-    <row r="195" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="195" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E195" s="53"/>
       <c r="F195" s="52"/>
       <c r="G195" s="54"/>
@@ -15702,7 +15706,7 @@
       <c r="P195" s="67"/>
       <c r="Q195" s="67"/>
     </row>
-    <row r="196" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="196" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E196" s="53"/>
       <c r="F196" s="52"/>
       <c r="G196" s="54"/>
@@ -15717,7 +15721,7 @@
       <c r="P196" s="67"/>
       <c r="Q196" s="67"/>
     </row>
-    <row r="197" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="197" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E197" s="53"/>
       <c r="F197" s="52"/>
       <c r="G197" s="54"/>
@@ -15732,7 +15736,7 @@
       <c r="P197" s="67"/>
       <c r="Q197" s="67"/>
     </row>
-    <row r="198" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="198" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E198" s="53"/>
       <c r="F198" s="52"/>
       <c r="G198" s="54"/>
@@ -15747,7 +15751,7 @@
       <c r="P198" s="67"/>
       <c r="Q198" s="67"/>
     </row>
-    <row r="199" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="199" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D199" s="59"/>
       <c r="E199" s="53"/>
       <c r="F199" s="59"/>
@@ -15763,7 +15767,7 @@
       <c r="P199" s="67"/>
       <c r="Q199" s="67"/>
     </row>
-    <row r="200" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="200" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D200" s="59"/>
       <c r="E200" s="53"/>
       <c r="F200" s="59"/>
@@ -15779,7 +15783,7 @@
       <c r="P200" s="67"/>
       <c r="Q200" s="67"/>
     </row>
-    <row r="201" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="201" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D201" s="59"/>
       <c r="E201" s="53"/>
       <c r="F201" s="59"/>
@@ -15795,7 +15799,7 @@
       <c r="P201" s="67"/>
       <c r="Q201" s="67"/>
     </row>
-    <row r="202" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="202" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D202" s="59"/>
       <c r="E202" s="53"/>
       <c r="F202" s="59"/>
@@ -15817,342 +15821,202 @@
     <filterColumn colId="7" showButton="0"/>
   </autoFilter>
   <mergeCells count="556">
-    <mergeCell ref="Q105:Q107"/>
-    <mergeCell ref="H105:H107"/>
-    <mergeCell ref="I105:I107"/>
-    <mergeCell ref="J105:J107"/>
-    <mergeCell ref="K105:K107"/>
-    <mergeCell ref="L105:L107"/>
-    <mergeCell ref="M105:M107"/>
-    <mergeCell ref="N105:N107"/>
-    <mergeCell ref="O105:O107"/>
-    <mergeCell ref="P105:P107"/>
-    <mergeCell ref="M120:M122"/>
-    <mergeCell ref="N120:N122"/>
-    <mergeCell ref="O120:O122"/>
-    <mergeCell ref="P120:P122"/>
-    <mergeCell ref="Q120:Q122"/>
-    <mergeCell ref="H120:H122"/>
-    <mergeCell ref="I120:I122"/>
-    <mergeCell ref="J120:J122"/>
-    <mergeCell ref="K120:K122"/>
-    <mergeCell ref="L120:L122"/>
-    <mergeCell ref="C116:C119"/>
-    <mergeCell ref="D116:D119"/>
-    <mergeCell ref="E116:E119"/>
-    <mergeCell ref="F116:F119"/>
-    <mergeCell ref="G116:G119"/>
-    <mergeCell ref="C120:C122"/>
-    <mergeCell ref="D120:D122"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="F120:F122"/>
-    <mergeCell ref="G120:G122"/>
-    <mergeCell ref="Q113:Q115"/>
-    <mergeCell ref="H113:H115"/>
-    <mergeCell ref="I113:I115"/>
-    <mergeCell ref="J113:J115"/>
-    <mergeCell ref="K113:K115"/>
-    <mergeCell ref="L113:L115"/>
-    <mergeCell ref="Q116:Q119"/>
-    <mergeCell ref="H116:H119"/>
-    <mergeCell ref="I116:I119"/>
-    <mergeCell ref="J116:J119"/>
-    <mergeCell ref="K116:K119"/>
-    <mergeCell ref="L116:L119"/>
-    <mergeCell ref="M116:M119"/>
-    <mergeCell ref="N116:N119"/>
-    <mergeCell ref="O116:O119"/>
-    <mergeCell ref="P116:P119"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="D113:D115"/>
-    <mergeCell ref="E113:E115"/>
-    <mergeCell ref="F113:F115"/>
-    <mergeCell ref="G113:G115"/>
-    <mergeCell ref="M113:M115"/>
-    <mergeCell ref="N113:N115"/>
-    <mergeCell ref="O113:O115"/>
-    <mergeCell ref="P113:P115"/>
-    <mergeCell ref="M108:M110"/>
-    <mergeCell ref="N108:N110"/>
-    <mergeCell ref="O108:O110"/>
-    <mergeCell ref="P108:P110"/>
-    <mergeCell ref="Q108:Q110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="I108:I110"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="K108:K110"/>
-    <mergeCell ref="L108:L110"/>
-    <mergeCell ref="C102:C104"/>
-    <mergeCell ref="D102:D104"/>
-    <mergeCell ref="E102:E104"/>
-    <mergeCell ref="F102:F104"/>
-    <mergeCell ref="G102:G104"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="C105:C107"/>
-    <mergeCell ref="D105:D107"/>
-    <mergeCell ref="E105:E107"/>
-    <mergeCell ref="F105:F107"/>
-    <mergeCell ref="G105:G107"/>
-    <mergeCell ref="Q99:Q101"/>
-    <mergeCell ref="H99:H101"/>
-    <mergeCell ref="I99:I101"/>
-    <mergeCell ref="J99:J101"/>
-    <mergeCell ref="K99:K101"/>
-    <mergeCell ref="L99:L101"/>
-    <mergeCell ref="Q102:Q104"/>
-    <mergeCell ref="H102:H104"/>
-    <mergeCell ref="I102:I104"/>
-    <mergeCell ref="J102:J104"/>
-    <mergeCell ref="K102:K104"/>
-    <mergeCell ref="L102:L104"/>
-    <mergeCell ref="M102:M104"/>
-    <mergeCell ref="N102:N104"/>
-    <mergeCell ref="O102:O104"/>
-    <mergeCell ref="P102:P104"/>
-    <mergeCell ref="C99:C101"/>
-    <mergeCell ref="D99:D101"/>
-    <mergeCell ref="E99:E101"/>
-    <mergeCell ref="F99:F101"/>
-    <mergeCell ref="G99:G101"/>
-    <mergeCell ref="M96:M98"/>
-    <mergeCell ref="N96:N98"/>
-    <mergeCell ref="O96:O98"/>
-    <mergeCell ref="P96:P98"/>
-    <mergeCell ref="M99:M101"/>
-    <mergeCell ref="N99:N101"/>
-    <mergeCell ref="O99:O101"/>
-    <mergeCell ref="P99:P101"/>
-    <mergeCell ref="Q96:Q98"/>
-    <mergeCell ref="H96:H98"/>
-    <mergeCell ref="I96:I98"/>
-    <mergeCell ref="J96:J98"/>
-    <mergeCell ref="K96:K98"/>
-    <mergeCell ref="L96:L98"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="D96:D98"/>
-    <mergeCell ref="E96:E98"/>
-    <mergeCell ref="F96:F98"/>
-    <mergeCell ref="G96:G98"/>
-    <mergeCell ref="M93:M95"/>
-    <mergeCell ref="N93:N95"/>
-    <mergeCell ref="O93:O95"/>
-    <mergeCell ref="P93:P95"/>
-    <mergeCell ref="Q93:Q95"/>
-    <mergeCell ref="H93:H95"/>
-    <mergeCell ref="I93:I95"/>
-    <mergeCell ref="J93:J95"/>
-    <mergeCell ref="K93:K95"/>
-    <mergeCell ref="L93:L95"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="D90:D92"/>
-    <mergeCell ref="E90:E92"/>
-    <mergeCell ref="F90:F92"/>
-    <mergeCell ref="G90:G92"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="E93:E95"/>
-    <mergeCell ref="F93:F95"/>
-    <mergeCell ref="G93:G95"/>
-    <mergeCell ref="Q87:Q89"/>
-    <mergeCell ref="H87:H89"/>
-    <mergeCell ref="I87:I89"/>
-    <mergeCell ref="J87:J89"/>
-    <mergeCell ref="K87:K89"/>
-    <mergeCell ref="L87:L89"/>
-    <mergeCell ref="Q90:Q92"/>
-    <mergeCell ref="H90:H92"/>
-    <mergeCell ref="I90:I92"/>
-    <mergeCell ref="J90:J92"/>
-    <mergeCell ref="K90:K92"/>
-    <mergeCell ref="L90:L92"/>
-    <mergeCell ref="M90:M92"/>
-    <mergeCell ref="N90:N92"/>
-    <mergeCell ref="O90:O92"/>
-    <mergeCell ref="P90:P92"/>
-    <mergeCell ref="C87:C89"/>
-    <mergeCell ref="D87:D89"/>
-    <mergeCell ref="E87:E89"/>
-    <mergeCell ref="F87:F89"/>
-    <mergeCell ref="G87:G89"/>
-    <mergeCell ref="M84:M86"/>
-    <mergeCell ref="N84:N86"/>
-    <mergeCell ref="O84:O86"/>
-    <mergeCell ref="P84:P86"/>
-    <mergeCell ref="M87:M89"/>
-    <mergeCell ref="N87:N89"/>
-    <mergeCell ref="O87:O89"/>
-    <mergeCell ref="P87:P89"/>
-    <mergeCell ref="Q84:Q86"/>
-    <mergeCell ref="H84:H86"/>
-    <mergeCell ref="I84:I86"/>
-    <mergeCell ref="J84:J86"/>
-    <mergeCell ref="K84:K86"/>
-    <mergeCell ref="L84:L86"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="D84:D86"/>
-    <mergeCell ref="E84:E86"/>
-    <mergeCell ref="F84:F86"/>
-    <mergeCell ref="G84:G86"/>
-    <mergeCell ref="M81:M83"/>
-    <mergeCell ref="N81:N83"/>
-    <mergeCell ref="O81:O83"/>
-    <mergeCell ref="P81:P83"/>
-    <mergeCell ref="Q81:Q83"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="K81:K83"/>
-    <mergeCell ref="L81:L83"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="D78:D80"/>
-    <mergeCell ref="E78:E80"/>
-    <mergeCell ref="F78:F80"/>
-    <mergeCell ref="G78:G80"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="E81:E83"/>
-    <mergeCell ref="F81:F83"/>
-    <mergeCell ref="G81:G83"/>
-    <mergeCell ref="Q75:Q77"/>
-    <mergeCell ref="H75:H77"/>
-    <mergeCell ref="I75:I77"/>
-    <mergeCell ref="J75:J77"/>
-    <mergeCell ref="K75:K77"/>
-    <mergeCell ref="L75:L77"/>
-    <mergeCell ref="Q78:Q80"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="K78:K80"/>
-    <mergeCell ref="L78:L80"/>
-    <mergeCell ref="M78:M80"/>
-    <mergeCell ref="N78:N80"/>
-    <mergeCell ref="O78:O80"/>
-    <mergeCell ref="P78:P80"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="D75:D77"/>
-    <mergeCell ref="E75:E77"/>
-    <mergeCell ref="F75:F77"/>
-    <mergeCell ref="G75:G77"/>
-    <mergeCell ref="M72:M74"/>
-    <mergeCell ref="N72:N74"/>
-    <mergeCell ref="O72:O74"/>
-    <mergeCell ref="P72:P74"/>
-    <mergeCell ref="M75:M77"/>
-    <mergeCell ref="N75:N77"/>
-    <mergeCell ref="O75:O77"/>
-    <mergeCell ref="P75:P77"/>
-    <mergeCell ref="Q72:Q74"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="I72:I74"/>
-    <mergeCell ref="J72:J74"/>
-    <mergeCell ref="K72:K74"/>
-    <mergeCell ref="L72:L74"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="E72:E74"/>
-    <mergeCell ref="F72:F74"/>
-    <mergeCell ref="G72:G74"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="N69:N71"/>
-    <mergeCell ref="O69:O71"/>
-    <mergeCell ref="P69:P71"/>
-    <mergeCell ref="Q69:Q71"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="D66:D68"/>
-    <mergeCell ref="E66:E68"/>
-    <mergeCell ref="F66:F68"/>
-    <mergeCell ref="G66:G68"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="E69:E71"/>
-    <mergeCell ref="F69:F71"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="Q63:Q65"/>
-    <mergeCell ref="H63:H65"/>
-    <mergeCell ref="I63:I65"/>
-    <mergeCell ref="J63:J65"/>
-    <mergeCell ref="K63:K65"/>
-    <mergeCell ref="L63:L65"/>
-    <mergeCell ref="Q66:Q68"/>
-    <mergeCell ref="H66:H68"/>
-    <mergeCell ref="I66:I68"/>
-    <mergeCell ref="J66:J68"/>
-    <mergeCell ref="K66:K68"/>
-    <mergeCell ref="L66:L68"/>
-    <mergeCell ref="M66:M68"/>
-    <mergeCell ref="N66:N68"/>
-    <mergeCell ref="O66:O68"/>
-    <mergeCell ref="P66:P68"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
-    <mergeCell ref="E63:E65"/>
-    <mergeCell ref="F63:F65"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="M60:M62"/>
-    <mergeCell ref="N60:N62"/>
-    <mergeCell ref="O60:O62"/>
-    <mergeCell ref="P60:P62"/>
-    <mergeCell ref="M63:M65"/>
-    <mergeCell ref="N63:N65"/>
-    <mergeCell ref="O63:O65"/>
-    <mergeCell ref="P63:P65"/>
-    <mergeCell ref="Q60:Q62"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="J60:J62"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="L60:L62"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="E60:E62"/>
-    <mergeCell ref="F60:F62"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="M57:M59"/>
-    <mergeCell ref="N57:N59"/>
-    <mergeCell ref="O57:O59"/>
-    <mergeCell ref="P57:P59"/>
-    <mergeCell ref="Q57:Q59"/>
-    <mergeCell ref="H57:H59"/>
-    <mergeCell ref="I57:I59"/>
-    <mergeCell ref="J57:J59"/>
-    <mergeCell ref="K57:K59"/>
-    <mergeCell ref="L57:L59"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="D54:D56"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="Q51:Q53"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="K51:K53"/>
-    <mergeCell ref="L51:L53"/>
-    <mergeCell ref="Q54:Q56"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="I54:I56"/>
-    <mergeCell ref="J54:J56"/>
-    <mergeCell ref="K54:K56"/>
-    <mergeCell ref="L54:L56"/>
-    <mergeCell ref="M54:M56"/>
-    <mergeCell ref="N54:N56"/>
-    <mergeCell ref="O54:O56"/>
-    <mergeCell ref="P54:P56"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="O5:O7"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="K5:K7"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M11:M13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="O11:O13"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="O14:O16"/>
+    <mergeCell ref="P14:P16"/>
+    <mergeCell ref="Q14:Q16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:M16"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="O18:O20"/>
+    <mergeCell ref="P18:P20"/>
+    <mergeCell ref="Q18:Q20"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="L18:L20"/>
+    <mergeCell ref="Q21:Q23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="K21:K23"/>
+    <mergeCell ref="L21:L23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="O21:O23"/>
+    <mergeCell ref="P21:P23"/>
+    <mergeCell ref="M24:M26"/>
+    <mergeCell ref="N24:N26"/>
+    <mergeCell ref="O24:O26"/>
+    <mergeCell ref="P24:P26"/>
+    <mergeCell ref="Q24:Q26"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="J24:J26"/>
+    <mergeCell ref="K24:K26"/>
+    <mergeCell ref="L24:L26"/>
+    <mergeCell ref="Q27:Q29"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="K27:K29"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="M27:M29"/>
+    <mergeCell ref="N27:N29"/>
+    <mergeCell ref="O27:O29"/>
+    <mergeCell ref="P27:P29"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="M30:M32"/>
+    <mergeCell ref="N30:N32"/>
+    <mergeCell ref="O30:O32"/>
+    <mergeCell ref="P30:P32"/>
+    <mergeCell ref="Q30:Q32"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="I30:I32"/>
+    <mergeCell ref="J30:J32"/>
+    <mergeCell ref="K30:K32"/>
+    <mergeCell ref="L30:L32"/>
+    <mergeCell ref="Q35:Q37"/>
+    <mergeCell ref="H35:H37"/>
+    <mergeCell ref="I35:I37"/>
+    <mergeCell ref="J35:J37"/>
+    <mergeCell ref="K35:K37"/>
+    <mergeCell ref="L35:L37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="M35:M37"/>
+    <mergeCell ref="N35:N37"/>
+    <mergeCell ref="O35:O37"/>
+    <mergeCell ref="P35:P37"/>
+    <mergeCell ref="M38:M40"/>
+    <mergeCell ref="N38:N40"/>
+    <mergeCell ref="O38:O40"/>
+    <mergeCell ref="P38:P40"/>
+    <mergeCell ref="Q38:Q40"/>
+    <mergeCell ref="H38:H40"/>
+    <mergeCell ref="I38:I40"/>
+    <mergeCell ref="J38:J40"/>
+    <mergeCell ref="K38:K40"/>
+    <mergeCell ref="L38:L40"/>
+    <mergeCell ref="Q41:Q43"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="K41:K43"/>
+    <mergeCell ref="L41:L43"/>
+    <mergeCell ref="M41:M43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="N41:N43"/>
+    <mergeCell ref="O41:O43"/>
+    <mergeCell ref="P41:P43"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="O51:O53"/>
+    <mergeCell ref="P51:P53"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="O44:O46"/>
+    <mergeCell ref="P44:P46"/>
     <mergeCell ref="Q44:Q46"/>
     <mergeCell ref="C48:C50"/>
     <mergeCell ref="D48:D50"/>
@@ -16177,202 +16041,342 @@
     <mergeCell ref="I44:I46"/>
     <mergeCell ref="J44:J46"/>
     <mergeCell ref="K44:K46"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="N41:N43"/>
-    <mergeCell ref="O41:O43"/>
-    <mergeCell ref="P41:P43"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="O51:O53"/>
-    <mergeCell ref="P51:P53"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="O44:O46"/>
-    <mergeCell ref="P44:P46"/>
-    <mergeCell ref="Q38:Q40"/>
-    <mergeCell ref="H38:H40"/>
-    <mergeCell ref="I38:I40"/>
-    <mergeCell ref="J38:J40"/>
-    <mergeCell ref="K38:K40"/>
-    <mergeCell ref="L38:L40"/>
-    <mergeCell ref="Q41:Q43"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="K41:K43"/>
-    <mergeCell ref="L41:L43"/>
-    <mergeCell ref="M41:M43"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="M35:M37"/>
-    <mergeCell ref="N35:N37"/>
-    <mergeCell ref="O35:O37"/>
-    <mergeCell ref="P35:P37"/>
-    <mergeCell ref="M38:M40"/>
-    <mergeCell ref="N38:N40"/>
-    <mergeCell ref="O38:O40"/>
-    <mergeCell ref="P38:P40"/>
-    <mergeCell ref="Q35:Q37"/>
-    <mergeCell ref="H35:H37"/>
-    <mergeCell ref="I35:I37"/>
-    <mergeCell ref="J35:J37"/>
-    <mergeCell ref="K35:K37"/>
-    <mergeCell ref="L35:L37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="M30:M32"/>
-    <mergeCell ref="N30:N32"/>
-    <mergeCell ref="O30:O32"/>
-    <mergeCell ref="P30:P32"/>
-    <mergeCell ref="Q30:Q32"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="I30:I32"/>
-    <mergeCell ref="J30:J32"/>
-    <mergeCell ref="K30:K32"/>
-    <mergeCell ref="L30:L32"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="Q24:Q26"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="J24:J26"/>
-    <mergeCell ref="K24:K26"/>
-    <mergeCell ref="L24:L26"/>
-    <mergeCell ref="Q27:Q29"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="I27:I29"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="K27:K29"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="M27:M29"/>
-    <mergeCell ref="N27:N29"/>
-    <mergeCell ref="O27:O29"/>
-    <mergeCell ref="P27:P29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="M21:M23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="O21:O23"/>
-    <mergeCell ref="P21:P23"/>
-    <mergeCell ref="M24:M26"/>
-    <mergeCell ref="N24:N26"/>
-    <mergeCell ref="O24:O26"/>
-    <mergeCell ref="P24:P26"/>
-    <mergeCell ref="Q21:Q23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="L21:L23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="O18:O20"/>
-    <mergeCell ref="P18:P20"/>
-    <mergeCell ref="Q18:Q20"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="J18:J20"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="L18:L20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="M11:M13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="N11:N13"/>
-    <mergeCell ref="O11:O13"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="N14:N16"/>
-    <mergeCell ref="O14:O16"/>
-    <mergeCell ref="P14:P16"/>
-    <mergeCell ref="Q14:Q16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="K14:K16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:M16"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="L8:L10"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="K5:K7"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="O8:O10"/>
-    <mergeCell ref="P8:P10"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="O5:O7"/>
-    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="Q51:Q53"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="K51:K53"/>
+    <mergeCell ref="L51:L53"/>
+    <mergeCell ref="Q54:Q56"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="I54:I56"/>
+    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="K54:K56"/>
+    <mergeCell ref="L54:L56"/>
+    <mergeCell ref="M54:M56"/>
+    <mergeCell ref="N54:N56"/>
+    <mergeCell ref="O54:O56"/>
+    <mergeCell ref="P54:P56"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="M57:M59"/>
+    <mergeCell ref="N57:N59"/>
+    <mergeCell ref="O57:O59"/>
+    <mergeCell ref="P57:P59"/>
+    <mergeCell ref="Q57:Q59"/>
+    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="I57:I59"/>
+    <mergeCell ref="J57:J59"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="L57:L59"/>
+    <mergeCell ref="Q60:Q62"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="L60:L62"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F60:F62"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="E63:E65"/>
+    <mergeCell ref="F63:F65"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="M60:M62"/>
+    <mergeCell ref="N60:N62"/>
+    <mergeCell ref="O60:O62"/>
+    <mergeCell ref="P60:P62"/>
+    <mergeCell ref="M63:M65"/>
+    <mergeCell ref="N63:N65"/>
+    <mergeCell ref="O63:O65"/>
+    <mergeCell ref="P63:P65"/>
+    <mergeCell ref="Q63:Q65"/>
+    <mergeCell ref="H63:H65"/>
+    <mergeCell ref="I63:I65"/>
+    <mergeCell ref="J63:J65"/>
+    <mergeCell ref="K63:K65"/>
+    <mergeCell ref="L63:L65"/>
+    <mergeCell ref="Q66:Q68"/>
+    <mergeCell ref="H66:H68"/>
+    <mergeCell ref="I66:I68"/>
+    <mergeCell ref="J66:J68"/>
+    <mergeCell ref="K66:K68"/>
+    <mergeCell ref="L66:L68"/>
+    <mergeCell ref="M66:M68"/>
+    <mergeCell ref="N66:N68"/>
+    <mergeCell ref="O66:O68"/>
+    <mergeCell ref="P66:P68"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="D66:D68"/>
+    <mergeCell ref="E66:E68"/>
+    <mergeCell ref="F66:F68"/>
+    <mergeCell ref="G66:G68"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="D69:D71"/>
+    <mergeCell ref="E69:E71"/>
+    <mergeCell ref="F69:F71"/>
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="N69:N71"/>
+    <mergeCell ref="O69:O71"/>
+    <mergeCell ref="P69:P71"/>
+    <mergeCell ref="Q69:Q71"/>
+    <mergeCell ref="H69:H71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="Q72:Q74"/>
+    <mergeCell ref="H72:H74"/>
+    <mergeCell ref="I72:I74"/>
+    <mergeCell ref="J72:J74"/>
+    <mergeCell ref="K72:K74"/>
+    <mergeCell ref="L72:L74"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="E72:E74"/>
+    <mergeCell ref="F72:F74"/>
+    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="D75:D77"/>
+    <mergeCell ref="E75:E77"/>
+    <mergeCell ref="F75:F77"/>
+    <mergeCell ref="G75:G77"/>
+    <mergeCell ref="M72:M74"/>
+    <mergeCell ref="N72:N74"/>
+    <mergeCell ref="O72:O74"/>
+    <mergeCell ref="P72:P74"/>
+    <mergeCell ref="M75:M77"/>
+    <mergeCell ref="N75:N77"/>
+    <mergeCell ref="O75:O77"/>
+    <mergeCell ref="P75:P77"/>
+    <mergeCell ref="Q75:Q77"/>
+    <mergeCell ref="H75:H77"/>
+    <mergeCell ref="I75:I77"/>
+    <mergeCell ref="J75:J77"/>
+    <mergeCell ref="K75:K77"/>
+    <mergeCell ref="L75:L77"/>
+    <mergeCell ref="Q78:Q80"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="K78:K80"/>
+    <mergeCell ref="L78:L80"/>
+    <mergeCell ref="M78:M80"/>
+    <mergeCell ref="N78:N80"/>
+    <mergeCell ref="O78:O80"/>
+    <mergeCell ref="P78:P80"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="D78:D80"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="F78:F80"/>
+    <mergeCell ref="G78:G80"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="E81:E83"/>
+    <mergeCell ref="F81:F83"/>
+    <mergeCell ref="G81:G83"/>
+    <mergeCell ref="M81:M83"/>
+    <mergeCell ref="N81:N83"/>
+    <mergeCell ref="O81:O83"/>
+    <mergeCell ref="P81:P83"/>
+    <mergeCell ref="Q81:Q83"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="K81:K83"/>
+    <mergeCell ref="L81:L83"/>
+    <mergeCell ref="Q84:Q86"/>
+    <mergeCell ref="H84:H86"/>
+    <mergeCell ref="I84:I86"/>
+    <mergeCell ref="J84:J86"/>
+    <mergeCell ref="K84:K86"/>
+    <mergeCell ref="L84:L86"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="D84:D86"/>
+    <mergeCell ref="E84:E86"/>
+    <mergeCell ref="F84:F86"/>
+    <mergeCell ref="G84:G86"/>
+    <mergeCell ref="C87:C89"/>
+    <mergeCell ref="D87:D89"/>
+    <mergeCell ref="E87:E89"/>
+    <mergeCell ref="F87:F89"/>
+    <mergeCell ref="G87:G89"/>
+    <mergeCell ref="M84:M86"/>
+    <mergeCell ref="N84:N86"/>
+    <mergeCell ref="O84:O86"/>
+    <mergeCell ref="P84:P86"/>
+    <mergeCell ref="M87:M89"/>
+    <mergeCell ref="N87:N89"/>
+    <mergeCell ref="O87:O89"/>
+    <mergeCell ref="P87:P89"/>
+    <mergeCell ref="Q87:Q89"/>
+    <mergeCell ref="H87:H89"/>
+    <mergeCell ref="I87:I89"/>
+    <mergeCell ref="J87:J89"/>
+    <mergeCell ref="K87:K89"/>
+    <mergeCell ref="L87:L89"/>
+    <mergeCell ref="Q90:Q92"/>
+    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="I90:I92"/>
+    <mergeCell ref="J90:J92"/>
+    <mergeCell ref="K90:K92"/>
+    <mergeCell ref="L90:L92"/>
+    <mergeCell ref="M90:M92"/>
+    <mergeCell ref="N90:N92"/>
+    <mergeCell ref="O90:O92"/>
+    <mergeCell ref="P90:P92"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="D90:D92"/>
+    <mergeCell ref="E90:E92"/>
+    <mergeCell ref="F90:F92"/>
+    <mergeCell ref="G90:G92"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="E93:E95"/>
+    <mergeCell ref="F93:F95"/>
+    <mergeCell ref="G93:G95"/>
+    <mergeCell ref="M93:M95"/>
+    <mergeCell ref="N93:N95"/>
+    <mergeCell ref="O93:O95"/>
+    <mergeCell ref="P93:P95"/>
+    <mergeCell ref="Q93:Q95"/>
+    <mergeCell ref="H93:H95"/>
+    <mergeCell ref="I93:I95"/>
+    <mergeCell ref="J93:J95"/>
+    <mergeCell ref="K93:K95"/>
+    <mergeCell ref="L93:L95"/>
+    <mergeCell ref="Q96:Q98"/>
+    <mergeCell ref="H96:H98"/>
+    <mergeCell ref="I96:I98"/>
+    <mergeCell ref="J96:J98"/>
+    <mergeCell ref="K96:K98"/>
+    <mergeCell ref="L96:L98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="D96:D98"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="F96:F98"/>
+    <mergeCell ref="G96:G98"/>
+    <mergeCell ref="C99:C101"/>
+    <mergeCell ref="D99:D101"/>
+    <mergeCell ref="E99:E101"/>
+    <mergeCell ref="F99:F101"/>
+    <mergeCell ref="G99:G101"/>
+    <mergeCell ref="M96:M98"/>
+    <mergeCell ref="N96:N98"/>
+    <mergeCell ref="O96:O98"/>
+    <mergeCell ref="P96:P98"/>
+    <mergeCell ref="M99:M101"/>
+    <mergeCell ref="N99:N101"/>
+    <mergeCell ref="O99:O101"/>
+    <mergeCell ref="P99:P101"/>
+    <mergeCell ref="Q99:Q101"/>
+    <mergeCell ref="H99:H101"/>
+    <mergeCell ref="I99:I101"/>
+    <mergeCell ref="J99:J101"/>
+    <mergeCell ref="K99:K101"/>
+    <mergeCell ref="L99:L101"/>
+    <mergeCell ref="Q102:Q104"/>
+    <mergeCell ref="H102:H104"/>
+    <mergeCell ref="I102:I104"/>
+    <mergeCell ref="J102:J104"/>
+    <mergeCell ref="K102:K104"/>
+    <mergeCell ref="L102:L104"/>
+    <mergeCell ref="M102:M104"/>
+    <mergeCell ref="N102:N104"/>
+    <mergeCell ref="O102:O104"/>
+    <mergeCell ref="P102:P104"/>
+    <mergeCell ref="C102:C104"/>
+    <mergeCell ref="D102:D104"/>
+    <mergeCell ref="E102:E104"/>
+    <mergeCell ref="F102:F104"/>
+    <mergeCell ref="G102:G104"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="C105:C107"/>
+    <mergeCell ref="D105:D107"/>
+    <mergeCell ref="E105:E107"/>
+    <mergeCell ref="F105:F107"/>
+    <mergeCell ref="G105:G107"/>
+    <mergeCell ref="M108:M110"/>
+    <mergeCell ref="N108:N110"/>
+    <mergeCell ref="O108:O110"/>
+    <mergeCell ref="P108:P110"/>
+    <mergeCell ref="Q108:Q110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="I108:I110"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="K108:K110"/>
+    <mergeCell ref="L108:L110"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:D115"/>
+    <mergeCell ref="E113:E115"/>
+    <mergeCell ref="F113:F115"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="M113:M115"/>
+    <mergeCell ref="N113:N115"/>
+    <mergeCell ref="O113:O115"/>
+    <mergeCell ref="P113:P115"/>
+    <mergeCell ref="Q113:Q115"/>
+    <mergeCell ref="H113:H115"/>
+    <mergeCell ref="I113:I115"/>
+    <mergeCell ref="J113:J115"/>
+    <mergeCell ref="K113:K115"/>
+    <mergeCell ref="L113:L115"/>
+    <mergeCell ref="Q116:Q119"/>
+    <mergeCell ref="H116:H119"/>
+    <mergeCell ref="I116:I119"/>
+    <mergeCell ref="J116:J119"/>
+    <mergeCell ref="K116:K119"/>
+    <mergeCell ref="L116:L119"/>
+    <mergeCell ref="M116:M119"/>
+    <mergeCell ref="N116:N119"/>
+    <mergeCell ref="O116:O119"/>
+    <mergeCell ref="P116:P119"/>
+    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="D116:D119"/>
+    <mergeCell ref="E116:E119"/>
+    <mergeCell ref="F116:F119"/>
+    <mergeCell ref="G116:G119"/>
+    <mergeCell ref="C120:C122"/>
+    <mergeCell ref="D120:D122"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="F120:F122"/>
+    <mergeCell ref="G120:G122"/>
+    <mergeCell ref="M120:M122"/>
+    <mergeCell ref="N120:N122"/>
+    <mergeCell ref="O120:O122"/>
+    <mergeCell ref="P120:P122"/>
+    <mergeCell ref="Q120:Q122"/>
+    <mergeCell ref="H120:H122"/>
+    <mergeCell ref="I120:I122"/>
+    <mergeCell ref="J120:J122"/>
+    <mergeCell ref="K120:K122"/>
+    <mergeCell ref="L120:L122"/>
+    <mergeCell ref="Q105:Q107"/>
+    <mergeCell ref="H105:H107"/>
+    <mergeCell ref="I105:I107"/>
+    <mergeCell ref="J105:J107"/>
+    <mergeCell ref="K105:K107"/>
+    <mergeCell ref="L105:L107"/>
+    <mergeCell ref="M105:M107"/>
+    <mergeCell ref="N105:N107"/>
+    <mergeCell ref="O105:O107"/>
+    <mergeCell ref="P105:P107"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -16395,197 +16399,197 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8B1907-1808-45DB-89DB-D7AD15506F3A}">
   <dimension ref="B1:B38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="38" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="38" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
         <v>358</v>
       </c>
@@ -16601,126 +16605,126 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A97597-49CE-4804-805A-84A20592BE98}">
   <dimension ref="A1:BC108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" style="1" customWidth="1"/>
-    <col min="12" max="17" width="17.7265625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.54296875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="1" customWidth="1"/>
+    <col min="12" max="17" width="17.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5546875" style="1" customWidth="1"/>
     <col min="20" max="20" width="15" style="1" customWidth="1"/>
-    <col min="21" max="25" width="13.1796875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16.54296875" style="1" customWidth="1"/>
-    <col min="27" max="28" width="13.1796875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="19.453125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.81640625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.1796875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.453125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="30.7265625" style="1" customWidth="1"/>
-    <col min="34" max="36" width="13.1796875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.54296875" style="1" customWidth="1"/>
-    <col min="38" max="43" width="16.7265625" style="1" customWidth="1"/>
-    <col min="44" max="45" width="13.26953125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="23.81640625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="22.54296875" style="1" customWidth="1"/>
-    <col min="48" max="48" width="24.1796875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="27.81640625" style="1" customWidth="1"/>
-    <col min="50" max="50" width="24.7265625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="22.7265625" style="1" customWidth="1"/>
-    <col min="52" max="55" width="13.26953125" style="1" customWidth="1"/>
-    <col min="56" max="16384" width="11.453125" style="1"/>
+    <col min="21" max="25" width="13.21875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16.5546875" style="1" customWidth="1"/>
+    <col min="27" max="28" width="13.21875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="13.77734375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="13.21875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="13.44140625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="30.77734375" style="1" customWidth="1"/>
+    <col min="34" max="36" width="13.21875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5546875" style="1" customWidth="1"/>
+    <col min="38" max="43" width="16.77734375" style="1" customWidth="1"/>
+    <col min="44" max="45" width="13.21875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="23.77734375" style="1" customWidth="1"/>
+    <col min="47" max="47" width="22.5546875" style="1" customWidth="1"/>
+    <col min="48" max="48" width="24.21875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="27.77734375" style="1" customWidth="1"/>
+    <col min="50" max="50" width="24.77734375" style="1" customWidth="1"/>
+    <col min="51" max="51" width="22.77734375" style="1" customWidth="1"/>
+    <col min="52" max="55" width="13.21875" style="1" customWidth="1"/>
+    <col min="56" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.5">
-      <c r="S1" s="173" t="s">
+      <c r="S1" s="174" t="s">
         <v>359</v>
       </c>
-      <c r="T1" s="173"/>
-      <c r="U1" s="173"/>
-      <c r="V1" s="173"/>
-      <c r="W1" s="173"/>
-      <c r="X1" s="173"/>
-      <c r="Y1" s="173"/>
-      <c r="Z1" s="173"/>
-      <c r="AA1" s="173"/>
-      <c r="AB1" s="173"/>
-      <c r="AC1" s="173"/>
-      <c r="AD1" s="173"/>
-      <c r="AE1" s="173"/>
-      <c r="AF1" s="173"/>
-      <c r="AG1" s="173"/>
+      <c r="T1" s="174"/>
+      <c r="U1" s="174"/>
+      <c r="V1" s="174"/>
+      <c r="W1" s="174"/>
+      <c r="X1" s="174"/>
+      <c r="Y1" s="174"/>
+      <c r="Z1" s="174"/>
+      <c r="AA1" s="174"/>
+      <c r="AB1" s="174"/>
+      <c r="AC1" s="174"/>
+      <c r="AD1" s="174"/>
+      <c r="AE1" s="174"/>
+      <c r="AF1" s="174"/>
+      <c r="AG1" s="174"/>
       <c r="AH1" s="14"/>
       <c r="AI1" s="14"/>
       <c r="AJ1" s="14"/>
-      <c r="AL1" s="173" t="s">
+      <c r="AL1" s="174" t="s">
         <v>360</v>
       </c>
-      <c r="AM1" s="173"/>
-      <c r="AN1" s="173"/>
-      <c r="AO1" s="173"/>
-      <c r="AP1" s="173"/>
-      <c r="AQ1" s="173"/>
+      <c r="AM1" s="174"/>
+      <c r="AN1" s="174"/>
+      <c r="AO1" s="174"/>
+      <c r="AP1" s="174"/>
+      <c r="AQ1" s="174"/>
       <c r="AR1" s="14"/>
       <c r="AS1" s="14"/>
-      <c r="AT1" s="173" t="s">
+      <c r="AT1" s="174" t="s">
         <v>361</v>
       </c>
-      <c r="AU1" s="173"/>
-      <c r="AV1" s="173"/>
-      <c r="AW1" s="173"/>
-      <c r="AX1" s="173"/>
-      <c r="AY1" s="173"/>
+      <c r="AU1" s="174"/>
+      <c r="AV1" s="174"/>
+      <c r="AW1" s="174"/>
+      <c r="AX1" s="174"/>
+      <c r="AY1" s="174"/>
       <c r="AZ1" s="14"/>
       <c r="BC1" s="14"/>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.5">
-      <c r="L2" s="173" t="s">
+      <c r="L2" s="174" t="s">
         <v>362</v>
       </c>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
-      <c r="O2" s="173"/>
-      <c r="P2" s="173"/>
-      <c r="Q2" s="173"/>
-      <c r="S2" s="174" t="s">
+      <c r="M2" s="174"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="174"/>
+      <c r="P2" s="174"/>
+      <c r="Q2" s="174"/>
+      <c r="S2" s="175" t="s">
         <v>363</v>
       </c>
-      <c r="T2" s="174"/>
-      <c r="U2" s="174"/>
-      <c r="V2" s="174"/>
-      <c r="W2" s="174"/>
-      <c r="X2" s="174"/>
-      <c r="Y2" s="174" t="s">
+      <c r="T2" s="175"/>
+      <c r="U2" s="175"/>
+      <c r="V2" s="175"/>
+      <c r="W2" s="175"/>
+      <c r="X2" s="175"/>
+      <c r="Y2" s="175" t="s">
         <v>364</v>
       </c>
-      <c r="Z2" s="174"/>
-      <c r="AA2" s="174"/>
-      <c r="AB2" s="174"/>
-      <c r="AC2" s="174" t="s">
+      <c r="Z2" s="175"/>
+      <c r="AA2" s="175"/>
+      <c r="AB2" s="175"/>
+      <c r="AC2" s="175" t="s">
         <v>365</v>
       </c>
-      <c r="AD2" s="174"/>
-      <c r="AE2" s="174"/>
-      <c r="AF2" s="174"/>
-      <c r="AG2" s="174"/>
+      <c r="AD2" s="175"/>
+      <c r="AE2" s="175"/>
+      <c r="AF2" s="175"/>
+      <c r="AG2" s="175"/>
       <c r="AH2" s="14"/>
       <c r="AI2" s="14"/>
       <c r="AJ2" s="14"/>
-      <c r="AL2" s="173"/>
-      <c r="AM2" s="173"/>
-      <c r="AN2" s="173"/>
-      <c r="AO2" s="173"/>
-      <c r="AP2" s="173"/>
-      <c r="AQ2" s="173"/>
+      <c r="AL2" s="174"/>
+      <c r="AM2" s="174"/>
+      <c r="AN2" s="174"/>
+      <c r="AO2" s="174"/>
+      <c r="AP2" s="174"/>
+      <c r="AQ2" s="174"/>
       <c r="AR2" s="14"/>
       <c r="AS2" s="14"/>
       <c r="AT2" s="14"/>
@@ -16817,16 +16821,16 @@
       <c r="AG3" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="AL3" s="175" t="s">
+      <c r="AL3" s="173" t="s">
         <v>387</v>
       </c>
-      <c r="AM3" s="175"/>
-      <c r="AN3" s="175"/>
-      <c r="AO3" s="175" t="s">
+      <c r="AM3" s="173"/>
+      <c r="AN3" s="173"/>
+      <c r="AO3" s="173" t="s">
         <v>388</v>
       </c>
-      <c r="AP3" s="175"/>
-      <c r="AQ3" s="175"/>
+      <c r="AP3" s="173"/>
+      <c r="AQ3" s="173"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
@@ -21783,16 +21787,16 @@
     <sortCondition ref="AU5:AU66"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
+    <mergeCell ref="AL2:AQ2"/>
     <mergeCell ref="AL3:AN3"/>
     <mergeCell ref="AO3:AQ3"/>
     <mergeCell ref="AT1:AY1"/>
     <mergeCell ref="S1:AG1"/>
     <mergeCell ref="AL1:AQ1"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
-    <mergeCell ref="AL2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
